--- a/01_Input/00_CO Validation/Bangladesh - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Bangladesh - Energy Projects.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27002"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27010"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UNDP-BD\Energy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="444" documentId="13_ncr:1_{F9E229CD-093B-4957-8526-AA7B64B04BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0DE3C47-EA5C-4767-A424-B05E324C092A}"/>
+  <xr:revisionPtr revIDLastSave="445" documentId="13_ncr:1_{F9E229CD-093B-4957-8526-AA7B64B04BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DBE5F1C-56F9-419A-B81B-D0BF652D166A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -954,7 +954,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1007,12 +1007,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFCD5B4"/>
         <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1266,7 +1260,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="267">
+  <cellXfs count="251">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1609,204 +1603,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="8" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1837,47 +1642,35 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1906,18 +1699,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1936,30 +1723,6 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2014,7 +1777,190 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2359,847 +2305,847 @@
   <dimension ref="A1:R24"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" style="132" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33" style="132" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" style="132" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" style="132" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.42578125" style="132" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" style="132" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" style="132" customWidth="1"/>
-    <col min="8" max="8" width="35.42578125" style="132" customWidth="1"/>
-    <col min="9" max="9" width="93.140625" style="132" customWidth="1"/>
-    <col min="10" max="10" width="19.42578125" style="132" customWidth="1"/>
-    <col min="11" max="11" width="18" style="132" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" style="132"/>
-    <col min="13" max="13" width="8.85546875" style="132"/>
-    <col min="14" max="14" width="31.7109375" style="132" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16" style="132" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.85546875" style="132"/>
+    <col min="1" max="1" width="9.28515625" style="130" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33" style="130" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" style="130" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" style="130" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.42578125" style="130" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" style="130" customWidth="1"/>
+    <col min="7" max="7" width="21.42578125" style="130" customWidth="1"/>
+    <col min="8" max="8" width="35.42578125" style="130" customWidth="1"/>
+    <col min="9" max="9" width="93.140625" style="130" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" style="130" customWidth="1"/>
+    <col min="11" max="11" width="18" style="130" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" style="130"/>
+    <col min="13" max="13" width="8.85546875" style="130"/>
+    <col min="14" max="14" width="31.7109375" style="130" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16" style="130" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.85546875" style="130"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="45.75">
-      <c r="A1" s="143" t="s">
+      <c r="A1" s="188" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="149" t="s">
+      <c r="B1" s="189" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="149" t="s">
+      <c r="C1" s="189" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="149" t="s">
+      <c r="D1" s="189" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="143" t="s">
+      <c r="E1" s="188" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="143" t="s">
+      <c r="F1" s="188" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="143" t="s">
+      <c r="G1" s="188" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="143" t="s">
+      <c r="H1" s="188" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="143" t="s">
+      <c r="I1" s="188" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="143" t="s">
+      <c r="J1" s="188" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="143" t="s">
+      <c r="K1" s="188" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="143" t="s">
+      <c r="L1" s="188" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="143" t="s">
+      <c r="M1" s="188" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="143" t="s">
+      <c r="N1" s="188" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="143" t="s">
+      <c r="O1" s="188" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="143" t="s">
+      <c r="P1" s="188" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="143" t="s">
+      <c r="Q1" s="188" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="143" t="s">
+      <c r="R1" s="188" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" s="135" customFormat="1" ht="91.5" customHeight="1">
-      <c r="A2" s="150" t="s">
+    <row r="2" spans="1:18" s="131" customFormat="1" ht="91.5" customHeight="1">
+      <c r="A2" s="190" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="133" t="s">
+      <c r="B2" s="191" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="134" t="s">
+      <c r="C2" s="192" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="151">
+      <c r="D2" s="193">
         <v>3767810</v>
       </c>
-      <c r="E2" s="99" t="s">
+      <c r="E2" s="194" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="99" t="s">
+      <c r="F2" s="194" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="144"/>
-      <c r="H2" s="99">
+      <c r="G2" s="188"/>
+      <c r="H2" s="194">
         <v>1</v>
       </c>
-      <c r="I2" s="265" t="s">
+      <c r="I2" s="249" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="214" t="s">
+      <c r="J2" s="195" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="215"/>
-      <c r="L2" s="215" t="s">
+      <c r="K2" s="196"/>
+      <c r="L2" s="196" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="71" t="s">
+      <c r="M2" s="194" t="s">
         <v>26</v>
       </c>
-      <c r="N2" s="71" t="s">
+      <c r="N2" s="194" t="s">
         <v>27</v>
       </c>
-      <c r="O2" s="71" t="s">
+      <c r="O2" s="194" t="s">
         <v>28</v>
       </c>
-      <c r="P2" s="71"/>
-      <c r="Q2" s="71"/>
-      <c r="R2" s="71"/>
+      <c r="P2" s="194"/>
+      <c r="Q2" s="194"/>
+      <c r="R2" s="194"/>
     </row>
     <row r="3" spans="1:18" ht="45.75">
-      <c r="A3" s="152"/>
-      <c r="B3" s="136"/>
-      <c r="C3" s="137"/>
-      <c r="D3" s="153"/>
-      <c r="E3" s="148" t="s">
+      <c r="A3" s="197"/>
+      <c r="B3" s="198"/>
+      <c r="C3" s="199"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="201" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="71" t="s">
+      <c r="F3" s="194" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="143"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="219"/>
-      <c r="J3" s="176"/>
-      <c r="K3" s="216"/>
-      <c r="L3" s="215"/>
-      <c r="M3" s="71"/>
-      <c r="N3" s="71"/>
-      <c r="O3" s="71"/>
-      <c r="P3" s="71"/>
-      <c r="Q3" s="71"/>
-      <c r="R3" s="71"/>
+      <c r="G3" s="188"/>
+      <c r="H3" s="194"/>
+      <c r="I3" s="202"/>
+      <c r="J3" s="203"/>
+      <c r="K3" s="204"/>
+      <c r="L3" s="196"/>
+      <c r="M3" s="194"/>
+      <c r="N3" s="194"/>
+      <c r="O3" s="194"/>
+      <c r="P3" s="194"/>
+      <c r="Q3" s="194"/>
+      <c r="R3" s="194"/>
     </row>
     <row r="4" spans="1:18" ht="154.5" customHeight="1">
-      <c r="A4" s="154"/>
-      <c r="B4" s="138"/>
-      <c r="C4" s="139"/>
-      <c r="D4" s="155"/>
-      <c r="E4" s="71" t="s">
+      <c r="A4" s="205"/>
+      <c r="B4" s="206"/>
+      <c r="C4" s="207"/>
+      <c r="D4" s="208"/>
+      <c r="E4" s="194" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="147" t="s">
+      <c r="F4" s="209" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="143"/>
-      <c r="H4" s="71">
+      <c r="G4" s="188"/>
+      <c r="H4" s="194">
         <v>1573000</v>
       </c>
-      <c r="I4" s="219"/>
-      <c r="J4" s="175"/>
-      <c r="K4" s="216"/>
-      <c r="L4" s="215"/>
-      <c r="M4" s="71"/>
-      <c r="N4" s="71"/>
-      <c r="O4" s="71"/>
-      <c r="P4" s="71"/>
-      <c r="Q4" s="71"/>
-      <c r="R4" s="71"/>
-    </row>
-    <row r="5" spans="1:18" s="135" customFormat="1" ht="60.75">
-      <c r="A5" s="162" t="s">
+      <c r="I4" s="202"/>
+      <c r="J4" s="210"/>
+      <c r="K4" s="204"/>
+      <c r="L4" s="196"/>
+      <c r="M4" s="194"/>
+      <c r="N4" s="194"/>
+      <c r="O4" s="194"/>
+      <c r="P4" s="194"/>
+      <c r="Q4" s="194"/>
+      <c r="R4" s="194"/>
+    </row>
+    <row r="5" spans="1:18" s="131" customFormat="1" ht="60.75">
+      <c r="A5" s="211" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="161" t="s">
+      <c r="B5" s="212" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="156"/>
-      <c r="D5" s="157">
+      <c r="C5" s="213"/>
+      <c r="D5" s="214">
         <v>1788991</v>
       </c>
-      <c r="E5" s="169" t="s">
+      <c r="E5" s="215" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="170" t="s">
+      <c r="F5" s="216" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="171"/>
-      <c r="H5" s="172">
+      <c r="G5" s="188"/>
+      <c r="H5" s="194">
         <v>100000</v>
       </c>
-      <c r="I5" s="215" t="s">
+      <c r="I5" s="196" t="s">
         <v>37</v>
       </c>
       <c r="J5" s="217" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="215"/>
-      <c r="L5" s="215"/>
-      <c r="M5" s="71"/>
-      <c r="N5" s="71"/>
-      <c r="O5" s="71"/>
-      <c r="P5" s="71"/>
-      <c r="Q5" s="71"/>
-      <c r="R5" s="71"/>
+      <c r="K5" s="196"/>
+      <c r="L5" s="196"/>
+      <c r="M5" s="194"/>
+      <c r="N5" s="194"/>
+      <c r="O5" s="194"/>
+      <c r="P5" s="194"/>
+      <c r="Q5" s="194"/>
+      <c r="R5" s="194"/>
     </row>
     <row r="6" spans="1:18" ht="81" customHeight="1">
-      <c r="A6" s="163"/>
-      <c r="B6" s="164"/>
-      <c r="C6" s="164"/>
-      <c r="D6" s="165"/>
-      <c r="E6" s="172" t="s">
+      <c r="A6" s="218"/>
+      <c r="B6" s="219"/>
+      <c r="C6" s="219"/>
+      <c r="D6" s="220"/>
+      <c r="E6" s="194" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="172" t="s">
+      <c r="F6" s="194" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="171">
+      <c r="G6" s="188">
         <v>0</v>
       </c>
-      <c r="H6" s="172">
+      <c r="H6" s="194">
         <v>15660</v>
       </c>
-      <c r="I6" s="219"/>
-      <c r="J6" s="218"/>
-      <c r="K6" s="216"/>
-      <c r="L6" s="215"/>
-      <c r="M6" s="71"/>
-      <c r="N6" s="71"/>
-      <c r="O6" s="71"/>
-      <c r="P6" s="71"/>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="71"/>
+      <c r="I6" s="202"/>
+      <c r="J6" s="221"/>
+      <c r="K6" s="204"/>
+      <c r="L6" s="196"/>
+      <c r="M6" s="194"/>
+      <c r="N6" s="194"/>
+      <c r="O6" s="194"/>
+      <c r="P6" s="194"/>
+      <c r="Q6" s="194"/>
+      <c r="R6" s="194"/>
     </row>
     <row r="7" spans="1:18" ht="200.25" customHeight="1">
-      <c r="A7" s="166"/>
-      <c r="B7" s="167"/>
-      <c r="C7" s="167"/>
-      <c r="D7" s="168"/>
-      <c r="E7" s="173" t="s">
+      <c r="A7" s="222"/>
+      <c r="B7" s="223"/>
+      <c r="C7" s="223"/>
+      <c r="D7" s="224"/>
+      <c r="E7" s="225" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="174" t="s">
+      <c r="F7" s="226" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="171">
+      <c r="G7" s="188">
         <v>0</v>
       </c>
-      <c r="H7" s="172">
+      <c r="H7" s="194">
         <v>200</v>
       </c>
-      <c r="I7" s="219"/>
-      <c r="J7" s="175"/>
-      <c r="K7" s="216"/>
-      <c r="L7" s="215"/>
-      <c r="M7" s="71"/>
-      <c r="N7" s="71"/>
-      <c r="O7" s="71"/>
-      <c r="P7" s="71"/>
-      <c r="Q7" s="71"/>
-      <c r="R7" s="71"/>
+      <c r="I7" s="202"/>
+      <c r="J7" s="210"/>
+      <c r="K7" s="204"/>
+      <c r="L7" s="196"/>
+      <c r="M7" s="194"/>
+      <c r="N7" s="194"/>
+      <c r="O7" s="194"/>
+      <c r="P7" s="194"/>
+      <c r="Q7" s="194"/>
+      <c r="R7" s="194"/>
     </row>
     <row r="8" spans="1:18" s="128" customFormat="1" ht="91.5">
-      <c r="A8" s="178"/>
-      <c r="B8" s="179" t="s">
+      <c r="A8" s="227"/>
+      <c r="B8" s="228" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="180"/>
-      <c r="D8" s="181">
+      <c r="C8" s="229"/>
+      <c r="D8" s="193">
         <v>9212322</v>
       </c>
-      <c r="E8" s="99" t="s">
+      <c r="E8" s="194" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="99" t="s">
+      <c r="F8" s="194" t="s">
         <v>42</v>
       </c>
-      <c r="G8" s="99">
+      <c r="G8" s="194">
         <v>0</v>
       </c>
-      <c r="H8" s="99">
+      <c r="H8" s="194">
         <v>1</v>
       </c>
-      <c r="I8" s="141" t="s">
+      <c r="I8" s="226" t="s">
         <v>43</v>
       </c>
-      <c r="J8" s="177" t="s">
+      <c r="J8" s="215" t="s">
         <v>44</v>
       </c>
-      <c r="K8" s="215"/>
-      <c r="L8" s="215"/>
-      <c r="M8" s="71"/>
-      <c r="N8" s="71"/>
-      <c r="O8" s="71"/>
-      <c r="P8" s="71"/>
-      <c r="Q8" s="71"/>
-      <c r="R8" s="71"/>
+      <c r="K8" s="196"/>
+      <c r="L8" s="196"/>
+      <c r="M8" s="194"/>
+      <c r="N8" s="194"/>
+      <c r="O8" s="194"/>
+      <c r="P8" s="194"/>
+      <c r="Q8" s="194"/>
+      <c r="R8" s="194"/>
     </row>
     <row r="9" spans="1:18" s="129" customFormat="1" ht="60.75">
-      <c r="A9" s="183"/>
-      <c r="B9" s="184"/>
-      <c r="C9" s="185"/>
-      <c r="D9" s="186"/>
-      <c r="E9" s="147" t="s">
+      <c r="A9" s="230"/>
+      <c r="B9" s="231"/>
+      <c r="C9" s="232"/>
+      <c r="D9" s="233"/>
+      <c r="E9" s="209" t="s">
         <v>45</v>
       </c>
-      <c r="F9" s="71" t="s">
+      <c r="F9" s="194" t="s">
         <v>46</v>
       </c>
-      <c r="G9" s="71">
+      <c r="G9" s="194">
         <v>0</v>
       </c>
-      <c r="H9" s="71">
+      <c r="H9" s="194">
         <v>80</v>
       </c>
-      <c r="I9" s="71" t="s">
+      <c r="I9" s="194" t="s">
         <v>47</v>
       </c>
-      <c r="J9" s="208"/>
-      <c r="K9" s="215"/>
-      <c r="L9" s="215"/>
-      <c r="M9" s="71"/>
-      <c r="N9" s="71"/>
-      <c r="O9" s="71"/>
-      <c r="P9" s="71"/>
-      <c r="Q9" s="71"/>
-      <c r="R9" s="71"/>
+      <c r="J9" s="234"/>
+      <c r="K9" s="196"/>
+      <c r="L9" s="196"/>
+      <c r="M9" s="194"/>
+      <c r="N9" s="194"/>
+      <c r="O9" s="194"/>
+      <c r="P9" s="194"/>
+      <c r="Q9" s="194"/>
+      <c r="R9" s="194"/>
     </row>
     <row r="10" spans="1:18" s="129" customFormat="1" ht="45.75">
-      <c r="A10" s="187"/>
-      <c r="B10" s="188"/>
-      <c r="C10" s="189"/>
-      <c r="D10" s="190"/>
-      <c r="E10" s="147" t="s">
+      <c r="A10" s="235"/>
+      <c r="B10" s="236"/>
+      <c r="C10" s="237"/>
+      <c r="D10" s="238"/>
+      <c r="E10" s="209" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="71" t="s">
+      <c r="F10" s="194" t="s">
         <v>48</v>
       </c>
-      <c r="G10" s="71">
+      <c r="G10" s="194">
         <v>0</v>
       </c>
-      <c r="H10" s="71">
+      <c r="H10" s="194">
         <v>2</v>
       </c>
-      <c r="I10" s="71" t="s">
+      <c r="I10" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="J10" s="209"/>
-      <c r="K10" s="215"/>
-      <c r="L10" s="215"/>
-      <c r="M10" s="71"/>
-      <c r="N10" s="71"/>
-      <c r="O10" s="71"/>
-      <c r="P10" s="71"/>
-      <c r="Q10" s="71"/>
-      <c r="R10" s="71"/>
+      <c r="J10" s="239"/>
+      <c r="K10" s="196"/>
+      <c r="L10" s="196"/>
+      <c r="M10" s="194"/>
+      <c r="N10" s="194"/>
+      <c r="O10" s="194"/>
+      <c r="P10" s="194"/>
+      <c r="Q10" s="194"/>
+      <c r="R10" s="194"/>
     </row>
     <row r="11" spans="1:18" ht="78" customHeight="1">
-      <c r="A11" s="192" t="s">
+      <c r="A11" s="240" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="193" t="s">
+      <c r="B11" s="241" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="194" t="s">
+      <c r="C11" s="242" t="s">
         <v>52</v>
       </c>
-      <c r="D11" s="182">
+      <c r="D11" s="243">
         <v>35200000</v>
       </c>
-      <c r="E11" s="172" t="s">
+      <c r="E11" s="194" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="172" t="s">
+      <c r="F11" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="G11" s="172" t="s">
+      <c r="G11" s="194" t="s">
         <v>54</v>
       </c>
-      <c r="H11" s="172">
+      <c r="H11" s="194">
         <v>1.1200000000000001</v>
       </c>
-      <c r="I11" s="71" t="s">
+      <c r="I11" s="194" t="s">
         <v>55</v>
       </c>
-      <c r="J11" s="71" t="s">
+      <c r="J11" s="194" t="s">
         <v>56</v>
       </c>
-      <c r="K11" s="71"/>
-      <c r="L11" s="71"/>
-      <c r="M11" s="71"/>
-      <c r="N11" s="71"/>
-      <c r="O11" s="71"/>
-      <c r="P11" s="71"/>
-      <c r="Q11" s="71"/>
-      <c r="R11" s="71"/>
-    </row>
-    <row r="12" spans="1:18" s="135" customFormat="1" ht="91.5">
-      <c r="A12" s="163"/>
-      <c r="B12" s="184"/>
-      <c r="C12" s="186"/>
-      <c r="D12" s="191">
+      <c r="K11" s="194"/>
+      <c r="L11" s="194"/>
+      <c r="M11" s="194"/>
+      <c r="N11" s="194"/>
+      <c r="O11" s="194"/>
+      <c r="P11" s="194"/>
+      <c r="Q11" s="194"/>
+      <c r="R11" s="194"/>
+    </row>
+    <row r="12" spans="1:18" s="131" customFormat="1" ht="91.5">
+      <c r="A12" s="218"/>
+      <c r="B12" s="231"/>
+      <c r="C12" s="233"/>
+      <c r="D12" s="244">
         <v>7000000</v>
       </c>
-      <c r="E12" s="99" t="s">
+      <c r="E12" s="194" t="s">
         <v>57</v>
       </c>
-      <c r="F12" s="99" t="s">
+      <c r="F12" s="194" t="s">
         <v>58</v>
       </c>
-      <c r="G12" s="99" t="s">
+      <c r="G12" s="194" t="s">
         <v>54</v>
       </c>
-      <c r="H12" s="99" t="s">
+      <c r="H12" s="194" t="s">
         <v>59</v>
       </c>
-      <c r="I12" s="99" t="s">
+      <c r="I12" s="194" t="s">
         <v>60</v>
       </c>
-      <c r="J12" s="210"/>
-      <c r="K12" s="99"/>
-      <c r="L12" s="99"/>
-      <c r="M12" s="71"/>
-      <c r="N12" s="71"/>
-      <c r="O12" s="71"/>
-      <c r="P12" s="71"/>
-      <c r="Q12" s="71"/>
-      <c r="R12" s="71"/>
-    </row>
-    <row r="13" spans="1:18" s="135" customFormat="1" ht="76.5">
-      <c r="A13" s="166"/>
-      <c r="B13" s="188"/>
-      <c r="C13" s="190"/>
-      <c r="D13" s="207">
+      <c r="J12" s="234"/>
+      <c r="K12" s="194"/>
+      <c r="L12" s="194"/>
+      <c r="M12" s="194"/>
+      <c r="N12" s="194"/>
+      <c r="O12" s="194"/>
+      <c r="P12" s="194"/>
+      <c r="Q12" s="194"/>
+      <c r="R12" s="194"/>
+    </row>
+    <row r="13" spans="1:18" s="131" customFormat="1" ht="76.5">
+      <c r="A13" s="222"/>
+      <c r="B13" s="236"/>
+      <c r="C13" s="238"/>
+      <c r="D13" s="244">
         <v>1300000</v>
       </c>
-      <c r="E13" s="172" t="s">
+      <c r="E13" s="194" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="172" t="s">
+      <c r="F13" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="G13" s="172" t="s">
+      <c r="G13" s="194" t="s">
         <v>54</v>
       </c>
-      <c r="H13" s="172">
+      <c r="H13" s="194">
         <v>0.35</v>
       </c>
-      <c r="I13" s="99" t="s">
+      <c r="I13" s="194" t="s">
         <v>61</v>
       </c>
-      <c r="J13" s="211"/>
-      <c r="K13" s="99"/>
-      <c r="L13" s="99"/>
-      <c r="M13" s="71"/>
-      <c r="N13" s="71"/>
-      <c r="O13" s="71"/>
-      <c r="P13" s="71"/>
-      <c r="Q13" s="71"/>
-      <c r="R13" s="71"/>
+      <c r="J13" s="239"/>
+      <c r="K13" s="194"/>
+      <c r="L13" s="194"/>
+      <c r="M13" s="194"/>
+      <c r="N13" s="194"/>
+      <c r="O13" s="194"/>
+      <c r="P13" s="194"/>
+      <c r="Q13" s="194"/>
+      <c r="R13" s="194"/>
     </row>
     <row r="14" spans="1:18" ht="106.5">
-      <c r="A14" s="195" t="s">
+      <c r="A14" s="215" t="s">
         <v>62</v>
       </c>
-      <c r="B14" s="161" t="s">
+      <c r="B14" s="212" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="196" t="s">
+      <c r="C14" s="133" t="s">
         <v>64</v>
       </c>
-      <c r="D14" s="206">
+      <c r="D14" s="245">
         <v>5356014</v>
       </c>
-      <c r="E14" s="172" t="s">
+      <c r="E14" s="194" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="172" t="s">
+      <c r="F14" s="194" t="s">
         <v>65</v>
       </c>
-      <c r="G14" s="206"/>
-      <c r="H14" s="206">
+      <c r="G14" s="245"/>
+      <c r="H14" s="245">
         <v>1730798</v>
       </c>
-      <c r="I14" s="71" t="s">
+      <c r="I14" s="194" t="s">
         <v>66</v>
       </c>
-      <c r="J14" s="213" t="s">
+      <c r="J14" s="229" t="s">
         <v>67</v>
       </c>
-      <c r="K14" s="71"/>
-      <c r="L14" s="71"/>
-      <c r="M14" s="71"/>
-      <c r="N14" s="71"/>
-      <c r="O14" s="71"/>
-      <c r="P14" s="71"/>
-      <c r="Q14" s="71"/>
-      <c r="R14" s="71"/>
+      <c r="K14" s="194"/>
+      <c r="L14" s="194"/>
+      <c r="M14" s="194"/>
+      <c r="N14" s="194"/>
+      <c r="O14" s="194"/>
+      <c r="P14" s="194"/>
+      <c r="Q14" s="194"/>
+      <c r="R14" s="194"/>
     </row>
     <row r="15" spans="1:18" ht="137.25">
-      <c r="A15" s="197"/>
-      <c r="B15" s="198"/>
-      <c r="C15" s="198"/>
-      <c r="D15" s="199"/>
-      <c r="E15" s="71" t="s">
+      <c r="A15" s="134"/>
+      <c r="B15" s="135"/>
+      <c r="C15" s="135"/>
+      <c r="D15" s="136"/>
+      <c r="E15" s="194" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="71" t="s">
+      <c r="F15" s="194" t="s">
         <v>69</v>
       </c>
-      <c r="G15" s="142">
+      <c r="G15" s="245">
         <v>30268</v>
       </c>
-      <c r="H15" s="142">
+      <c r="H15" s="245">
         <v>110000</v>
       </c>
-      <c r="I15" s="71" t="s">
+      <c r="I15" s="194" t="s">
         <v>70</v>
       </c>
-      <c r="J15" s="212"/>
-      <c r="K15" s="158">
+      <c r="J15" s="246"/>
+      <c r="K15" s="247">
         <v>0.4</v>
       </c>
-      <c r="L15" s="71"/>
-      <c r="M15" s="71"/>
-      <c r="N15" s="71"/>
-      <c r="O15" s="71"/>
-      <c r="P15" s="71"/>
-      <c r="Q15" s="71"/>
-      <c r="R15" s="71"/>
-    </row>
-    <row r="16" spans="1:18" s="135" customFormat="1" ht="106.5">
-      <c r="A16" s="200"/>
-      <c r="B16" s="201"/>
-      <c r="C16" s="201"/>
-      <c r="D16" s="202"/>
-      <c r="E16" s="99" t="s">
+      <c r="L15" s="194"/>
+      <c r="M15" s="194"/>
+      <c r="N15" s="194"/>
+      <c r="O15" s="194"/>
+      <c r="P15" s="194"/>
+      <c r="Q15" s="194"/>
+      <c r="R15" s="194"/>
+    </row>
+    <row r="16" spans="1:18" s="131" customFormat="1" ht="106.5">
+      <c r="A16" s="137"/>
+      <c r="B16" s="138"/>
+      <c r="C16" s="138"/>
+      <c r="D16" s="139"/>
+      <c r="E16" s="194" t="s">
         <v>71</v>
       </c>
-      <c r="F16" s="172" t="s">
+      <c r="F16" s="194" t="s">
         <v>72</v>
       </c>
-      <c r="G16" s="172"/>
-      <c r="H16" s="206">
+      <c r="G16" s="194"/>
+      <c r="H16" s="245">
         <v>6</v>
       </c>
-      <c r="I16" s="99" t="s">
+      <c r="I16" s="194" t="s">
         <v>73</v>
       </c>
-      <c r="J16" s="212"/>
-      <c r="K16" s="99"/>
-      <c r="L16" s="99"/>
-      <c r="M16" s="71"/>
-      <c r="N16" s="71"/>
-      <c r="O16" s="71"/>
-      <c r="P16" s="71"/>
-      <c r="Q16" s="71"/>
-      <c r="R16" s="71"/>
+      <c r="J16" s="246"/>
+      <c r="K16" s="194"/>
+      <c r="L16" s="194"/>
+      <c r="M16" s="194"/>
+      <c r="N16" s="194"/>
+      <c r="O16" s="194"/>
+      <c r="P16" s="194"/>
+      <c r="Q16" s="194"/>
+      <c r="R16" s="194"/>
     </row>
     <row r="17" spans="1:18" ht="60.75">
-      <c r="A17" s="203"/>
-      <c r="B17" s="204"/>
-      <c r="C17" s="204"/>
-      <c r="D17" s="205"/>
-      <c r="E17" s="71" t="s">
+      <c r="A17" s="140"/>
+      <c r="B17" s="141"/>
+      <c r="C17" s="141"/>
+      <c r="D17" s="142"/>
+      <c r="E17" s="194" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="71" t="s">
+      <c r="F17" s="194" t="s">
         <v>74</v>
       </c>
-      <c r="G17" s="71"/>
-      <c r="H17" s="71">
+      <c r="G17" s="194"/>
+      <c r="H17" s="194">
         <v>1220</v>
       </c>
-      <c r="I17" s="71" t="s">
+      <c r="I17" s="194" t="s">
         <v>75</v>
       </c>
-      <c r="J17" s="209"/>
-      <c r="K17" s="71"/>
-      <c r="L17" s="71"/>
-      <c r="M17" s="71"/>
-      <c r="N17" s="71"/>
-      <c r="O17" s="71"/>
-      <c r="P17" s="71"/>
-      <c r="Q17" s="71"/>
-      <c r="R17" s="71"/>
+      <c r="J17" s="239"/>
+      <c r="K17" s="194"/>
+      <c r="L17" s="194"/>
+      <c r="M17" s="194"/>
+      <c r="N17" s="194"/>
+      <c r="O17" s="194"/>
+      <c r="P17" s="194"/>
+      <c r="Q17" s="194"/>
+      <c r="R17" s="194"/>
     </row>
     <row r="18" spans="1:18" ht="106.5">
-      <c r="A18" s="159" t="s">
+      <c r="A18" s="248" t="s">
         <v>76</v>
       </c>
-      <c r="B18" s="143" t="s">
+      <c r="B18" s="188" t="s">
         <v>77</v>
       </c>
-      <c r="C18" s="71"/>
-      <c r="D18" s="142">
+      <c r="C18" s="194"/>
+      <c r="D18" s="245">
         <v>475000</v>
       </c>
-      <c r="E18" s="71" t="s">
+      <c r="E18" s="194" t="s">
         <v>29</v>
       </c>
-      <c r="F18" s="71" t="s">
+      <c r="F18" s="194" t="s">
         <v>78</v>
       </c>
-      <c r="G18" s="71"/>
-      <c r="H18" s="71" t="s">
+      <c r="G18" s="194"/>
+      <c r="H18" s="194" t="s">
         <v>79</v>
       </c>
-      <c r="I18" s="71" t="s">
+      <c r="I18" s="194" t="s">
         <v>80</v>
       </c>
-      <c r="J18" s="71" t="s">
+      <c r="J18" s="194" t="s">
         <v>81</v>
       </c>
-      <c r="K18" s="71"/>
-      <c r="L18" s="71"/>
-      <c r="M18" s="71"/>
-      <c r="N18" s="71"/>
-      <c r="O18" s="71"/>
-      <c r="P18" s="71"/>
-      <c r="Q18" s="71"/>
-      <c r="R18" s="71"/>
-    </row>
-    <row r="19" spans="1:18" s="135" customFormat="1" ht="106.5">
-      <c r="A19" s="99"/>
-      <c r="B19" s="144" t="s">
+      <c r="K18" s="194"/>
+      <c r="L18" s="194"/>
+      <c r="M18" s="194"/>
+      <c r="N18" s="194"/>
+      <c r="O18" s="194"/>
+      <c r="P18" s="194"/>
+      <c r="Q18" s="194"/>
+      <c r="R18" s="194"/>
+    </row>
+    <row r="19" spans="1:18" s="131" customFormat="1" ht="106.5">
+      <c r="A19" s="194"/>
+      <c r="B19" s="188" t="s">
         <v>82</v>
       </c>
-      <c r="C19" s="140"/>
-      <c r="D19" s="140">
+      <c r="C19" s="245"/>
+      <c r="D19" s="245">
         <v>150000</v>
       </c>
-      <c r="E19" s="99" t="s">
+      <c r="E19" s="194" t="s">
         <v>83</v>
       </c>
-      <c r="F19" s="172" t="s">
+      <c r="F19" s="194" t="s">
         <v>84</v>
       </c>
-      <c r="G19" s="172">
+      <c r="G19" s="194">
         <v>0</v>
       </c>
-      <c r="H19" s="172" t="s">
+      <c r="H19" s="194" t="s">
         <v>85</v>
       </c>
-      <c r="I19" s="99" t="s">
+      <c r="I19" s="194" t="s">
         <v>86</v>
       </c>
-      <c r="J19" s="130" t="s">
+      <c r="J19" s="225" t="s">
         <v>87</v>
       </c>
-      <c r="K19" s="99"/>
-      <c r="L19" s="99"/>
-      <c r="M19" s="71"/>
-      <c r="N19" s="71"/>
-      <c r="O19" s="71"/>
-      <c r="P19" s="71"/>
-      <c r="Q19" s="71"/>
-      <c r="R19" s="71"/>
-    </row>
-    <row r="20" spans="1:18" s="135" customFormat="1" ht="121.5">
-      <c r="A20" s="99"/>
-      <c r="B20" s="99" t="s">
+      <c r="K19" s="194"/>
+      <c r="L19" s="194"/>
+      <c r="M19" s="194"/>
+      <c r="N19" s="194"/>
+      <c r="O19" s="194"/>
+      <c r="P19" s="194"/>
+      <c r="Q19" s="194"/>
+      <c r="R19" s="194"/>
+    </row>
+    <row r="20" spans="1:18" s="131" customFormat="1" ht="121.5">
+      <c r="A20" s="194"/>
+      <c r="B20" s="194" t="s">
         <v>88</v>
       </c>
-      <c r="C20" s="140"/>
-      <c r="D20" s="140">
+      <c r="C20" s="245"/>
+      <c r="D20" s="245">
         <v>600000</v>
       </c>
-      <c r="E20" s="99" t="s">
+      <c r="E20" s="194" t="s">
         <v>57</v>
       </c>
-      <c r="F20" s="99" t="s">
+      <c r="F20" s="194" t="s">
         <v>89</v>
       </c>
-      <c r="G20" s="160">
+      <c r="G20" s="247">
         <v>0.7</v>
       </c>
-      <c r="H20" s="99">
+      <c r="H20" s="194">
         <v>5000</v>
       </c>
-      <c r="I20" s="99" t="s">
+      <c r="I20" s="194" t="s">
         <v>90</v>
       </c>
-      <c r="J20" s="130" t="s">
+      <c r="J20" s="225" t="s">
         <v>91</v>
       </c>
-      <c r="K20" s="99"/>
-      <c r="L20" s="99"/>
-      <c r="M20" s="71"/>
-      <c r="N20" s="71"/>
-      <c r="O20" s="71"/>
-      <c r="P20" s="71"/>
-      <c r="Q20" s="71"/>
-      <c r="R20" s="71"/>
-    </row>
-    <row r="21" spans="1:18" s="135" customFormat="1" ht="91.5">
-      <c r="A21" s="71"/>
-      <c r="B21" s="71" t="s">
+      <c r="K20" s="194"/>
+      <c r="L20" s="194"/>
+      <c r="M20" s="194"/>
+      <c r="N20" s="194"/>
+      <c r="O20" s="194"/>
+      <c r="P20" s="194"/>
+      <c r="Q20" s="194"/>
+      <c r="R20" s="194"/>
+    </row>
+    <row r="21" spans="1:18" s="131" customFormat="1" ht="91.5">
+      <c r="A21" s="194"/>
+      <c r="B21" s="194" t="s">
         <v>92</v>
       </c>
-      <c r="C21" s="71"/>
-      <c r="D21" s="142">
+      <c r="C21" s="194"/>
+      <c r="D21" s="245">
         <v>300000</v>
       </c>
-      <c r="E21" s="71" t="s">
+      <c r="E21" s="194" t="s">
         <v>29</v>
       </c>
-      <c r="F21" s="71" t="s">
+      <c r="F21" s="194" t="s">
         <v>93</v>
       </c>
-      <c r="G21" s="71">
+      <c r="G21" s="194">
         <v>0</v>
       </c>
-      <c r="H21" s="71">
+      <c r="H21" s="194">
         <v>1</v>
       </c>
-      <c r="I21" s="71" t="s">
+      <c r="I21" s="194" t="s">
         <v>94</v>
       </c>
-      <c r="J21" s="131" t="s">
+      <c r="J21" s="225" t="s">
         <v>91</v>
       </c>
-      <c r="K21" s="71"/>
-      <c r="L21" s="71"/>
-      <c r="M21" s="71"/>
-      <c r="N21" s="71"/>
-      <c r="O21" s="71"/>
-      <c r="P21" s="71"/>
-      <c r="Q21" s="71"/>
-      <c r="R21" s="71"/>
+      <c r="K21" s="194"/>
+      <c r="L21" s="194"/>
+      <c r="M21" s="194"/>
+      <c r="N21" s="194"/>
+      <c r="O21" s="194"/>
+      <c r="P21" s="194"/>
+      <c r="Q21" s="194"/>
+      <c r="R21" s="194"/>
     </row>
     <row r="22" spans="1:18" ht="91.5">
-      <c r="A22" s="71"/>
-      <c r="B22" s="71" t="s">
+      <c r="A22" s="194"/>
+      <c r="B22" s="194" t="s">
         <v>95</v>
       </c>
-      <c r="C22" s="142"/>
-      <c r="D22" s="145">
+      <c r="C22" s="245"/>
+      <c r="D22" s="132">
         <v>160000</v>
       </c>
-      <c r="E22" s="71" t="s">
+      <c r="E22" s="194" t="s">
         <v>29</v>
       </c>
-      <c r="F22" s="71" t="s">
+      <c r="F22" s="194" t="s">
         <v>96</v>
       </c>
-      <c r="G22" s="71">
+      <c r="G22" s="194">
         <v>1</v>
       </c>
-      <c r="H22" s="71">
+      <c r="H22" s="194">
         <v>3</v>
       </c>
-      <c r="I22" s="71" t="s">
+      <c r="I22" s="194" t="s">
         <v>97</v>
       </c>
-      <c r="J22" s="131" t="s">
+      <c r="J22" s="225" t="s">
         <v>91</v>
       </c>
-      <c r="K22" s="71"/>
-      <c r="L22" s="71"/>
-      <c r="M22" s="71"/>
-      <c r="N22" s="71"/>
-      <c r="O22" s="71"/>
-      <c r="P22" s="71"/>
-      <c r="Q22" s="71"/>
-      <c r="R22" s="71"/>
-    </row>
-    <row r="23" spans="1:18" s="135" customFormat="1" ht="121.5">
-      <c r="A23" s="99"/>
-      <c r="B23" s="99" t="s">
+      <c r="K22" s="194"/>
+      <c r="L22" s="194"/>
+      <c r="M22" s="194"/>
+      <c r="N22" s="194"/>
+      <c r="O22" s="194"/>
+      <c r="P22" s="194"/>
+      <c r="Q22" s="194"/>
+      <c r="R22" s="194"/>
+    </row>
+    <row r="23" spans="1:18" s="131" customFormat="1" ht="121.5">
+      <c r="A23" s="194"/>
+      <c r="B23" s="194" t="s">
         <v>98</v>
       </c>
-      <c r="C23" s="146"/>
-      <c r="D23" s="146">
+      <c r="C23" s="132"/>
+      <c r="D23" s="132">
         <v>1250000</v>
       </c>
-      <c r="E23" s="99" t="s">
+      <c r="E23" s="194" t="s">
         <v>99</v>
       </c>
-      <c r="F23" s="99" t="s">
+      <c r="F23" s="194" t="s">
         <v>100</v>
       </c>
-      <c r="G23" s="99">
+      <c r="G23" s="194">
         <v>326</v>
       </c>
-      <c r="H23" s="172">
+      <c r="H23" s="194">
         <v>2000</v>
       </c>
-      <c r="I23" s="99" t="s">
+      <c r="I23" s="194" t="s">
         <v>101</v>
       </c>
-      <c r="J23" s="130" t="s">
+      <c r="J23" s="225" t="s">
         <v>91</v>
       </c>
-      <c r="K23" s="99"/>
-      <c r="L23" s="99"/>
-      <c r="M23" s="71"/>
-      <c r="N23" s="71"/>
-      <c r="O23" s="71"/>
-      <c r="P23" s="71"/>
-      <c r="Q23" s="71"/>
-      <c r="R23" s="71"/>
+      <c r="K23" s="194"/>
+      <c r="L23" s="194"/>
+      <c r="M23" s="194"/>
+      <c r="N23" s="194"/>
+      <c r="O23" s="194"/>
+      <c r="P23" s="194"/>
+      <c r="Q23" s="194"/>
+      <c r="R23" s="194"/>
     </row>
     <row r="24" spans="1:18" ht="275.25">
-      <c r="A24" s="71">
+      <c r="A24" s="194">
         <v>106912</v>
       </c>
-      <c r="B24" s="71" t="s">
+      <c r="B24" s="194" t="s">
         <v>102</v>
       </c>
-      <c r="C24" s="71"/>
-      <c r="D24" s="142">
+      <c r="C24" s="194"/>
+      <c r="D24" s="245">
         <v>489000</v>
       </c>
-      <c r="E24" s="71" t="s">
+      <c r="E24" s="194" t="s">
         <v>29</v>
       </c>
-      <c r="F24" s="71" t="s">
+      <c r="F24" s="194" t="s">
         <v>103</v>
       </c>
-      <c r="G24" s="71" t="s">
+      <c r="G24" s="194" t="s">
         <v>104</v>
       </c>
-      <c r="H24" s="71"/>
-      <c r="I24" s="71" t="s">
+      <c r="H24" s="194"/>
+      <c r="I24" s="194" t="s">
         <v>105</v>
       </c>
-      <c r="J24" s="131" t="s">
+      <c r="J24" s="225" t="s">
         <v>24</v>
       </c>
-      <c r="K24" s="71"/>
-      <c r="L24" s="71" t="s">
+      <c r="K24" s="194"/>
+      <c r="L24" s="194" t="s">
         <v>25</v>
       </c>
-      <c r="M24" s="71"/>
-      <c r="N24" s="71"/>
-      <c r="O24" s="71"/>
-      <c r="P24" s="71"/>
-      <c r="Q24" s="71"/>
-      <c r="R24" s="71"/>
+      <c r="M24" s="194"/>
+      <c r="N24" s="194"/>
+      <c r="O24" s="194"/>
+      <c r="P24" s="194"/>
+      <c r="Q24" s="194"/>
+      <c r="R24" s="194"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3311,14 +3257,14 @@
       </c>
     </row>
     <row r="2" spans="1:13" s="94" customFormat="1" ht="91.5" customHeight="1">
-      <c r="A2" s="240" t="s">
+      <c r="A2" s="146" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="243" t="s">
+      <c r="B2" s="149" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="233"/>
-      <c r="D2" s="236" t="s">
+      <c r="C2" s="164"/>
+      <c r="D2" s="167" t="s">
         <v>107</v>
       </c>
       <c r="E2" s="90" t="s">
@@ -3331,14 +3277,14 @@
       <c r="H2" s="93" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="266" t="s">
+      <c r="I2" s="250" t="s">
         <v>109</v>
       </c>
-      <c r="J2" s="220" t="s">
+      <c r="J2" s="153" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="225"/>
-      <c r="L2" s="222" t="s">
+      <c r="K2" s="158"/>
+      <c r="L2" s="155" t="s">
         <v>25</v>
       </c>
       <c r="M2" s="120" t="s">
@@ -3346,10 +3292,10 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45.75">
-      <c r="A3" s="241"/>
-      <c r="B3" s="244"/>
-      <c r="C3" s="234"/>
-      <c r="D3" s="237"/>
+      <c r="A3" s="147"/>
+      <c r="B3" s="150"/>
+      <c r="C3" s="165"/>
+      <c r="D3" s="168"/>
       <c r="E3" s="67" t="s">
         <v>111</v>
       </c>
@@ -3358,17 +3304,17 @@
       <c r="H3" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="230"/>
-      <c r="J3" s="221"/>
-      <c r="K3" s="226"/>
-      <c r="L3" s="223"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="154"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="156"/>
       <c r="M3" s="121"/>
     </row>
     <row r="4" spans="1:13" ht="45.75">
-      <c r="A4" s="242"/>
-      <c r="B4" s="245"/>
-      <c r="C4" s="235"/>
-      <c r="D4" s="238"/>
+      <c r="A4" s="148"/>
+      <c r="B4" s="151"/>
+      <c r="C4" s="166"/>
+      <c r="D4" s="169"/>
       <c r="E4" s="69" t="s">
         <v>31</v>
       </c>
@@ -3379,17 +3325,17 @@
       <c r="H4" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="231"/>
-      <c r="J4" s="221"/>
-      <c r="K4" s="226"/>
-      <c r="L4" s="223"/>
+      <c r="I4" s="163"/>
+      <c r="J4" s="154"/>
+      <c r="K4" s="159"/>
+      <c r="L4" s="156"/>
       <c r="M4" s="121"/>
     </row>
     <row r="5" spans="1:13" s="94" customFormat="1" ht="76.5">
-      <c r="A5" s="246" t="s">
+      <c r="A5" s="152" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="229" t="s">
+      <c r="B5" s="144" t="s">
         <v>34</v>
       </c>
       <c r="C5" s="91"/>
@@ -3404,19 +3350,19 @@
         <v>113</v>
       </c>
       <c r="H5" s="91"/>
-      <c r="I5" s="232" t="s">
+      <c r="I5" s="145" t="s">
         <v>114</v>
       </c>
-      <c r="J5" s="221"/>
-      <c r="K5" s="226"/>
-      <c r="L5" s="223"/>
+      <c r="J5" s="154"/>
+      <c r="K5" s="159"/>
+      <c r="L5" s="156"/>
       <c r="M5" s="120" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="37.5" customHeight="1">
-      <c r="A6" s="246"/>
-      <c r="B6" s="229"/>
+      <c r="A6" s="152"/>
+      <c r="B6" s="144"/>
       <c r="C6" s="62"/>
       <c r="D6" s="68"/>
       <c r="E6" s="69" t="s">
@@ -3429,15 +3375,15 @@
       <c r="H6" s="96" t="s">
         <v>38</v>
       </c>
-      <c r="I6" s="232"/>
-      <c r="J6" s="221"/>
-      <c r="K6" s="226"/>
-      <c r="L6" s="223"/>
+      <c r="I6" s="145"/>
+      <c r="J6" s="154"/>
+      <c r="K6" s="159"/>
+      <c r="L6" s="156"/>
       <c r="M6" s="121"/>
     </row>
     <row r="7" spans="1:13" ht="45" customHeight="1">
-      <c r="A7" s="246"/>
-      <c r="B7" s="229"/>
+      <c r="A7" s="152"/>
+      <c r="B7" s="144"/>
       <c r="C7" s="62"/>
       <c r="D7" s="68"/>
       <c r="E7" s="67" t="s">
@@ -3450,15 +3396,15 @@
       <c r="H7" s="97" t="s">
         <v>116</v>
       </c>
-      <c r="I7" s="232"/>
-      <c r="J7" s="221"/>
-      <c r="K7" s="226"/>
-      <c r="L7" s="223"/>
+      <c r="I7" s="145"/>
+      <c r="J7" s="154"/>
+      <c r="K7" s="159"/>
+      <c r="L7" s="156"/>
       <c r="M7" s="121"/>
     </row>
     <row r="8" spans="1:13" s="101" customFormat="1" ht="45.75">
-      <c r="A8" s="228"/>
-      <c r="B8" s="229" t="s">
+      <c r="A8" s="161"/>
+      <c r="B8" s="144" t="s">
         <v>41</v>
       </c>
       <c r="C8" s="90"/>
@@ -3483,15 +3429,15 @@
       <c r="J8" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="K8" s="226"/>
-      <c r="L8" s="223"/>
+      <c r="K8" s="159"/>
+      <c r="L8" s="156"/>
       <c r="M8" s="122" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:13" s="15" customFormat="1" ht="60.75">
-      <c r="A9" s="228"/>
-      <c r="B9" s="229"/>
+      <c r="A9" s="161"/>
+      <c r="B9" s="144"/>
       <c r="C9" s="65"/>
       <c r="D9" s="66"/>
       <c r="E9" s="65" t="s">
@@ -3510,13 +3456,13 @@
         <v>47</v>
       </c>
       <c r="J9" s="65"/>
-      <c r="K9" s="226"/>
-      <c r="L9" s="223"/>
+      <c r="K9" s="159"/>
+      <c r="L9" s="156"/>
       <c r="M9" s="123"/>
     </row>
     <row r="10" spans="1:13" s="15" customFormat="1" ht="76.5">
-      <c r="A10" s="228"/>
-      <c r="B10" s="229"/>
+      <c r="A10" s="161"/>
+      <c r="B10" s="144"/>
       <c r="C10" s="65"/>
       <c r="D10" s="66"/>
       <c r="E10" s="65" t="s">
@@ -3535,15 +3481,15 @@
         <v>49</v>
       </c>
       <c r="J10" s="65"/>
-      <c r="K10" s="227"/>
-      <c r="L10" s="224"/>
+      <c r="K10" s="160"/>
+      <c r="L10" s="157"/>
       <c r="M10" s="123"/>
     </row>
     <row r="11" spans="1:13" ht="183">
-      <c r="A11" s="239" t="s">
+      <c r="A11" s="143" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="229" t="s">
+      <c r="B11" s="144" t="s">
         <v>51</v>
       </c>
       <c r="C11" s="73"/>
@@ -3573,8 +3519,8 @@
       <c r="M11" s="121"/>
     </row>
     <row r="12" spans="1:13" s="94" customFormat="1" ht="106.5">
-      <c r="A12" s="239"/>
-      <c r="B12" s="229"/>
+      <c r="A12" s="143"/>
+      <c r="B12" s="144"/>
       <c r="C12" s="102"/>
       <c r="D12" s="103" t="s">
         <v>124</v>
@@ -3604,8 +3550,8 @@
       </c>
     </row>
     <row r="13" spans="1:13" s="94" customFormat="1" ht="91.5">
-      <c r="A13" s="239"/>
-      <c r="B13" s="229"/>
+      <c r="A13" s="143"/>
+      <c r="B13" s="144"/>
       <c r="C13" s="102"/>
       <c r="D13" s="103" t="s">
         <v>127</v>
@@ -3638,7 +3584,7 @@
       <c r="A14" s="76" t="s">
         <v>62</v>
       </c>
-      <c r="B14" s="229" t="s">
+      <c r="B14" s="144" t="s">
         <v>63</v>
       </c>
       <c r="C14" s="77" t="s">
@@ -3670,8 +3616,8 @@
       <c r="M14" s="121"/>
     </row>
     <row r="15" spans="1:13" ht="305.25">
-      <c r="A15" s="232"/>
-      <c r="B15" s="229"/>
+      <c r="A15" s="145"/>
+      <c r="B15" s="144"/>
       <c r="C15" s="77" t="s">
         <v>64</v>
       </c>
@@ -3703,8 +3649,8 @@
       <c r="M15" s="121"/>
     </row>
     <row r="16" spans="1:13" s="94" customFormat="1" ht="167.25">
-      <c r="A16" s="232"/>
-      <c r="B16" s="229"/>
+      <c r="A16" s="145"/>
+      <c r="B16" s="144"/>
       <c r="C16" s="110" t="s">
         <v>64</v>
       </c>
@@ -3729,8 +3675,8 @@
       </c>
     </row>
     <row r="17" spans="1:13" ht="106.5">
-      <c r="A17" s="232"/>
-      <c r="B17" s="229"/>
+      <c r="A17" s="145"/>
+      <c r="B17" s="144"/>
       <c r="C17" s="77" t="s">
         <v>64</v>
       </c>
@@ -3980,14 +3926,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
     <mergeCell ref="J2:J7"/>
     <mergeCell ref="L2:L10"/>
     <mergeCell ref="K2:K10"/>
@@ -3997,6 +3935,14 @@
     <mergeCell ref="I5:I7"/>
     <mergeCell ref="C2:C4"/>
     <mergeCell ref="D2:D4"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <hyperlinks>
@@ -4075,10 +4021,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="91.5">
-      <c r="A2" s="255" t="s">
+      <c r="A2" s="178" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="250" t="s">
+      <c r="B2" s="173" t="s">
         <v>19</v>
       </c>
       <c r="C2" s="1"/>
@@ -4095,19 +4041,19 @@
       <c r="H2" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="247" t="s">
+      <c r="I2" s="170" t="s">
         <v>158</v>
       </c>
       <c r="J2" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="247" t="s">
+      <c r="K2" s="170" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="76.5">
-      <c r="A3" s="256"/>
-      <c r="B3" s="251"/>
+      <c r="A3" s="179"/>
+      <c r="B3" s="174"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="19" t="s">
@@ -4120,13 +4066,13 @@
       <c r="H3" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="I3" s="248"/>
+      <c r="I3" s="171"/>
       <c r="J3" s="43"/>
-      <c r="K3" s="248"/>
+      <c r="K3" s="171"/>
     </row>
     <row r="4" spans="1:11" ht="60.75">
-      <c r="A4" s="257"/>
-      <c r="B4" s="252"/>
+      <c r="A4" s="180"/>
+      <c r="B4" s="175"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="9" t="s">
@@ -4139,15 +4085,15 @@
       <c r="H4" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="I4" s="249"/>
+      <c r="I4" s="172"/>
       <c r="J4" s="44"/>
-      <c r="K4" s="249"/>
+      <c r="K4" s="172"/>
     </row>
     <row r="5" spans="1:11" ht="106.5">
-      <c r="A5" s="255" t="s">
+      <c r="A5" s="178" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="250" t="s">
+      <c r="B5" s="173" t="s">
         <v>34</v>
       </c>
       <c r="C5" s="1"/>
@@ -4162,19 +4108,19 @@
       <c r="H5" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="I5" s="247" t="s">
+      <c r="I5" s="170" t="s">
         <v>163</v>
       </c>
       <c r="J5" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="247" t="s">
+      <c r="K5" s="170" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="45.75">
-      <c r="A6" s="256"/>
-      <c r="B6" s="251"/>
+      <c r="A6" s="179"/>
+      <c r="B6" s="174"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="9" t="s">
@@ -4185,13 +4131,13 @@
       <c r="H6" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="I6" s="248"/>
+      <c r="I6" s="171"/>
       <c r="J6" s="43"/>
-      <c r="K6" s="248"/>
+      <c r="K6" s="171"/>
     </row>
     <row r="7" spans="1:11" ht="106.5">
-      <c r="A7" s="256"/>
-      <c r="B7" s="251"/>
+      <c r="A7" s="179"/>
+      <c r="B7" s="174"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="19" t="s">
@@ -4202,13 +4148,13 @@
       <c r="H7" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="I7" s="248"/>
+      <c r="I7" s="171"/>
       <c r="J7" s="44"/>
-      <c r="K7" s="249"/>
+      <c r="K7" s="172"/>
     </row>
     <row r="8" spans="1:11" ht="167.25">
-      <c r="A8" s="257"/>
-      <c r="B8" s="252"/>
+      <c r="A8" s="180"/>
+      <c r="B8" s="175"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="9" t="s">
@@ -4219,17 +4165,17 @@
       <c r="H8" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="I8" s="249"/>
+      <c r="I8" s="172"/>
       <c r="J8" s="57" t="s">
         <v>24</v>
       </c>
       <c r="K8" s="58"/>
     </row>
     <row r="9" spans="1:11" s="15" customFormat="1" ht="45.75">
-      <c r="A9" s="258" t="s">
+      <c r="A9" s="181" t="s">
         <v>169</v>
       </c>
-      <c r="B9" s="250" t="s">
+      <c r="B9" s="173" t="s">
         <v>41</v>
       </c>
       <c r="C9" s="7"/>
@@ -4257,8 +4203,8 @@
       </c>
     </row>
     <row r="10" spans="1:11" s="15" customFormat="1" ht="60.75">
-      <c r="A10" s="259"/>
-      <c r="B10" s="251"/>
+      <c r="A10" s="182"/>
+      <c r="B10" s="174"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
       <c r="E10" s="7" t="s">
@@ -4280,8 +4226,8 @@
       <c r="K10" s="50"/>
     </row>
     <row r="11" spans="1:11" s="15" customFormat="1" ht="45.75">
-      <c r="A11" s="260"/>
-      <c r="B11" s="252"/>
+      <c r="A11" s="183"/>
+      <c r="B11" s="175"/>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7" t="s">
@@ -4305,10 +4251,10 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="137.25">
-      <c r="A12" s="253" t="s">
+      <c r="A12" s="176" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="254" t="s">
+      <c r="B12" s="177" t="s">
         <v>51</v>
       </c>
       <c r="C12" s="16"/>
@@ -4338,8 +4284,8 @@
       </c>
     </row>
     <row r="13" spans="1:11" ht="76.5">
-      <c r="A13" s="253"/>
-      <c r="B13" s="254"/>
+      <c r="A13" s="176"/>
+      <c r="B13" s="177"/>
       <c r="C13" s="16"/>
       <c r="D13" s="4" t="s">
         <v>178</v>
@@ -4367,8 +4313,8 @@
       </c>
     </row>
     <row r="14" spans="1:11" ht="60.75">
-      <c r="A14" s="253"/>
-      <c r="B14" s="254"/>
+      <c r="A14" s="176"/>
+      <c r="B14" s="177"/>
       <c r="C14" s="16"/>
       <c r="D14" s="4" t="s">
         <v>181</v>
@@ -4410,7 +4356,7 @@
       <c r="A16" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="250" t="s">
+      <c r="B16" s="173" t="s">
         <v>63</v>
       </c>
       <c r="C16" s="24" t="s">
@@ -4440,8 +4386,8 @@
       <c r="K16" s="20"/>
     </row>
     <row r="17" spans="1:11" ht="183">
-      <c r="A17" s="247"/>
-      <c r="B17" s="251"/>
+      <c r="A17" s="170"/>
+      <c r="B17" s="174"/>
       <c r="C17" s="24" t="s">
         <v>64</v>
       </c>
@@ -4469,8 +4415,8 @@
       <c r="K17" s="20"/>
     </row>
     <row r="18" spans="1:11" ht="167.25">
-      <c r="A18" s="248"/>
-      <c r="B18" s="251"/>
+      <c r="A18" s="171"/>
+      <c r="B18" s="174"/>
       <c r="C18" s="24" t="s">
         <v>64</v>
       </c>
@@ -4496,8 +4442,8 @@
       <c r="K18" s="20"/>
     </row>
     <row r="19" spans="1:11" ht="106.5">
-      <c r="A19" s="249"/>
-      <c r="B19" s="252"/>
+      <c r="A19" s="172"/>
+      <c r="B19" s="175"/>
       <c r="C19" s="24" t="s">
         <v>64</v>
       </c>
@@ -4788,7 +4734,7 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="261" t="s">
+      <c r="A2" s="184" t="s">
         <v>197</v>
       </c>
       <c r="B2" t="s">
@@ -4799,7 +4745,7 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="261"/>
+      <c r="A3" s="184"/>
       <c r="B3" t="s">
         <v>21</v>
       </c>
@@ -4808,7 +4754,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="261"/>
+      <c r="A4" s="184"/>
       <c r="B4" t="s">
         <v>83</v>
       </c>
@@ -4817,7 +4763,7 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="262" t="s">
+      <c r="A5" s="185" t="s">
         <v>201</v>
       </c>
       <c r="B5" t="s">
@@ -4828,7 +4774,7 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="262"/>
+      <c r="A6" s="185"/>
       <c r="B6" t="s">
         <v>203</v>
       </c>
@@ -4837,7 +4783,7 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="262"/>
+      <c r="A7" s="185"/>
       <c r="B7" t="s">
         <v>57</v>
       </c>
@@ -4846,7 +4792,7 @@
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="262"/>
+      <c r="A8" s="185"/>
       <c r="B8" t="s">
         <v>99</v>
       </c>
@@ -4855,7 +4801,7 @@
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="262"/>
+      <c r="A9" s="185"/>
       <c r="B9" t="s">
         <v>68</v>
       </c>
@@ -4864,7 +4810,7 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="263" t="s">
+      <c r="A10" s="186" t="s">
         <v>167</v>
       </c>
       <c r="B10" t="s">
@@ -4875,7 +4821,7 @@
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="263"/>
+      <c r="A11" s="186"/>
       <c r="B11" t="s">
         <v>71</v>
       </c>
@@ -4884,7 +4830,7 @@
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="264" t="s">
+      <c r="A12" s="187" t="s">
         <v>211</v>
       </c>
       <c r="B12" t="s">
@@ -4895,7 +4841,7 @@
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="264"/>
+      <c r="A13" s="187"/>
       <c r="B13" t="s">
         <v>213</v>
       </c>
@@ -4904,7 +4850,7 @@
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="264"/>
+      <c r="A14" s="187"/>
       <c r="B14" t="s">
         <v>215</v>
       </c>
@@ -4946,6 +4892,68 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+    <SharedWithUsers xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59">
+      <UserInfo>
+        <DisplayName>Akiko Yamamoto</DisplayName>
+        <AccountId>84</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Arif Mohammad Faisal</DisplayName>
+        <AccountId>1690</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Maliha Muzammil</DisplayName>
+        <AccountId>1969</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Van Nguyen</DisplayName>
+        <AccountId>1970</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Riad Meddeb</DisplayName>
+        <AccountId>9</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Benjamin Keller</DisplayName>
+        <AccountId>1227</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Bahtiyar Kurt</DisplayName>
+        <AccountId>206</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Stefano Pistolese</DisplayName>
+        <AccountId>772</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -5194,70 +5202,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-    <SharedWithUsers xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59">
-      <UserInfo>
-        <DisplayName>Akiko Yamamoto</DisplayName>
-        <AccountId>84</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Arif Mohammad Faisal</DisplayName>
-        <AccountId>1690</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Maliha Muzammil</DisplayName>
-        <AccountId>1969</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Van Nguyen</DisplayName>
-        <AccountId>1970</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Riad Meddeb</DisplayName>
-        <AccountId>9</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Benjamin Keller</DisplayName>
-        <AccountId>1227</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Bahtiyar Kurt</DisplayName>
-        <AccountId>206</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Stefano Pistolese</DisplayName>
-        <AccountId>772</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3011BB0-07FE-4680-800E-7F4C36F905EE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D06A8A7-AAD0-46D5-9E3E-4D298B186157}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5265,5 +5211,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D06A8A7-AAD0-46D5-9E3E-4D298B186157}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3011BB0-07FE-4680-800E-7F4C36F905EE}"/>
 </file>
--- a/01_Input/00_CO Validation/Bangladesh - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Bangladesh - Energy Projects.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10114"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ben/Documents/UNDP/SEH/Energy-Moonshot-Tracker/01_Input/00_CO Validation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UNDP-BD\Energy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E19F15A-A975-5244-9AD7-74D7C53FF354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="653" documentId="13_ncr:1_{F9E229CD-093B-4957-8526-AA7B64B04BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6F11B5D-5BEE-4400-A444-2EA03BC518C6}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="740" windowWidth="19680" windowHeight="17080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects (3)" sheetId="4" r:id="rId1"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="251">
   <si>
     <t>Project ID</t>
   </si>
@@ -86,7 +86,7 @@
     <t>Link</t>
   </si>
   <si>
-    <t xml:space="preserve">Budget </t>
+    <t>Budget</t>
   </si>
   <si>
     <t>Beneficiary Category</t>
@@ -155,6 +155,17 @@
     <t>No. of waste to energy facilities, rooftop PV, energy efficiency in building, etc</t>
   </si>
   <si>
+    <t>The project addresses the development challenge of increased negative economic and environmental impacts from fossil use and other non-sustainable practices in urban areas by enabling low-carbon interventions and investments in energy-efficiency (EE) and renewable energy (RE) in buildings and built environment and to support urban development in Bangladesh. 
+GHG emission reduction of 1.573 million tons of tCO2 (lifetime) resulting from EE, RE and W2E interventions (Direct) and 4.718 million tons of CO2 as consequential (indirect) emission reduction after the project’s end. About 600 Kw of energy generation is expected.
+1 Bangladesh Low-Carbon Cities Network established ; Database on energy performance on commercial building established at SREDA;BNBC revised with EE adopted 
+2 waste to energy
+3 rooftop PV (public)
+10 rooftop PV (private)
+6 energy effociency in buildings(public)
+24 energy efficiency in buildings(private)
+On comment column: Expected to generate 1MW of energy</t>
+  </si>
+  <si>
     <t>GEF</t>
   </si>
   <si>
@@ -179,7 +190,7 @@
     <t>National</t>
   </si>
   <si>
-    <t>GHG Emission Reduction</t>
+    <t>GHG Emissions Reduction</t>
   </si>
   <si>
     <t>GHG Emission Reduction target in updated NDC</t>
@@ -195,6 +206,14 @@
   </si>
   <si>
     <t>Number of people benefiting from the development of EV ecosystem</t>
+  </si>
+  <si>
+    <t>This Project is to reduce GHG emissions with EV ecosystem development that promote environmentally friendly, energy-efficient, low-carbon transport and urban systems in Bangladesh with an enhanced policy-regulatory institutional framework with appropriate regulations for EVs and EV charging stations, accompanied by tailored capacity-building and awareness-raising efforts
+Total no. of project beneficiaries are 672,600 that includes passengers of e-bus, 2-3-4 wheelers, technicians, govt staffs, private sectors etc.
+Assessment of Regulatory Framework and Market development for EV and EVCS, Recycling and Disposal of Batteries with strategy for environmentally sound manufacturing of EV and EV Components;Preparation of PPP business models for local charging stations and installation of hybrid grid-solar charging stations as well as, Battery recycling and reuse in Bangladesh
+100 persons will be trained on operation and maintenance of charging infrastructure (e-Buses and 2-3-wheeler station; 100 persons will be trained on environmentally sound and safe handling and recycling of batteries and verification
+Installation of 4 Charging Station (EV Charger, 300-500 kW) for e-Buses; Installation of 3 Solar Hybrid (80 kW; 25 to 30 kW from Solar) for 2-3-4 Wheelers; 
+On comment column: It is expected that 100,000 people will be benefitted</t>
   </si>
   <si>
     <t xml:space="preserve">GHG Emission Reduction target </t>
@@ -217,6 +236,12 @@
     <t>Number of nano-grids installed and operational.</t>
   </si>
   <si>
+    <t>Nano-grid will cover 20-25 households
+30 nano-grids with covering
+300 to 450 households 
+On comment column: It is expected that about 1MW energy will be generated</t>
+  </si>
+  <si>
     <t>Adaptation Fund</t>
   </si>
   <si>
@@ -270,6 +295,16 @@
     <t>325 HH</t>
   </si>
   <si>
+    <t>54 community level drinking water supply with electric solar powered motors implemented by Union Parishads
+Budget is updated
+On comment column: About 325 household will be benefitted</t>
+  </si>
+  <si>
+    <t>7 community level rooftop solar home systems  implemented by Union Parishads
+Budget is updated
+On comment column: It is expected that about 350KW energy will be generated</t>
+  </si>
+  <si>
     <t>00110796(AC Unit) &amp; 00117012 (PMU)</t>
   </si>
   <si>
@@ -280,6 +315,10 @@
   </si>
   <si>
     <t>GHG emission reductions (ton CO2eq)</t>
+  </si>
+  <si>
+    <t>The project’s ultimate goal is to implement structural changes in RAC manufacturing and servicing sectors for cleaner production and contribute to the quality of people's lives, through the protection of the ozone layer and reduction in direct and indirect emissions. This project will phase-out 310.78 kg HCFC-22 equivalent to 17.09 ODP tons, which is 66% of Bangladesh´s consumption of HCFCs in RAC manufacturing sector, contributing to the reduction target for 2025.
+Baseline: Consumption of ODS 47.22 ODP ton</t>
   </si>
   <si>
     <t>MLF</t>
@@ -299,6 +338,10 @@
   </si>
   <si>
     <t>Number of small enterprises benefiting from the project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The HPMP Stage II project is supporting six private sector small enterprises namely Unitech Products (BD) Ltd., Elite Hi-Tech Industries Ltd., AC Bazar Industry, Supreme Air Conditioning, Cooling Point Engineering Services and Walton Hi-Tech Industries Ltd with a funding support of  5,356,014.
+On comment column: Six private companies are getting benefits from the project.The objective of this project is to phase out of 17.09 ODP tones (1,730,798 CO2-eq tons) from 5 air conditioning and 1 chiller manufacturing/assembler enterprises. </t>
   </si>
   <si>
     <t xml:space="preserve">Number of individuals who participate in trainings for energy activities. </t>
@@ -351,6 +394,11 @@
     <t>5000 HH</t>
   </si>
   <si>
+    <t>local Villages of the CHT area faces serious health related problems due to high GHG gas emitting cooking stoves that are also fuel inefficient. A2I has been working with local innovators to develop energy efficient fuel stoves that are also environmentally friendly for the residents of that area.
+15-25% of households using improved cooking stove
+On comment column: About 5,000 Household got the benefits</t>
+  </si>
+  <si>
     <t>Government of Bangladesh-50 million, Other donors (Gate Foundation, FB, Vital strategy, etc.): 9 million)</t>
   </si>
   <si>
@@ -360,6 +408,10 @@
     <t>% of people with restrictive access to household water in remote CHT areas</t>
   </si>
   <si>
+    <t>The southeastern part of Bangladesh is extensively hilly region and the people living here are not habituated to use modern water technologies. So, they have to collect water from natural sources particularly from the downhill springs for drinking, household chores and irrigation. To solve the water crisis of the communities at these regions, A2I has developed a water lifting system using Hydraulic Ram Pump to supply water from downhill source to uphill utilizing the water hammer effect for drinking and irrigation purposes at Bandarban, Bangladesh.
+On comment column: About 5000 farmers get benefits</t>
+  </si>
+  <si>
     <t>Govt of Bangladesh-50 million, Other donors (Gate Foundation, FB, Vital strategy, etc.): 9 million)</t>
   </si>
   <si>
@@ -397,6 +449,10 @@
   </si>
   <si>
     <t>No. of schools that are using the Multimedia Classroom</t>
+  </si>
+  <si>
+    <t>As we progress through the generations, Technological advancement is happening at an exponential rate. To fully support our youth, technological advancements are also essential in the education sector. On top of that the Bangladeshi Government has taken the initiative to engulf the education stream of Bangladesh under one digital format. To accomodate this initiative, we developed a highly efficient Multimedia Classroom system that is completely powered through solar energy. With this innovation, we can empower our local youth in rural areas to recieve the same education as urban areas.
+On comment column: About 2000 students get benefits</t>
   </si>
   <si>
     <t>Bangladesh: First Biennial Update Report to the UNFCCC</t>
@@ -429,6 +485,9 @@
 5. Gaps and constraints indentified</t>
   </si>
   <si>
+    <t xml:space="preserve">Budget </t>
+  </si>
+  <si>
     <t>Category</t>
   </si>
   <si>
@@ -462,6 +521,9 @@
     <t>Policy and Regulatory Frameworks</t>
   </si>
   <si>
+    <t>GHG Emission Reduction</t>
+  </si>
+  <si>
     <t>00116395</t>
   </si>
   <si>
@@ -835,9 +897,6 @@
   </si>
   <si>
     <t>Any other type of beneficiary (please specify justification in Notes)</t>
-  </si>
-  <si>
-    <t>Budget</t>
   </si>
 </sst>
 </file>
@@ -849,7 +908,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -861,7 +920,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -937,7 +995,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -955,7 +1013,6 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -963,7 +1020,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -987,7 +1043,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -1175,6 +1231,15 @@
     </border>
     <border>
       <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -1184,13 +1249,51 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="218">
+  <cellXfs count="257">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1533,13 +1636,73 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1548,33 +1711,117 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1583,6 +1830,12 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1609,6 +1862,150 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1617,183 +2014,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2121,334 +2341,348 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D47B4E4F-0AFC-46D6-97E6-4C30BF9BA353}">
-  <dimension ref="A1:T24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U24"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" style="35" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33" style="35" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="35" customWidth="1"/>
-    <col min="4" max="4" width="16.5" style="35" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.5" style="128" customWidth="1"/>
-    <col min="6" max="6" width="20.6640625" style="128" customWidth="1"/>
-    <col min="7" max="7" width="21.5" style="128" customWidth="1"/>
-    <col min="8" max="8" width="35.5" style="128" customWidth="1"/>
-    <col min="9" max="9" width="19.5" style="128" customWidth="1"/>
-    <col min="10" max="10" width="18" style="128" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" style="128" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.83203125" style="128"/>
-    <col min="13" max="13" width="31.6640625" style="128" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="23.6640625" style="128" customWidth="1"/>
-    <col min="15" max="15" width="8.5" style="128" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.5" style="128" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.1640625" style="128" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.33203125" style="128" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="30.33203125" style="128" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.6640625" style="128" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="8.83203125" style="128"/>
+    <col min="1" max="1" width="9.28515625" style="128" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33" style="128" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" style="128" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" style="128" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.42578125" style="128" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" style="128" customWidth="1"/>
+    <col min="7" max="7" width="21.42578125" style="128" customWidth="1"/>
+    <col min="8" max="8" width="35.42578125" style="128" customWidth="1"/>
+    <col min="9" max="9" width="93.140625" style="128" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" style="128" customWidth="1"/>
+    <col min="11" max="11" width="18" style="128" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.85546875" style="128" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.85546875" style="128"/>
+    <col min="14" max="14" width="31.7109375" style="128" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" style="128" customWidth="1"/>
+    <col min="16" max="16" width="8.42578125" style="128" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.5703125" style="128" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="23.140625" style="128" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.28515625" style="128" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="30.28515625" style="128" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.7109375" style="128" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="8.85546875" style="128"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="161" t="s">
+    <row r="1" spans="1:21" ht="30.75">
+      <c r="A1" s="141" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="162" t="s">
+      <c r="B1" s="142" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="162" t="s">
+      <c r="C1" s="142" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="162" t="s">
-        <v>239</v>
-      </c>
-      <c r="E1" s="159" t="s">
+      <c r="D1" s="142" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="141" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="130" t="s">
+      <c r="F1" s="141" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="130" t="s">
+      <c r="G1" s="141" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="130" t="s">
+      <c r="H1" s="141" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="130" t="s">
+      <c r="I1" s="141" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="141" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="130" t="s">
+      <c r="K1" s="141" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="151" t="s">
+      <c r="L1" s="201" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="152" t="s">
+      <c r="M1" s="202" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="151" t="s">
+      <c r="N1" s="201" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="151" t="s">
+      <c r="O1" s="201" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="152" t="s">
+      <c r="P1" s="202" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="152" t="s">
+      <c r="Q1" s="202" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" s="153" t="s">
+      <c r="R1" s="203" t="s">
         <v>17</v>
       </c>
-      <c r="R1" s="154" t="s">
+      <c r="S1" s="204" t="s">
         <v>18</v>
       </c>
-      <c r="S1" s="153" t="s">
+      <c r="T1" s="203" t="s">
         <v>19</v>
       </c>
-      <c r="T1" s="154" t="s">
+      <c r="U1" s="204" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="129" customFormat="1" ht="91.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="163" t="s">
+    <row r="2" spans="1:21" s="129" customFormat="1" ht="91.5" customHeight="1">
+      <c r="A2" s="143" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="161" t="s">
+      <c r="B2" s="144" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="164" t="s">
+      <c r="C2" s="145" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="146">
         <v>3767810</v>
       </c>
-      <c r="E2" s="134" t="s">
+      <c r="E2" s="69" t="s">
         <v>24</v>
       </c>
       <c r="F2" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="130"/>
+      <c r="G2" s="141"/>
       <c r="H2" s="69">
         <v>1</v>
       </c>
-      <c r="I2" s="131" t="s">
+      <c r="I2" s="252" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="63"/>
-      <c r="K2" s="155" t="s">
+      <c r="J2" s="147" t="s">
         <v>27</v>
       </c>
-      <c r="L2" s="72"/>
-      <c r="M2" s="134" t="s">
+      <c r="K2" s="63"/>
+      <c r="L2" s="205" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="72"/>
+      <c r="M2" s="72"/>
+      <c r="N2" s="154" t="s">
+        <v>29</v>
+      </c>
       <c r="O2" s="72"/>
       <c r="P2" s="72"/>
       <c r="Q2" s="72"/>
-      <c r="R2" s="68" t="s">
+      <c r="R2" s="72"/>
+      <c r="S2" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="T2" s="72"/>
+      <c r="U2" s="68"/>
+    </row>
+    <row r="3" spans="1:21" ht="45.75">
+      <c r="A3" s="148"/>
+      <c r="B3" s="149"/>
+      <c r="C3" s="150"/>
+      <c r="D3" s="151"/>
+      <c r="E3" s="152" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="69" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="141"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="210"/>
+      <c r="J3" s="153"/>
+      <c r="K3" s="199"/>
+      <c r="L3" s="205" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" s="72"/>
+      <c r="N3" s="154" t="s">
         <v>29</v>
       </c>
-      <c r="S2" s="72"/>
-      <c r="T2" s="68"/>
-    </row>
-    <row r="3" spans="1:20" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" s="163"/>
-      <c r="B3" s="161"/>
-      <c r="C3" s="164"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="132" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="69" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="130"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="133"/>
-      <c r="J3" s="149"/>
-      <c r="K3" s="155" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" s="72"/>
-      <c r="M3" s="134" t="s">
-        <v>28</v>
-      </c>
-      <c r="N3" s="72" t="s">
-        <v>31</v>
-      </c>
-      <c r="O3" s="72"/>
-      <c r="P3" s="72" t="s">
+      <c r="O3" s="72" t="s">
         <v>32</v>
       </c>
+      <c r="P3" s="72"/>
       <c r="Q3" s="72" t="s">
-        <v>31</v>
-      </c>
-      <c r="R3" s="68"/>
-      <c r="S3" s="72" t="s">
         <v>33</v>
       </c>
-      <c r="T3" s="68"/>
-    </row>
-    <row r="4" spans="1:20" ht="154.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="163"/>
-      <c r="B4" s="161"/>
-      <c r="C4" s="164"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="134" t="s">
+      <c r="R3" s="72" t="s">
+        <v>32</v>
+      </c>
+      <c r="S3" s="68"/>
+      <c r="T3" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="134" t="s">
+      <c r="U3" s="68"/>
+    </row>
+    <row r="4" spans="1:21" ht="154.5" customHeight="1">
+      <c r="A4" s="155"/>
+      <c r="B4" s="156"/>
+      <c r="C4" s="157"/>
+      <c r="D4" s="158"/>
+      <c r="E4" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="130"/>
+      <c r="F4" s="154" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="141"/>
       <c r="H4" s="69">
         <v>1573000</v>
       </c>
-      <c r="I4" s="135"/>
-      <c r="J4" s="149"/>
-      <c r="K4" s="155" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4" s="72"/>
-      <c r="M4" s="134" t="s">
+      <c r="I4" s="210"/>
+      <c r="J4" s="159"/>
+      <c r="K4" s="199"/>
+      <c r="L4" s="205" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="72"/>
+      <c r="M4" s="72"/>
+      <c r="N4" s="154" t="s">
+        <v>29</v>
+      </c>
       <c r="O4" s="72"/>
       <c r="P4" s="72"/>
       <c r="Q4" s="72"/>
-      <c r="R4" s="68"/>
-      <c r="S4" s="72"/>
-      <c r="T4" s="68"/>
-    </row>
-    <row r="5" spans="1:20" s="129" customFormat="1" ht="64" x14ac:dyDescent="0.2">
-      <c r="A5" s="166" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="167" t="s">
+      <c r="R4" s="72"/>
+      <c r="S4" s="68"/>
+      <c r="T4" s="72"/>
+      <c r="U4" s="68"/>
+    </row>
+    <row r="5" spans="1:21" s="129" customFormat="1" ht="60.75">
+      <c r="A5" s="160" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="161"/>
-      <c r="D5" s="11">
+      <c r="B5" s="161" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="162"/>
+      <c r="D5" s="163">
         <v>1788991</v>
       </c>
-      <c r="E5" s="142" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="137" t="s">
+      <c r="E5" s="164" t="s">
         <v>39</v>
       </c>
-      <c r="G5" s="130"/>
+      <c r="F5" s="165" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="141"/>
       <c r="H5" s="69">
         <v>100000</v>
       </c>
-      <c r="I5" s="150" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="63"/>
-      <c r="K5" s="155" t="s">
+      <c r="I5" s="209" t="s">
+        <v>41</v>
+      </c>
+      <c r="J5" s="200" t="s">
         <v>27</v>
       </c>
-      <c r="L5" s="72"/>
-      <c r="M5" s="134" t="s">
+      <c r="K5" s="63"/>
+      <c r="L5" s="205" t="s">
         <v>28</v>
       </c>
-      <c r="N5" s="72"/>
+      <c r="M5" s="72"/>
+      <c r="N5" s="154" t="s">
+        <v>29</v>
+      </c>
       <c r="O5" s="72"/>
       <c r="P5" s="72"/>
       <c r="Q5" s="72"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="72"/>
-      <c r="T5" s="68"/>
-    </row>
-    <row r="6" spans="1:20" ht="81" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R5" s="72"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="72"/>
+      <c r="U5" s="68"/>
+    </row>
+    <row r="6" spans="1:21" ht="81" customHeight="1">
       <c r="A6" s="166"/>
-      <c r="B6" s="166"/>
-      <c r="C6" s="166"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="134" t="s">
-        <v>34</v>
+      <c r="B6" s="167"/>
+      <c r="C6" s="167"/>
+      <c r="D6" s="168"/>
+      <c r="E6" t="s">
+        <v>35</v>
       </c>
       <c r="F6" s="69" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" s="130">
+        <v>42</v>
+      </c>
+      <c r="G6" s="141">
         <v>0</v>
       </c>
       <c r="H6" s="69">
         <v>15660</v>
       </c>
-      <c r="I6" s="133"/>
-      <c r="J6" s="149"/>
-      <c r="K6" s="155" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6" s="72"/>
-      <c r="M6" s="134" t="s">
+      <c r="I6" s="210"/>
+      <c r="J6" s="153"/>
+      <c r="K6" s="199"/>
+      <c r="L6" s="205" t="s">
         <v>28</v>
       </c>
-      <c r="N6" s="72"/>
+      <c r="M6" s="72"/>
+      <c r="N6" s="154" t="s">
+        <v>29</v>
+      </c>
       <c r="O6" s="72"/>
       <c r="P6" s="72"/>
       <c r="Q6" s="72"/>
-      <c r="R6" s="68"/>
-      <c r="S6" s="72"/>
-      <c r="T6" s="68"/>
-    </row>
-    <row r="7" spans="1:20" ht="200.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="166"/>
-      <c r="B7" s="166"/>
-      <c r="C7" s="166"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="160" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" s="139" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" s="130">
+      <c r="R6" s="72"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="68"/>
+    </row>
+    <row r="7" spans="1:21" ht="200.25" customHeight="1">
+      <c r="A7" s="169"/>
+      <c r="B7" s="170"/>
+      <c r="C7" s="170"/>
+      <c r="D7" s="171"/>
+      <c r="E7" s="172" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="173" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="141">
         <v>0</v>
       </c>
       <c r="H7" s="69">
         <v>200</v>
       </c>
-      <c r="I7" s="135"/>
-      <c r="J7" s="149"/>
-      <c r="K7" s="155" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" s="72"/>
-      <c r="M7" s="134" t="s">
+      <c r="I7" s="210"/>
+      <c r="J7" s="159"/>
+      <c r="K7" s="199"/>
+      <c r="L7" s="205" t="s">
         <v>28</v>
       </c>
-      <c r="N7" s="72"/>
+      <c r="M7" s="72"/>
+      <c r="N7" s="154" t="s">
+        <v>29</v>
+      </c>
       <c r="O7" s="72"/>
       <c r="P7" s="72"/>
       <c r="Q7" s="72"/>
-      <c r="R7" s="68"/>
-      <c r="S7" s="72"/>
-      <c r="T7" s="68"/>
-    </row>
-    <row r="8" spans="1:20" s="126" customFormat="1" ht="48" x14ac:dyDescent="0.2">
-      <c r="A8" s="168">
+      <c r="R7" s="72"/>
+      <c r="S7" s="68"/>
+      <c r="T7" s="72"/>
+      <c r="U7" s="68"/>
+    </row>
+    <row r="8" spans="1:21" s="126" customFormat="1" ht="91.5">
+      <c r="A8" s="174">
         <v>93848</v>
       </c>
-      <c r="B8" s="167" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="169" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="11">
+      <c r="B8" s="175" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="206" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="146">
         <v>9212322</v>
       </c>
-      <c r="E8" s="134" t="s">
+      <c r="E8" s="69" t="s">
         <v>24</v>
       </c>
       <c r="F8" s="69" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G8" s="69">
         <v>0</v>
@@ -2456,37 +2690,40 @@
       <c r="H8" s="69">
         <v>1</v>
       </c>
-      <c r="I8" s="136" t="s">
-        <v>46</v>
-      </c>
-      <c r="J8" s="63"/>
-      <c r="K8" s="155" t="s">
-        <v>27</v>
-      </c>
-      <c r="L8" s="72"/>
-      <c r="M8" s="134" t="s">
-        <v>47</v>
-      </c>
-      <c r="N8" s="72"/>
+      <c r="I8" s="173" t="s">
+        <v>48</v>
+      </c>
+      <c r="J8" s="164" t="s">
+        <v>49</v>
+      </c>
+      <c r="K8" s="63"/>
+      <c r="L8" s="205" t="s">
+        <v>28</v>
+      </c>
+      <c r="M8" s="72"/>
+      <c r="N8" s="154" t="s">
+        <v>50</v>
+      </c>
       <c r="O8" s="72"/>
       <c r="P8" s="72"/>
       <c r="Q8" s="72"/>
-      <c r="R8" s="68" t="s">
-        <v>29</v>
-      </c>
-      <c r="S8" s="72"/>
-      <c r="T8" s="68"/>
-    </row>
-    <row r="9" spans="1:20" s="127" customFormat="1" ht="48" x14ac:dyDescent="0.2">
-      <c r="A9" s="168"/>
-      <c r="B9" s="167"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="134" t="s">
-        <v>48</v>
+      <c r="R8" s="72"/>
+      <c r="S8" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="T8" s="72"/>
+      <c r="U8" s="68"/>
+    </row>
+    <row r="9" spans="1:21" s="127" customFormat="1" ht="60.75">
+      <c r="A9" s="177"/>
+      <c r="B9" s="178"/>
+      <c r="C9" s="179"/>
+      <c r="D9" s="180"/>
+      <c r="E9" s="154" t="s">
+        <v>51</v>
       </c>
       <c r="F9" s="69" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G9" s="69">
         <v>0</v>
@@ -2494,33 +2731,36 @@
       <c r="H9" s="69">
         <v>80</v>
       </c>
-      <c r="I9" s="141"/>
-      <c r="J9" s="63"/>
-      <c r="K9" s="155" t="s">
-        <v>27</v>
-      </c>
-      <c r="L9" s="72"/>
-      <c r="M9" s="134" t="s">
-        <v>47</v>
-      </c>
-      <c r="N9" s="72"/>
+      <c r="I9" s="69" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" s="181"/>
+      <c r="K9" s="63"/>
+      <c r="L9" s="205" t="s">
+        <v>28</v>
+      </c>
+      <c r="M9" s="72"/>
+      <c r="N9" s="154" t="s">
+        <v>50</v>
+      </c>
       <c r="O9" s="72"/>
       <c r="P9" s="72"/>
       <c r="Q9" s="72"/>
-      <c r="R9" s="68"/>
-      <c r="S9" s="72"/>
-      <c r="T9" s="68"/>
-    </row>
-    <row r="10" spans="1:20" s="127" customFormat="1" ht="48" x14ac:dyDescent="0.2">
-      <c r="A10" s="168"/>
-      <c r="B10" s="167"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="134" t="s">
-        <v>48</v>
+      <c r="R9" s="72"/>
+      <c r="S9" s="68"/>
+      <c r="T9" s="72"/>
+      <c r="U9" s="68"/>
+    </row>
+    <row r="10" spans="1:21" s="127" customFormat="1" ht="45.75">
+      <c r="A10" s="182"/>
+      <c r="B10" s="183"/>
+      <c r="C10" s="184"/>
+      <c r="D10" s="185"/>
+      <c r="E10" s="154" t="s">
+        <v>51</v>
       </c>
       <c r="F10" s="69" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G10" s="69">
         <v>0</v>
@@ -2528,431 +2768,464 @@
       <c r="H10" s="69">
         <v>2</v>
       </c>
-      <c r="I10" s="143"/>
-      <c r="J10" s="63"/>
-      <c r="K10" s="155" t="s">
-        <v>27</v>
-      </c>
-      <c r="L10" s="72"/>
-      <c r="M10" s="134" t="s">
-        <v>47</v>
-      </c>
-      <c r="N10" s="72"/>
+      <c r="I10" s="69" t="s">
+        <v>55</v>
+      </c>
+      <c r="J10" s="186"/>
+      <c r="K10" s="63"/>
+      <c r="L10" s="205" t="s">
+        <v>28</v>
+      </c>
+      <c r="M10" s="72"/>
+      <c r="N10" s="154" t="s">
+        <v>50</v>
+      </c>
       <c r="O10" s="72"/>
       <c r="P10" s="72"/>
       <c r="Q10" s="72"/>
-      <c r="R10" s="68"/>
-      <c r="S10" s="72"/>
-      <c r="T10" s="68"/>
-    </row>
-    <row r="11" spans="1:20" ht="78" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="166" t="s">
-        <v>53</v>
-      </c>
-      <c r="B11" s="167" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" s="164" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" s="173">
+      <c r="R10" s="72"/>
+      <c r="S10" s="68"/>
+      <c r="T10" s="72"/>
+      <c r="U10" s="68"/>
+    </row>
+    <row r="11" spans="1:21" ht="78" customHeight="1">
+      <c r="A11" s="187" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="188" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="189" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="190">
         <v>35200000</v>
       </c>
-      <c r="E11" s="134" t="s">
+      <c r="E11" s="69" t="s">
         <v>24</v>
       </c>
       <c r="F11" s="69" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G11" s="69" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H11" s="69">
         <v>1.1200000000000001</v>
       </c>
       <c r="I11" s="69" t="s">
-        <v>59</v>
-      </c>
-      <c r="J11" s="69"/>
-      <c r="K11" s="155" t="s">
-        <v>27</v>
-      </c>
-      <c r="L11" s="72"/>
-      <c r="M11" s="134" t="s">
+        <v>61</v>
+      </c>
+      <c r="J11" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="K11" s="69"/>
+      <c r="L11" s="205" t="s">
         <v>28</v>
       </c>
-      <c r="N11" s="72"/>
+      <c r="M11" s="72"/>
+      <c r="N11" s="154" t="s">
+        <v>29</v>
+      </c>
       <c r="O11" s="72"/>
       <c r="P11" s="72"/>
       <c r="Q11" s="72"/>
-      <c r="R11" s="68" t="s">
+      <c r="R11" s="72"/>
+      <c r="S11" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="T11" s="72"/>
+      <c r="U11" s="68"/>
+    </row>
+    <row r="12" spans="1:21" ht="91.5">
+      <c r="A12" s="166"/>
+      <c r="B12" s="178"/>
+      <c r="C12" s="180"/>
+      <c r="D12" s="191">
+        <v>7000000</v>
+      </c>
+      <c r="E12" s="69" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" s="69" t="s">
+        <v>64</v>
+      </c>
+      <c r="G12" s="69" t="s">
+        <v>60</v>
+      </c>
+      <c r="H12" s="69" t="s">
+        <v>65</v>
+      </c>
+      <c r="I12" s="69" t="s">
+        <v>66</v>
+      </c>
+      <c r="J12" s="181"/>
+      <c r="K12" s="69"/>
+      <c r="L12" s="205" t="s">
+        <v>28</v>
+      </c>
+      <c r="M12" s="72"/>
+      <c r="N12" s="154" t="s">
         <v>29</v>
       </c>
-      <c r="S11" s="72"/>
-      <c r="T11" s="68"/>
-    </row>
-    <row r="12" spans="1:20" ht="80" x14ac:dyDescent="0.2">
-      <c r="A12" s="166"/>
-      <c r="B12" s="167"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="173">
-        <v>7000000</v>
-      </c>
-      <c r="E12" s="134" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" s="69" t="s">
-        <v>61</v>
-      </c>
-      <c r="G12" s="69" t="s">
-        <v>57</v>
-      </c>
-      <c r="H12" s="69" t="s">
-        <v>62</v>
-      </c>
-      <c r="I12" s="141"/>
-      <c r="J12" s="69"/>
-      <c r="K12" s="155" t="s">
-        <v>27</v>
-      </c>
-      <c r="L12" s="72"/>
-      <c r="M12" s="134" t="s">
-        <v>28</v>
-      </c>
-      <c r="N12" s="72"/>
       <c r="O12" s="72"/>
       <c r="P12" s="72"/>
       <c r="Q12" s="72"/>
-      <c r="R12" s="68"/>
-      <c r="S12" s="72"/>
-      <c r="T12" s="68"/>
-    </row>
-    <row r="13" spans="1:20" ht="32" x14ac:dyDescent="0.2">
-      <c r="A13" s="166"/>
-      <c r="B13" s="167"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="173">
+      <c r="R12" s="72"/>
+      <c r="S12" s="68"/>
+      <c r="T12" s="72"/>
+      <c r="U12" s="68"/>
+    </row>
+    <row r="13" spans="1:21" ht="76.5">
+      <c r="A13" s="169"/>
+      <c r="B13" s="183"/>
+      <c r="C13" s="185"/>
+      <c r="D13" s="191">
         <v>1300000</v>
       </c>
-      <c r="E13" s="134" t="s">
+      <c r="E13" s="69" t="s">
         <v>24</v>
       </c>
       <c r="F13" s="69" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G13" s="69" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H13" s="69">
         <v>0.35</v>
       </c>
-      <c r="I13" s="143"/>
-      <c r="J13" s="69"/>
-      <c r="K13" s="155" t="s">
-        <v>27</v>
-      </c>
-      <c r="L13" s="72"/>
-      <c r="M13" s="134" t="s">
+      <c r="I13" s="69" t="s">
+        <v>67</v>
+      </c>
+      <c r="J13" s="186"/>
+      <c r="K13" s="69"/>
+      <c r="L13" s="205" t="s">
         <v>28</v>
       </c>
-      <c r="N13" s="72"/>
+      <c r="M13" s="72"/>
+      <c r="N13" s="154" t="s">
+        <v>29</v>
+      </c>
       <c r="O13" s="72"/>
       <c r="P13" s="72"/>
       <c r="Q13" s="72"/>
-      <c r="R13" s="68" t="s">
+      <c r="R13" s="72"/>
+      <c r="S13" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="T13" s="72"/>
+      <c r="U13" s="68"/>
+    </row>
+    <row r="14" spans="1:21" ht="106.5">
+      <c r="A14" s="164" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="161" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="131" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" s="192">
+        <v>5356014</v>
+      </c>
+      <c r="E14" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" s="69" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14" s="192"/>
+      <c r="H14" s="192">
+        <v>1730798</v>
+      </c>
+      <c r="I14" s="69" t="s">
+        <v>72</v>
+      </c>
+      <c r="J14" s="176" t="s">
+        <v>73</v>
+      </c>
+      <c r="K14" s="69"/>
+      <c r="L14" s="205" t="s">
+        <v>28</v>
+      </c>
+      <c r="M14" s="72"/>
+      <c r="N14" s="154" t="s">
         <v>29</v>
       </c>
-      <c r="S13" s="72"/>
-      <c r="T13" s="68"/>
-    </row>
-    <row r="14" spans="1:20" ht="80" x14ac:dyDescent="0.2">
-      <c r="A14" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="B14" s="167" t="s">
-        <v>64</v>
-      </c>
-      <c r="C14" s="164" t="s">
-        <v>65</v>
-      </c>
-      <c r="D14" s="11">
-        <v>5356014</v>
-      </c>
-      <c r="E14" s="134" t="s">
-        <v>34</v>
-      </c>
-      <c r="F14" s="69" t="s">
-        <v>66</v>
-      </c>
-      <c r="G14" s="144"/>
-      <c r="H14" s="144">
-        <v>1730798</v>
-      </c>
-      <c r="I14" s="140" t="s">
-        <v>67</v>
-      </c>
-      <c r="J14" s="69"/>
-      <c r="K14" s="155" t="s">
-        <v>27</v>
-      </c>
-      <c r="L14" s="72"/>
-      <c r="M14" s="134" t="s">
-        <v>28</v>
-      </c>
-      <c r="N14" s="72"/>
       <c r="O14" s="72"/>
       <c r="P14" s="72"/>
       <c r="Q14" s="72"/>
-      <c r="R14" s="68"/>
-      <c r="S14" s="72"/>
-      <c r="T14" s="68"/>
-    </row>
-    <row r="15" spans="1:20" ht="128" x14ac:dyDescent="0.2">
-      <c r="A15" s="170"/>
-      <c r="B15" s="170"/>
-      <c r="C15" s="170"/>
-      <c r="D15" s="174"/>
-      <c r="E15" s="134" t="s">
-        <v>68</v>
+      <c r="R14" s="72"/>
+      <c r="S14" s="68"/>
+      <c r="T14" s="72"/>
+      <c r="U14" s="68"/>
+    </row>
+    <row r="15" spans="1:21" ht="137.25">
+      <c r="A15" s="132"/>
+      <c r="B15" s="133"/>
+      <c r="C15" s="133"/>
+      <c r="D15" s="134"/>
+      <c r="E15" s="69" t="s">
+        <v>74</v>
       </c>
       <c r="F15" s="69" t="s">
-        <v>69</v>
-      </c>
-      <c r="G15" s="144">
+        <v>75</v>
+      </c>
+      <c r="G15" s="192">
         <v>30268</v>
       </c>
-      <c r="H15" s="144">
+      <c r="H15" s="192">
         <v>110000</v>
       </c>
-      <c r="I15" s="145"/>
-      <c r="J15" s="146">
+      <c r="I15" s="69" t="s">
+        <v>76</v>
+      </c>
+      <c r="J15" s="193"/>
+      <c r="K15" s="194">
         <v>0.4</v>
       </c>
-      <c r="K15" s="155" t="s">
-        <v>27</v>
-      </c>
-      <c r="L15" s="72"/>
-      <c r="M15" s="134" t="s">
+      <c r="L15" s="205" t="s">
         <v>28</v>
       </c>
-      <c r="N15" s="72"/>
+      <c r="M15" s="72"/>
+      <c r="N15" s="154" t="s">
+        <v>29</v>
+      </c>
       <c r="O15" s="72"/>
       <c r="P15" s="72"/>
       <c r="Q15" s="72"/>
-      <c r="R15" s="68"/>
-      <c r="S15" s="72"/>
-      <c r="T15" s="68"/>
-    </row>
-    <row r="16" spans="1:20" s="129" customFormat="1" ht="48" x14ac:dyDescent="0.2">
-      <c r="A16" s="170"/>
-      <c r="B16" s="170"/>
-      <c r="C16" s="170"/>
-      <c r="D16" s="174"/>
-      <c r="E16" s="134" t="s">
-        <v>71</v>
+      <c r="R15" s="72"/>
+      <c r="S15" s="68"/>
+      <c r="T15" s="72"/>
+      <c r="U15" s="68"/>
+    </row>
+    <row r="16" spans="1:21" s="129" customFormat="1" ht="106.5">
+      <c r="A16" s="135"/>
+      <c r="B16" s="136"/>
+      <c r="C16" s="136"/>
+      <c r="D16" s="137"/>
+      <c r="E16" s="69" t="s">
+        <v>77</v>
       </c>
       <c r="F16" s="69" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G16" s="69"/>
-      <c r="H16" s="144">
+      <c r="H16" s="192">
         <v>6</v>
       </c>
-      <c r="I16" s="145"/>
-      <c r="J16" s="69"/>
-      <c r="K16" s="155" t="s">
-        <v>27</v>
-      </c>
-      <c r="L16" s="72"/>
-      <c r="M16" s="134" t="s">
+      <c r="I16" s="69" t="s">
+        <v>79</v>
+      </c>
+      <c r="J16" s="193"/>
+      <c r="K16" s="69"/>
+      <c r="L16" s="205" t="s">
         <v>28</v>
       </c>
-      <c r="N16" s="72"/>
+      <c r="M16" s="72"/>
+      <c r="N16" s="154" t="s">
+        <v>29</v>
+      </c>
       <c r="O16" s="72"/>
       <c r="P16" s="72"/>
       <c r="Q16" s="72"/>
-      <c r="R16" s="68"/>
-      <c r="S16" s="72"/>
-      <c r="T16" s="68"/>
-    </row>
-    <row r="17" spans="1:20" ht="64" x14ac:dyDescent="0.2">
-      <c r="A17" s="170"/>
-      <c r="B17" s="170"/>
-      <c r="C17" s="170"/>
-      <c r="D17" s="174"/>
-      <c r="E17" s="134" t="s">
-        <v>41</v>
+      <c r="R16" s="72"/>
+      <c r="S16" s="68"/>
+      <c r="T16" s="72"/>
+      <c r="U16" s="68"/>
+    </row>
+    <row r="17" spans="1:21" ht="60.75">
+      <c r="A17" s="138"/>
+      <c r="B17" s="139"/>
+      <c r="C17" s="139"/>
+      <c r="D17" s="140"/>
+      <c r="E17" s="69" t="s">
+        <v>43</v>
       </c>
       <c r="F17" s="69" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G17" s="69"/>
       <c r="H17" s="69">
         <v>1220</v>
       </c>
-      <c r="I17" s="143"/>
-      <c r="J17" s="69"/>
-      <c r="K17" s="155" t="s">
-        <v>27</v>
-      </c>
-      <c r="L17" s="72"/>
-      <c r="M17" s="134" t="s">
+      <c r="I17" s="69" t="s">
+        <v>81</v>
+      </c>
+      <c r="J17" s="186"/>
+      <c r="K17" s="69"/>
+      <c r="L17" s="205" t="s">
         <v>28</v>
       </c>
-      <c r="N17" s="72"/>
+      <c r="M17" s="72"/>
+      <c r="N17" s="154" t="s">
+        <v>29</v>
+      </c>
       <c r="O17" s="72"/>
       <c r="P17" s="72"/>
       <c r="Q17" s="72"/>
-      <c r="R17" s="68"/>
-      <c r="S17" s="72"/>
-      <c r="T17" s="68"/>
-    </row>
-    <row r="18" spans="1:20" ht="96" x14ac:dyDescent="0.2">
-      <c r="A18" s="163" t="s">
-        <v>75</v>
-      </c>
-      <c r="B18" s="161" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11">
+      <c r="R17" s="72"/>
+      <c r="S17" s="68"/>
+      <c r="T17" s="72"/>
+      <c r="U17" s="68"/>
+    </row>
+    <row r="18" spans="1:21" ht="106.5">
+      <c r="A18" s="195" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" s="141" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="69"/>
+      <c r="D18" s="192">
         <v>475000</v>
       </c>
-      <c r="E18" s="134" t="s">
+      <c r="E18" s="69" t="s">
         <v>19</v>
       </c>
       <c r="F18" s="69" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G18" s="69"/>
       <c r="H18" s="69" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I18" s="69" t="s">
-        <v>80</v>
-      </c>
-      <c r="J18" s="69"/>
-      <c r="K18" s="155" t="s">
-        <v>27</v>
-      </c>
-      <c r="L18" s="72"/>
-      <c r="M18" s="134" t="s">
+        <v>86</v>
+      </c>
+      <c r="J18" s="69" t="s">
+        <v>87</v>
+      </c>
+      <c r="K18" s="69"/>
+      <c r="L18" s="205" t="s">
         <v>28</v>
       </c>
-      <c r="N18" s="72" t="s">
-        <v>31</v>
-      </c>
-      <c r="O18" s="72"/>
-      <c r="P18" s="72" t="s">
-        <v>81</v>
-      </c>
+      <c r="M18" s="72"/>
+      <c r="N18" s="154" t="s">
+        <v>29</v>
+      </c>
+      <c r="O18" s="72" t="s">
+        <v>32</v>
+      </c>
+      <c r="P18" s="72"/>
       <c r="Q18" s="72" t="s">
-        <v>82</v>
-      </c>
-      <c r="R18" s="68"/>
-      <c r="S18" s="72" t="s">
-        <v>33</v>
-      </c>
-      <c r="T18" s="68"/>
-    </row>
-    <row r="19" spans="1:20" s="129" customFormat="1" ht="96" x14ac:dyDescent="0.2">
-      <c r="A19" s="11">
+        <v>88</v>
+      </c>
+      <c r="R18" s="72" t="s">
+        <v>89</v>
+      </c>
+      <c r="S18" s="68"/>
+      <c r="T18" s="72" t="s">
+        <v>34</v>
+      </c>
+      <c r="U18" s="68"/>
+    </row>
+    <row r="19" spans="1:21" s="129" customFormat="1" ht="106.5">
+      <c r="A19" s="69">
         <v>93849</v>
       </c>
-      <c r="B19" s="161" t="s">
-        <v>83</v>
-      </c>
-      <c r="C19" s="171" t="s">
-        <v>84</v>
-      </c>
-      <c r="D19" s="11">
+      <c r="B19" s="141" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="207" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" s="192">
         <v>150000</v>
       </c>
-      <c r="E19" s="134" t="s">
-        <v>85</v>
+      <c r="E19" s="69" t="s">
+        <v>92</v>
       </c>
       <c r="F19" s="69" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G19" s="69">
         <v>0</v>
       </c>
       <c r="H19" s="69" t="s">
-        <v>87</v>
-      </c>
-      <c r="I19" s="138" t="s">
-        <v>88</v>
-      </c>
-      <c r="J19" s="69"/>
-      <c r="K19" s="155" t="s">
-        <v>27</v>
-      </c>
-      <c r="L19" s="72"/>
-      <c r="M19" s="134" t="s">
+        <v>94</v>
+      </c>
+      <c r="I19" s="69" t="s">
+        <v>95</v>
+      </c>
+      <c r="J19" s="172" t="s">
+        <v>96</v>
+      </c>
+      <c r="K19" s="69"/>
+      <c r="L19" s="205" t="s">
         <v>28</v>
       </c>
-      <c r="N19" s="72"/>
+      <c r="M19" s="72"/>
+      <c r="N19" s="154" t="s">
+        <v>29</v>
+      </c>
       <c r="O19" s="72"/>
       <c r="P19" s="72"/>
       <c r="Q19" s="72"/>
-      <c r="R19" s="68"/>
-      <c r="S19" s="72"/>
-      <c r="T19" s="68"/>
-    </row>
-    <row r="20" spans="1:20" s="129" customFormat="1" ht="80" x14ac:dyDescent="0.2">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C20" s="165"/>
-      <c r="D20" s="11">
+      <c r="R19" s="72"/>
+      <c r="S19" s="68"/>
+      <c r="T19" s="72"/>
+      <c r="U19" s="68"/>
+    </row>
+    <row r="20" spans="1:21" s="129" customFormat="1" ht="121.5">
+      <c r="A20" s="69"/>
+      <c r="B20" s="69" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" s="192"/>
+      <c r="D20" s="192">
         <v>600000</v>
       </c>
-      <c r="E20" s="134" t="s">
-        <v>60</v>
+      <c r="E20" s="69" t="s">
+        <v>63</v>
       </c>
       <c r="F20" s="69" t="s">
-        <v>90</v>
-      </c>
-      <c r="G20" s="146">
+        <v>98</v>
+      </c>
+      <c r="G20" s="194">
         <v>0.7</v>
       </c>
       <c r="H20" s="69">
         <v>5000</v>
       </c>
-      <c r="I20" s="138" t="s">
-        <v>91</v>
-      </c>
-      <c r="J20" s="69"/>
-      <c r="K20" s="155" t="s">
-        <v>27</v>
-      </c>
-      <c r="L20" s="72"/>
-      <c r="M20" s="134" t="s">
+      <c r="I20" s="69" t="s">
+        <v>99</v>
+      </c>
+      <c r="J20" s="172" t="s">
+        <v>100</v>
+      </c>
+      <c r="K20" s="69"/>
+      <c r="L20" s="205" t="s">
         <v>28</v>
       </c>
-      <c r="N20" s="72"/>
+      <c r="M20" s="72"/>
+      <c r="N20" s="154" t="s">
+        <v>29</v>
+      </c>
       <c r="O20" s="72"/>
       <c r="P20" s="72"/>
       <c r="Q20" s="72"/>
-      <c r="R20" s="68"/>
-      <c r="S20" s="72"/>
-      <c r="T20" s="68"/>
-    </row>
-    <row r="21" spans="1:20" s="129" customFormat="1" ht="80" x14ac:dyDescent="0.2">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11">
+      <c r="R20" s="72"/>
+      <c r="S20" s="68"/>
+      <c r="T20" s="72"/>
+      <c r="U20" s="68"/>
+    </row>
+    <row r="21" spans="1:21" s="129" customFormat="1" ht="91.5">
+      <c r="A21" s="69"/>
+      <c r="B21" s="69" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" s="69"/>
+      <c r="D21" s="192">
         <v>300000</v>
       </c>
-      <c r="E21" s="134" t="s">
+      <c r="E21" s="69" t="s">
         <v>19</v>
       </c>
       <c r="F21" s="69" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="G21" s="69">
         <v>0</v>
@@ -2960,47 +3233,50 @@
       <c r="H21" s="69">
         <v>1</v>
       </c>
-      <c r="I21" s="138" t="s">
-        <v>91</v>
-      </c>
-      <c r="J21" s="69"/>
-      <c r="K21" s="155" t="s">
-        <v>27</v>
-      </c>
-      <c r="L21" s="72"/>
-      <c r="M21" s="134" t="s">
+      <c r="I21" s="69" t="s">
+        <v>103</v>
+      </c>
+      <c r="J21" s="172" t="s">
+        <v>100</v>
+      </c>
+      <c r="K21" s="69"/>
+      <c r="L21" s="205" t="s">
         <v>28</v>
       </c>
-      <c r="N21" s="72" t="s">
-        <v>31</v>
-      </c>
-      <c r="O21" s="72"/>
-      <c r="P21" s="72" t="s">
-        <v>95</v>
-      </c>
+      <c r="M21" s="72"/>
+      <c r="N21" s="154" t="s">
+        <v>29</v>
+      </c>
+      <c r="O21" s="72" t="s">
+        <v>32</v>
+      </c>
+      <c r="P21" s="72"/>
       <c r="Q21" s="72" t="s">
-        <v>96</v>
-      </c>
-      <c r="R21" s="68"/>
-      <c r="S21" s="72" t="s">
-        <v>33</v>
-      </c>
-      <c r="T21" s="68"/>
-    </row>
-    <row r="22" spans="1:20" ht="80" x14ac:dyDescent="0.2">
-      <c r="A22" s="11"/>
-      <c r="B22" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="C22" s="165"/>
-      <c r="D22" s="175">
+        <v>104</v>
+      </c>
+      <c r="R21" s="72" t="s">
+        <v>105</v>
+      </c>
+      <c r="S21" s="68"/>
+      <c r="T21" s="72" t="s">
+        <v>34</v>
+      </c>
+      <c r="U21" s="68"/>
+    </row>
+    <row r="22" spans="1:21" ht="144" customHeight="1">
+      <c r="A22" s="69"/>
+      <c r="B22" s="69" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" s="192"/>
+      <c r="D22" s="196">
         <v>160000</v>
       </c>
-      <c r="E22" s="134" t="s">
+      <c r="E22" s="69" t="s">
         <v>19</v>
       </c>
       <c r="F22" s="69" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="G22" s="69">
         <v>1</v>
@@ -3008,47 +3284,50 @@
       <c r="H22" s="69">
         <v>3</v>
       </c>
-      <c r="I22" s="138" t="s">
-        <v>91</v>
-      </c>
-      <c r="J22" s="69"/>
-      <c r="K22" s="155" t="s">
-        <v>27</v>
-      </c>
-      <c r="L22" s="72"/>
-      <c r="M22" s="134" t="s">
+      <c r="I22" s="69" t="s">
+        <v>108</v>
+      </c>
+      <c r="J22" s="172" t="s">
+        <v>100</v>
+      </c>
+      <c r="K22" s="69"/>
+      <c r="L22" s="205" t="s">
         <v>28</v>
       </c>
-      <c r="N22" s="72" t="s">
-        <v>100</v>
-      </c>
-      <c r="O22" s="72"/>
-      <c r="P22" s="72" t="s">
-        <v>32</v>
-      </c>
+      <c r="M22" s="72"/>
+      <c r="N22" s="154" t="s">
+        <v>29</v>
+      </c>
+      <c r="O22" s="72" t="s">
+        <v>109</v>
+      </c>
+      <c r="P22" s="72"/>
       <c r="Q22" s="72" t="s">
-        <v>82</v>
-      </c>
-      <c r="R22" s="68"/>
-      <c r="S22" s="72" t="s">
         <v>33</v>
       </c>
-      <c r="T22" s="68"/>
-    </row>
-    <row r="23" spans="1:20" s="129" customFormat="1" ht="80" x14ac:dyDescent="0.2">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="C23" s="172"/>
-      <c r="D23" s="175">
+      <c r="R22" s="72" t="s">
+        <v>89</v>
+      </c>
+      <c r="S22" s="68"/>
+      <c r="T22" s="72" t="s">
+        <v>34</v>
+      </c>
+      <c r="U22" s="68"/>
+    </row>
+    <row r="23" spans="1:21" s="129" customFormat="1" ht="121.5">
+      <c r="A23" s="69"/>
+      <c r="B23" s="69" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" s="130"/>
+      <c r="D23" s="196">
         <v>1250000</v>
       </c>
-      <c r="E23" s="134" t="s">
-        <v>102</v>
+      <c r="E23" s="69" t="s">
+        <v>111</v>
       </c>
       <c r="F23" s="69" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="G23" s="69">
         <v>326</v>
@@ -3056,103 +3335,113 @@
       <c r="H23" s="69">
         <v>2000</v>
       </c>
-      <c r="I23" s="138" t="s">
-        <v>91</v>
-      </c>
-      <c r="J23" s="69"/>
-      <c r="K23" s="155" t="s">
-        <v>27</v>
-      </c>
-      <c r="L23" s="72"/>
-      <c r="M23" s="134" t="s">
+      <c r="I23" s="69" t="s">
+        <v>113</v>
+      </c>
+      <c r="J23" s="172" t="s">
+        <v>100</v>
+      </c>
+      <c r="K23" s="69"/>
+      <c r="L23" s="205" t="s">
         <v>28</v>
       </c>
-      <c r="N23" s="72"/>
+      <c r="M23" s="72"/>
+      <c r="N23" s="154" t="s">
+        <v>29</v>
+      </c>
       <c r="O23" s="72"/>
       <c r="P23" s="72"/>
       <c r="Q23" s="72"/>
-      <c r="R23" s="68"/>
-      <c r="S23" s="72"/>
-      <c r="T23" s="68"/>
-    </row>
-    <row r="24" spans="1:20" ht="272" x14ac:dyDescent="0.2">
-      <c r="A24" s="11">
+      <c r="R23" s="72"/>
+      <c r="S23" s="68"/>
+      <c r="T23" s="72"/>
+      <c r="U23" s="68"/>
+    </row>
+    <row r="24" spans="1:21" ht="275.25">
+      <c r="A24" s="69">
         <v>106912</v>
       </c>
-      <c r="B24" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="C24" s="169" t="s">
-        <v>105</v>
-      </c>
-      <c r="D24" s="11">
+      <c r="B24" s="69" t="s">
+        <v>114</v>
+      </c>
+      <c r="C24" s="208" t="s">
+        <v>115</v>
+      </c>
+      <c r="D24" s="192">
         <v>489000</v>
       </c>
-      <c r="E24" s="134" t="s">
+      <c r="E24" s="69" t="s">
         <v>19</v>
       </c>
       <c r="F24" s="69" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="G24" s="69" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="H24" s="69"/>
-      <c r="I24" s="138" t="s">
-        <v>26</v>
-      </c>
-      <c r="J24" s="69"/>
-      <c r="K24" s="155" t="s">
+      <c r="I24" s="69" t="s">
+        <v>118</v>
+      </c>
+      <c r="J24" s="172" t="s">
         <v>27</v>
       </c>
-      <c r="L24" s="72"/>
-      <c r="M24" s="134" t="s">
+      <c r="K24" s="69"/>
+      <c r="L24" s="205" t="s">
         <v>28</v>
       </c>
-      <c r="N24" s="72" t="s">
-        <v>31</v>
-      </c>
-      <c r="O24" s="72"/>
-      <c r="P24" s="72" t="s">
-        <v>81</v>
-      </c>
+      <c r="M24" s="72"/>
+      <c r="N24" s="154" t="s">
+        <v>29</v>
+      </c>
+      <c r="O24" s="72" t="s">
+        <v>32</v>
+      </c>
+      <c r="P24" s="72"/>
       <c r="Q24" s="72" t="s">
-        <v>82</v>
-      </c>
-      <c r="R24" s="68"/>
-      <c r="S24" s="72" t="s">
-        <v>33</v>
-      </c>
-      <c r="T24" s="68"/>
+        <v>88</v>
+      </c>
+      <c r="R24" s="72" t="s">
+        <v>89</v>
+      </c>
+      <c r="S24" s="68"/>
+      <c r="T24" s="72" t="s">
+        <v>34</v>
+      </c>
+      <c r="U24" s="68"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="I5:I7"/>
+    <mergeCell ref="I2:I4"/>
+  </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <dataValidations count="9">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P24" xr:uid="{50BC6D76-B0DE-424B-A0F5-F3C85CF484BB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q24" xr:uid="{50BC6D76-B0DE-424B-A0F5-F3C85CF484BB}">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O24" xr:uid="{62483C04-38BE-4F6D-B81D-E1F3BC42C93A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P24" xr:uid="{62483C04-38BE-4F6D-B81D-E1F3BC42C93A}">
       <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M24" xr:uid="{08FCFAEA-6806-46C6-962B-8245A865ECF4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N24" xr:uid="{08FCFAEA-6806-46C6-962B-8245A865ECF4}">
       <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N24" xr:uid="{CBE1B3B5-5FA1-4DA6-AA75-48A7E29C1A64}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O24" xr:uid="{CBE1B3B5-5FA1-4DA6-AA75-48A7E29C1A64}">
       <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy, Overall"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K24" xr:uid="{07A695C6-F7C4-4590-B736-45B3A80CC5E9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L24" xr:uid="{07A695C6-F7C4-4590-B736-45B3A80CC5E9}">
       <formula1>"Non-VF, VF"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L24" xr:uid="{25115A9B-B357-42FD-B1AC-232114B311C3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M24" xr:uid="{25115A9B-B357-42FD-B1AC-232114B311C3}">
       <formula1>"Finance, Gender, Efficiency, Just, Health"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S24" xr:uid="{2F04C272-1E8B-47DF-A0A3-277723DA9DED}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T24" xr:uid="{2F04C272-1E8B-47DF-A0A3-277723DA9DED}">
       <formula1>"National, Regional, City, Community"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R24" xr:uid="{32854381-4DCD-4E29-9E8B-45CF8418AA7A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S24" xr:uid="{32854381-4DCD-4E29-9E8B-45CF8418AA7A}">
       <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Other, Unknown"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q24" xr:uid="{064C5753-C5FB-40A5-96E4-2253C486FFE0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R24" xr:uid="{064C5753-C5FB-40A5-96E4-2253C486FFE0}">
       <formula1>"Electricity Access, Energy Efficiency, Renewable Energy, Infrastructure,  Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid, Research &amp; Innovation, Grant &amp; Investment"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3191,23 +3480,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5A33DB6-E091-4CF4-AC1B-DD9D21C57768}">
   <dimension ref="A1:M24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" customWidth="1"/>
-    <col min="4" max="4" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" customWidth="1"/>
-    <col min="6" max="6" width="18.33203125" style="15" customWidth="1"/>
-    <col min="7" max="7" width="35.5" style="16" customWidth="1"/>
-    <col min="8" max="8" width="20.6640625" customWidth="1"/>
-    <col min="9" max="9" width="25.5" customWidth="1"/>
-    <col min="10" max="10" width="19.5" customWidth="1"/>
-    <col min="11" max="12" width="9.1640625"/>
-    <col min="13" max="13" width="42.6640625" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" style="15" customWidth="1"/>
+    <col min="7" max="7" width="35.42578125" style="16" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.5703125" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" customWidth="1"/>
+    <col min="11" max="12" width="9.140625"/>
+    <col min="13" max="13" width="42.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13">
       <c r="A1" s="60" t="s">
         <v>0</v>
       </c>
@@ -3218,7 +3507,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="82" t="s">
-        <v>3</v>
+        <v>119</v>
       </c>
       <c r="E1" s="60" t="s">
         <v>4</v>
@@ -3242,166 +3531,166 @@
         <v>10</v>
       </c>
       <c r="L1" s="38" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="M1" s="117" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" s="92" customFormat="1" ht="91.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="179" t="s">
-        <v>111</v>
-      </c>
-      <c r="B2" s="182" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" s="92" customFormat="1" ht="91.5" customHeight="1">
+      <c r="A2" s="214" t="s">
+        <v>122</v>
+      </c>
+      <c r="B2" s="217" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="198"/>
-      <c r="D2" s="201" t="s">
-        <v>112</v>
+      <c r="C2" s="232"/>
+      <c r="D2" s="235" t="s">
+        <v>123</v>
       </c>
       <c r="E2" s="88" t="s">
         <v>24</v>
       </c>
       <c r="F2" s="89"/>
       <c r="G2" s="90" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="H2" s="91" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="195" t="s">
-        <v>114</v>
-      </c>
-      <c r="J2" s="186" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" s="191"/>
-      <c r="L2" s="188" t="s">
-        <v>115</v>
+      <c r="I2" s="253" t="s">
+        <v>125</v>
+      </c>
+      <c r="J2" s="221" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="226"/>
+      <c r="L2" s="223" t="s">
+        <v>126</v>
       </c>
       <c r="M2" s="118" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" s="180"/>
-      <c r="B3" s="183"/>
-      <c r="C3" s="199"/>
-      <c r="D3" s="202"/>
+        <v>127</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="45.75">
+      <c r="A3" s="215"/>
+      <c r="B3" s="218"/>
+      <c r="C3" s="233"/>
+      <c r="D3" s="236"/>
       <c r="E3" s="65" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="F3" s="66"/>
       <c r="G3" s="74"/>
       <c r="H3" s="64" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="196"/>
-      <c r="J3" s="187"/>
-      <c r="K3" s="192"/>
-      <c r="L3" s="189"/>
+        <v>31</v>
+      </c>
+      <c r="I3" s="230"/>
+      <c r="J3" s="222"/>
+      <c r="K3" s="227"/>
+      <c r="L3" s="224"/>
       <c r="M3" s="119"/>
     </row>
-    <row r="4" spans="1:13" ht="32" x14ac:dyDescent="0.2">
-      <c r="A4" s="181"/>
-      <c r="B4" s="184"/>
-      <c r="C4" s="200"/>
-      <c r="D4" s="203"/>
+    <row r="4" spans="1:13" ht="45.75">
+      <c r="A4" s="216"/>
+      <c r="B4" s="219"/>
+      <c r="C4" s="234"/>
+      <c r="D4" s="237"/>
       <c r="E4" s="67" t="s">
-        <v>34</v>
+        <v>129</v>
       </c>
       <c r="F4" s="60"/>
       <c r="G4" s="74">
         <v>1573000</v>
       </c>
       <c r="H4" s="64" t="s">
-        <v>35</v>
-      </c>
-      <c r="I4" s="197"/>
-      <c r="J4" s="187"/>
-      <c r="K4" s="192"/>
-      <c r="L4" s="189"/>
+        <v>36</v>
+      </c>
+      <c r="I4" s="231"/>
+      <c r="J4" s="222"/>
+      <c r="K4" s="227"/>
+      <c r="L4" s="224"/>
       <c r="M4" s="119"/>
     </row>
-    <row r="5" spans="1:13" s="92" customFormat="1" ht="64" x14ac:dyDescent="0.2">
-      <c r="A5" s="185" t="s">
-        <v>118</v>
-      </c>
-      <c r="B5" s="177" t="s">
-        <v>37</v>
+    <row r="5" spans="1:13" s="92" customFormat="1" ht="76.5">
+      <c r="A5" s="220" t="s">
+        <v>130</v>
+      </c>
+      <c r="B5" s="212" t="s">
+        <v>38</v>
       </c>
       <c r="C5" s="89"/>
       <c r="D5" s="93" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="E5" s="89" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="F5" s="89"/>
       <c r="G5" s="90" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H5" s="89"/>
-      <c r="I5" s="178" t="s">
-        <v>122</v>
-      </c>
-      <c r="J5" s="187"/>
-      <c r="K5" s="192"/>
-      <c r="L5" s="189"/>
+      <c r="I5" s="213" t="s">
+        <v>134</v>
+      </c>
+      <c r="J5" s="222"/>
+      <c r="K5" s="227"/>
+      <c r="L5" s="224"/>
       <c r="M5" s="118" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="185"/>
-      <c r="B6" s="177"/>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="37.5" customHeight="1">
+      <c r="A6" s="220"/>
+      <c r="B6" s="212"/>
       <c r="C6" s="60"/>
       <c r="D6" s="66"/>
       <c r="E6" s="67" t="s">
-        <v>34</v>
+        <v>129</v>
       </c>
       <c r="F6" s="60"/>
       <c r="G6" s="74">
         <v>15660</v>
       </c>
       <c r="H6" s="94" t="s">
-        <v>40</v>
-      </c>
-      <c r="I6" s="178"/>
-      <c r="J6" s="187"/>
-      <c r="K6" s="192"/>
-      <c r="L6" s="189"/>
+        <v>42</v>
+      </c>
+      <c r="I6" s="213"/>
+      <c r="J6" s="222"/>
+      <c r="K6" s="227"/>
+      <c r="L6" s="224"/>
       <c r="M6" s="119"/>
     </row>
-    <row r="7" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="185"/>
-      <c r="B7" s="177"/>
+    <row r="7" spans="1:13" ht="45" customHeight="1">
+      <c r="A7" s="220"/>
+      <c r="B7" s="212"/>
       <c r="C7" s="60"/>
       <c r="D7" s="66"/>
       <c r="E7" s="65" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="F7" s="60"/>
       <c r="G7" s="74">
         <v>200</v>
       </c>
       <c r="H7" s="95" t="s">
-        <v>125</v>
-      </c>
-      <c r="I7" s="178"/>
-      <c r="J7" s="187"/>
-      <c r="K7" s="192"/>
-      <c r="L7" s="189"/>
+        <v>137</v>
+      </c>
+      <c r="I7" s="213"/>
+      <c r="J7" s="222"/>
+      <c r="K7" s="227"/>
+      <c r="L7" s="224"/>
       <c r="M7" s="119"/>
     </row>
-    <row r="8" spans="1:13" s="99" customFormat="1" ht="32" x14ac:dyDescent="0.2">
-      <c r="A8" s="194"/>
-      <c r="B8" s="177" t="s">
-        <v>43</v>
+    <row r="8" spans="1:13" s="99" customFormat="1" ht="45.75">
+      <c r="A8" s="229"/>
+      <c r="B8" s="212" t="s">
+        <v>45</v>
       </c>
       <c r="C8" s="88"/>
       <c r="D8" s="96" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="E8" s="88" t="s">
         <v>24</v>
@@ -3410,30 +3699,30 @@
         <v>0</v>
       </c>
       <c r="G8" s="90" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="H8" s="88" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I8" s="98" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="J8" s="88" t="s">
-        <v>46</v>
-      </c>
-      <c r="K8" s="192"/>
-      <c r="L8" s="189"/>
+        <v>49</v>
+      </c>
+      <c r="K8" s="227"/>
+      <c r="L8" s="224"/>
       <c r="M8" s="120" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" s="13" customFormat="1" ht="48" x14ac:dyDescent="0.2">
-      <c r="A9" s="194"/>
-      <c r="B9" s="177"/>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" s="13" customFormat="1" ht="60.75">
+      <c r="A9" s="229"/>
+      <c r="B9" s="212"/>
       <c r="C9" s="63"/>
       <c r="D9" s="64"/>
       <c r="E9" s="63" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="F9" s="69">
         <v>0</v>
@@ -3442,23 +3731,23 @@
         <v>80</v>
       </c>
       <c r="H9" s="63" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="I9" s="63" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J9" s="63"/>
-      <c r="K9" s="192"/>
-      <c r="L9" s="189"/>
+      <c r="K9" s="227"/>
+      <c r="L9" s="224"/>
       <c r="M9" s="121"/>
     </row>
-    <row r="10" spans="1:13" s="13" customFormat="1" ht="64" x14ac:dyDescent="0.2">
-      <c r="A10" s="194"/>
-      <c r="B10" s="177"/>
+    <row r="10" spans="1:13" s="13" customFormat="1" ht="76.5">
+      <c r="A10" s="229"/>
+      <c r="B10" s="212"/>
       <c r="C10" s="63"/>
       <c r="D10" s="64"/>
       <c r="E10" s="63" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="F10" s="69">
         <v>0</v>
@@ -3467,157 +3756,157 @@
         <v>2</v>
       </c>
       <c r="H10" s="63" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I10" s="63" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J10" s="63"/>
-      <c r="K10" s="193"/>
-      <c r="L10" s="190"/>
+      <c r="K10" s="228"/>
+      <c r="L10" s="225"/>
       <c r="M10" s="121"/>
     </row>
-    <row r="11" spans="1:13" ht="160" x14ac:dyDescent="0.2">
-      <c r="A11" s="176" t="s">
-        <v>131</v>
-      </c>
-      <c r="B11" s="177" t="s">
-        <v>132</v>
+    <row r="11" spans="1:13" ht="183">
+      <c r="A11" s="211" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" s="212" t="s">
+        <v>144</v>
       </c>
       <c r="C11" s="71"/>
       <c r="D11" s="85" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="E11" s="63" t="s">
         <v>24</v>
       </c>
       <c r="F11" s="72" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G11" s="77">
         <v>1.1200000000000001</v>
       </c>
       <c r="H11" s="72" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="I11" s="64" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J11" s="71" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="K11" s="62"/>
       <c r="L11" s="62"/>
       <c r="M11" s="119"/>
     </row>
-    <row r="12" spans="1:13" s="92" customFormat="1" ht="96" x14ac:dyDescent="0.2">
-      <c r="A12" s="176"/>
-      <c r="B12" s="177"/>
+    <row r="12" spans="1:13" s="92" customFormat="1" ht="106.5">
+      <c r="A12" s="211"/>
+      <c r="B12" s="212"/>
       <c r="C12" s="100"/>
       <c r="D12" s="101" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="E12" s="100" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" s="102" t="s">
         <v>60</v>
       </c>
-      <c r="F12" s="102" t="s">
-        <v>57</v>
-      </c>
       <c r="G12" s="103" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H12" s="102" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I12" s="104" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="J12" s="100" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="K12" s="105"/>
       <c r="L12" s="105"/>
       <c r="M12" s="118" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" s="92" customFormat="1" ht="96" x14ac:dyDescent="0.2">
-      <c r="A13" s="176"/>
-      <c r="B13" s="177"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" s="92" customFormat="1" ht="91.5">
+      <c r="A13" s="211"/>
+      <c r="B13" s="212"/>
       <c r="C13" s="100"/>
       <c r="D13" s="101" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="E13" s="100" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="F13" s="102" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G13" s="103" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H13" s="102" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I13" s="104" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="J13" s="100" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="K13" s="105"/>
       <c r="L13" s="105"/>
       <c r="M13" s="118" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="288" x14ac:dyDescent="0.2">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="321">
       <c r="A14" s="74" t="s">
-        <v>63</v>
-      </c>
-      <c r="B14" s="177" t="s">
-        <v>64</v>
+        <v>68</v>
+      </c>
+      <c r="B14" s="212" t="s">
+        <v>69</v>
       </c>
       <c r="C14" s="75" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D14" s="84" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="E14" s="77" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F14" s="76" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="G14" s="76">
         <v>17.09</v>
       </c>
       <c r="H14" s="74" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="I14" s="74" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="J14" s="71" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K14" s="62"/>
       <c r="L14" s="62"/>
       <c r="M14" s="119"/>
     </row>
-    <row r="15" spans="1:13" ht="272" x14ac:dyDescent="0.2">
-      <c r="A15" s="178"/>
-      <c r="B15" s="177"/>
+    <row r="15" spans="1:13" ht="305.25">
+      <c r="A15" s="213"/>
+      <c r="B15" s="212"/>
       <c r="C15" s="75" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D15" s="84" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="E15" s="77" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F15" s="84">
         <v>30268</v>
@@ -3626,13 +3915,13 @@
         <v>110000</v>
       </c>
       <c r="H15" s="106" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="I15" s="74" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="J15" s="71" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K15" s="107">
         <v>0.4</v>
@@ -3640,71 +3929,71 @@
       <c r="L15" s="62"/>
       <c r="M15" s="119"/>
     </row>
-    <row r="16" spans="1:13" s="92" customFormat="1" ht="176" x14ac:dyDescent="0.2">
-      <c r="A16" s="178"/>
-      <c r="B16" s="177"/>
+    <row r="16" spans="1:13" s="92" customFormat="1" ht="167.25">
+      <c r="A16" s="213"/>
+      <c r="B16" s="212"/>
       <c r="C16" s="108" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D16" s="91" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="E16" s="103" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F16" s="90"/>
       <c r="G16" s="109"/>
       <c r="I16" s="90" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="J16" s="110" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K16" s="105"/>
       <c r="L16" s="105"/>
       <c r="M16" s="122" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="96" x14ac:dyDescent="0.2">
-      <c r="A17" s="178"/>
-      <c r="B17" s="177"/>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="106.5">
+      <c r="A17" s="213"/>
+      <c r="B17" s="212"/>
       <c r="C17" s="75" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D17" s="64" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="E17" s="77" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="F17" s="74"/>
       <c r="G17" s="64">
         <v>1220</v>
       </c>
       <c r="H17" s="74" t="s">
+        <v>80</v>
+      </c>
+      <c r="I17" s="74" t="s">
+        <v>81</v>
+      </c>
+      <c r="J17" s="62" t="s">
         <v>73</v>
-      </c>
-      <c r="I17" s="74" t="s">
-        <v>74</v>
-      </c>
-      <c r="J17" s="62" t="s">
-        <v>67</v>
       </c>
       <c r="K17" s="62"/>
       <c r="L17" s="62"/>
       <c r="M17" s="119"/>
     </row>
-    <row r="18" spans="1:13" ht="176" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" ht="167.25">
       <c r="A18" s="78" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="B18" s="79" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C18" s="62"/>
       <c r="D18" s="83" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="E18" s="80" t="s">
         <v>19</v>
@@ -3712,90 +4001,90 @@
       <c r="F18" s="73"/>
       <c r="G18" s="74"/>
       <c r="H18" s="80" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="I18" s="64" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="J18" s="68" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="K18" s="62"/>
       <c r="L18" s="62"/>
       <c r="M18" s="119"/>
     </row>
-    <row r="19" spans="1:13" s="92" customFormat="1" ht="160" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" s="92" customFormat="1" ht="183">
       <c r="A19" s="105"/>
       <c r="B19" s="111" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C19" s="112"/>
       <c r="D19" s="96" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="E19" s="104" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F19" s="113">
         <v>0</v>
       </c>
       <c r="G19" s="90" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="H19" s="104" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="I19" s="104" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="J19" s="114" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="K19" s="105"/>
       <c r="L19" s="105"/>
       <c r="M19" s="123" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" s="92" customFormat="1" ht="320" x14ac:dyDescent="0.2">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" s="92" customFormat="1" ht="336">
       <c r="A20" s="105"/>
       <c r="B20" s="88" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C20" s="112"/>
       <c r="D20" s="96" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="E20" s="104" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F20" s="113">
         <v>0.7</v>
       </c>
       <c r="G20" s="90"/>
       <c r="H20" s="104" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="I20" s="104" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="J20" s="114" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="K20" s="105"/>
       <c r="L20" s="105"/>
       <c r="M20" s="124" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" s="92" customFormat="1" ht="112" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" s="92" customFormat="1" ht="106.5">
       <c r="A21" s="62"/>
       <c r="B21" s="70" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C21" s="71"/>
       <c r="D21" s="84" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="E21" s="70" t="s">
         <v>19</v>
@@ -3807,26 +4096,26 @@
         <v>1</v>
       </c>
       <c r="H21" s="70" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="I21" s="70" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="J21" s="87" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="K21" s="62"/>
       <c r="L21" s="62"/>
       <c r="M21" s="125"/>
     </row>
-    <row r="22" spans="1:13" ht="96" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" ht="91.5">
       <c r="A22" s="62"/>
       <c r="B22" s="70" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="C22" s="81"/>
       <c r="D22" s="86" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="E22" s="70" t="s">
         <v>19</v>
@@ -3838,29 +4127,29 @@
         <v>3</v>
       </c>
       <c r="H22" s="70" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="I22" s="70" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="J22" s="87" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="K22" s="62"/>
       <c r="L22" s="62"/>
       <c r="M22" s="119"/>
     </row>
-    <row r="23" spans="1:13" s="92" customFormat="1" ht="350" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13" s="92" customFormat="1" ht="381.75">
       <c r="A23" s="105"/>
       <c r="B23" s="104" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="C23" s="115"/>
       <c r="D23" s="116" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="E23" s="104" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="F23" s="100">
         <v>326</v>
@@ -3869,50 +4158,50 @@
         <v>1000</v>
       </c>
       <c r="H23" s="104" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="I23" s="104" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="J23" s="114" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="K23" s="105"/>
       <c r="L23" s="105"/>
       <c r="M23" s="118" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="350" x14ac:dyDescent="0.2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="336">
       <c r="A24" s="77">
         <v>106912</v>
       </c>
       <c r="B24" s="64" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C24" s="77"/>
       <c r="D24" s="84" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="E24" s="64" t="s">
+        <v>128</v>
+      </c>
+      <c r="F24" s="64" t="s">
         <v>117</v>
-      </c>
-      <c r="F24" s="64" t="s">
-        <v>107</v>
       </c>
       <c r="G24" s="74"/>
       <c r="H24" s="64" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="I24" s="64" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="J24" s="87" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K24" s="62"/>
       <c r="L24" s="67" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="M24" s="119"/>
     </row>
@@ -3963,21 +4252,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" customWidth="1"/>
-    <col min="4" max="4" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="20.6640625" customWidth="1"/>
-    <col min="7" max="7" width="18.33203125" style="15" customWidth="1"/>
-    <col min="8" max="8" width="35.5" style="16" customWidth="1"/>
-    <col min="9" max="9" width="25.5" customWidth="1"/>
-    <col min="10" max="10" width="19.5" customWidth="1"/>
-    <col min="11" max="11" width="22.5" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="20.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" style="15" customWidth="1"/>
+    <col min="8" max="8" width="35.42578125" style="16" customWidth="1"/>
+    <col min="9" max="9" width="25.5703125" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" customWidth="1"/>
+    <col min="11" max="11" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3988,7 +4277,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="59" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -4009,14 +4298,14 @@
         <v>9</v>
       </c>
       <c r="K1" s="39" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="80" x14ac:dyDescent="0.2">
-      <c r="A2" s="212" t="s">
-        <v>111</v>
-      </c>
-      <c r="B2" s="207" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="91.5">
+      <c r="A2" s="246" t="s">
+        <v>122</v>
+      </c>
+      <c r="B2" s="241" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="1"/>
@@ -4031,62 +4320,62 @@
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="I2" s="204" t="s">
-        <v>171</v>
+        <v>124</v>
+      </c>
+      <c r="I2" s="238" t="s">
+        <v>183</v>
       </c>
       <c r="J2" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" s="204" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="80" x14ac:dyDescent="0.2">
-      <c r="A3" s="213"/>
-      <c r="B3" s="208"/>
+        <v>27</v>
+      </c>
+      <c r="K2" s="238" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="76.5">
+      <c r="A3" s="247"/>
+      <c r="B3" s="242"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="17" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="I3" s="205"/>
+        <v>185</v>
+      </c>
+      <c r="I3" s="239"/>
       <c r="J3" s="41"/>
-      <c r="K3" s="205"/>
-    </row>
-    <row r="4" spans="1:11" ht="48" x14ac:dyDescent="0.2">
-      <c r="A4" s="214"/>
-      <c r="B4" s="209"/>
+      <c r="K3" s="239"/>
+    </row>
+    <row r="4" spans="1:11" ht="60.75">
+      <c r="A4" s="248"/>
+      <c r="B4" s="243"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="7" t="s">
-        <v>34</v>
+        <v>129</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="I4" s="206"/>
+        <v>186</v>
+      </c>
+      <c r="I4" s="240"/>
       <c r="J4" s="42"/>
-      <c r="K4" s="206"/>
-    </row>
-    <row r="5" spans="1:11" ht="96" x14ac:dyDescent="0.2">
-      <c r="A5" s="212" t="s">
-        <v>118</v>
-      </c>
-      <c r="B5" s="207" t="s">
-        <v>37</v>
+      <c r="K4" s="240"/>
+    </row>
+    <row r="5" spans="1:11" ht="106.5">
+      <c r="A5" s="246" t="s">
+        <v>130</v>
+      </c>
+      <c r="B5" s="241" t="s">
+        <v>38</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="8">
@@ -4098,77 +4387,77 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="I5" s="204" t="s">
-        <v>176</v>
+        <v>187</v>
+      </c>
+      <c r="I5" s="238" t="s">
+        <v>188</v>
       </c>
       <c r="J5" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="K5" s="204" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A6" s="213"/>
-      <c r="B6" s="208"/>
+        <v>27</v>
+      </c>
+      <c r="K5" s="238" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="45.75">
+      <c r="A6" s="247"/>
+      <c r="B6" s="242"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="7" t="s">
-        <v>34</v>
+        <v>129</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="I6" s="205"/>
+        <v>190</v>
+      </c>
+      <c r="I6" s="239"/>
       <c r="J6" s="41"/>
-      <c r="K6" s="205"/>
-    </row>
-    <row r="7" spans="1:11" ht="96" x14ac:dyDescent="0.2">
-      <c r="A7" s="213"/>
-      <c r="B7" s="208"/>
+      <c r="K6" s="239"/>
+    </row>
+    <row r="7" spans="1:11" ht="106.5">
+      <c r="A7" s="247"/>
+      <c r="B7" s="242"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="17" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="F7" s="9"/>
       <c r="G7" s="1"/>
       <c r="H7" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="I7" s="205"/>
+        <v>137</v>
+      </c>
+      <c r="I7" s="239"/>
       <c r="J7" s="42"/>
-      <c r="K7" s="206"/>
-    </row>
-    <row r="8" spans="1:11" ht="160" x14ac:dyDescent="0.2">
-      <c r="A8" s="214"/>
-      <c r="B8" s="209"/>
+      <c r="K7" s="240"/>
+    </row>
+    <row r="8" spans="1:11" ht="167.25">
+      <c r="A8" s="248"/>
+      <c r="B8" s="243"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="7" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="I8" s="206"/>
+        <v>193</v>
+      </c>
+      <c r="I8" s="240"/>
       <c r="J8" s="55" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K8" s="56"/>
     </row>
-    <row r="9" spans="1:11" s="13" customFormat="1" ht="32" x14ac:dyDescent="0.2">
-      <c r="A9" s="215" t="s">
-        <v>182</v>
-      </c>
-      <c r="B9" s="207" t="s">
-        <v>43</v>
+    <row r="9" spans="1:11" s="13" customFormat="1" ht="45.75">
+      <c r="A9" s="249" t="s">
+        <v>194</v>
+      </c>
+      <c r="B9" s="241" t="s">
+        <v>45</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="10">
@@ -4178,162 +4467,162 @@
         <v>24</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G9" s="11">
         <v>0</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="44" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K9" s="47" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" s="13" customFormat="1" ht="48" x14ac:dyDescent="0.2">
-      <c r="A10" s="216"/>
-      <c r="B10" s="208"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="13" customFormat="1" ht="60.75">
+      <c r="A10" s="250"/>
+      <c r="B10" s="242"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G10" s="11">
         <v>0</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J10" s="45"/>
       <c r="K10" s="48"/>
     </row>
-    <row r="11" spans="1:11" s="13" customFormat="1" ht="48" x14ac:dyDescent="0.2">
-      <c r="A11" s="217"/>
-      <c r="B11" s="209"/>
+    <row r="11" spans="1:11" s="13" customFormat="1" ht="45.75">
+      <c r="A11" s="251"/>
+      <c r="B11" s="243"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G11" s="11">
         <v>0</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="J11" s="46"/>
       <c r="K11" s="49" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="112" x14ac:dyDescent="0.2">
-      <c r="A12" s="210" t="s">
-        <v>131</v>
-      </c>
-      <c r="B12" s="211" t="s">
-        <v>132</v>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="137.25">
+      <c r="A12" s="244" t="s">
+        <v>143</v>
+      </c>
+      <c r="B12" s="245" t="s">
+        <v>144</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="50" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>24</v>
       </c>
       <c r="F12" s="35" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G12" s="35" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H12" s="35" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="J12" s="51" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="K12" s="52" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="64" x14ac:dyDescent="0.2">
-      <c r="A13" s="210"/>
-      <c r="B13" s="211"/>
+        <v>202</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="76.5">
+      <c r="A13" s="244"/>
+      <c r="B13" s="245"/>
       <c r="C13" s="14"/>
       <c r="D13" s="2" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="E13" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="F13" s="35" t="s">
-        <v>57</v>
-      </c>
       <c r="G13" s="35" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="K13" s="57" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="64" x14ac:dyDescent="0.2">
-      <c r="A14" s="210"/>
-      <c r="B14" s="211"/>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="60.75">
+      <c r="A14" s="244"/>
+      <c r="B14" s="245"/>
       <c r="C14" s="14"/>
       <c r="D14" s="2" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="F14" s="35" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G14" s="35" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H14" s="35" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="K14" s="57" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="18"/>
       <c r="B15" s="18"/>
       <c r="C15" s="18"/>
@@ -4344,53 +4633,53 @@
       <c r="H15" s="20"/>
       <c r="I15" s="18"/>
     </row>
-    <row r="16" spans="1:11" ht="288" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="321">
       <c r="A16" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="B16" s="207" t="s">
-        <v>64</v>
+        <v>68</v>
+      </c>
+      <c r="B16" s="241" t="s">
+        <v>69</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D16" s="23">
         <v>5356014</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="G16" s="23" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="H16" s="23" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="I16" s="21" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K16" s="18"/>
     </row>
-    <row r="17" spans="1:11" ht="176" x14ac:dyDescent="0.2">
-      <c r="A17" s="204"/>
-      <c r="B17" s="208"/>
+    <row r="17" spans="1:11" ht="183">
+      <c r="A17" s="238"/>
+      <c r="B17" s="242"/>
       <c r="C17" s="22" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D17" s="23">
         <v>5356014</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F17" s="21" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="G17" s="23">
         <v>30268</v>
@@ -4399,73 +4688,73 @@
         <v>110000</v>
       </c>
       <c r="I17" s="21" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K17" s="18"/>
     </row>
-    <row r="18" spans="1:11" ht="176" x14ac:dyDescent="0.2">
-      <c r="A18" s="205"/>
-      <c r="B18" s="208"/>
+    <row r="18" spans="1:11" ht="167.25">
+      <c r="A18" s="239"/>
+      <c r="B18" s="242"/>
       <c r="C18" s="22" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="G18" s="21"/>
       <c r="H18" s="23" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="I18" s="21" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="J18" s="55" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K18" s="18"/>
     </row>
-    <row r="19" spans="1:11" ht="96" x14ac:dyDescent="0.2">
-      <c r="A19" s="206"/>
-      <c r="B19" s="209"/>
+    <row r="19" spans="1:11" ht="106.5">
+      <c r="A19" s="240"/>
+      <c r="B19" s="243"/>
       <c r="C19" s="22" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="F19" s="21" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G19" s="21"/>
       <c r="H19" s="21">
         <v>1220</v>
       </c>
       <c r="I19" s="21" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J19" s="18" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K19" s="18"/>
     </row>
-    <row r="20" spans="1:11" ht="96" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" ht="106.5">
       <c r="A20" s="30" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C20" s="18"/>
       <c r="D20" s="31">
@@ -4475,92 +4764,92 @@
         <v>19</v>
       </c>
       <c r="F20" s="32" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="G20" s="19"/>
       <c r="H20" s="33" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I20" s="18"/>
       <c r="J20" s="55" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="K20" s="55" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="160" x14ac:dyDescent="0.2">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="183">
       <c r="A21" s="18"/>
       <c r="B21" s="9" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C21" s="25"/>
       <c r="D21" s="26">
         <v>150000</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="G21" s="27">
         <v>0</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="J21" s="54" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="K21" s="18"/>
     </row>
-    <row r="22" spans="1:11" ht="320" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" ht="336">
       <c r="A22" s="18"/>
       <c r="B22" s="5" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C22" s="25"/>
       <c r="D22" s="26">
         <v>600000</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="G22" s="27">
         <v>0.7</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="J22" s="53" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="K22" s="18"/>
     </row>
-    <row r="23" spans="1:11" ht="112" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" ht="106.5">
       <c r="A23" s="18"/>
       <c r="B23" s="12" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C23" s="14"/>
       <c r="D23" s="26">
         <v>300000</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="G23" s="14">
         <v>0</v>
@@ -4569,17 +4858,17 @@
         <v>1</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="J23" s="53" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="K23" s="18"/>
     </row>
-    <row r="24" spans="1:11" ht="80" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" ht="91.5">
       <c r="A24" s="18"/>
       <c r="B24" s="12" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="C24" s="25"/>
       <c r="D24" s="28">
@@ -4589,7 +4878,7 @@
         <v>19</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="G24" s="14">
         <v>1</v>
@@ -4598,27 +4887,27 @@
         <v>3</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="J24" s="53" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="K24" s="18"/>
     </row>
-    <row r="25" spans="1:11" ht="350" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" ht="381.75">
       <c r="A25" s="18"/>
       <c r="B25" s="12" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="C25" s="29"/>
       <c r="D25" s="28">
         <v>1250000</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="G25" s="14">
         <v>326</v>
@@ -4627,41 +4916,41 @@
         <v>1000</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="J25" s="53" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="K25" s="18"/>
     </row>
-    <row r="26" spans="1:11" ht="304" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" ht="336">
       <c r="A26" s="37">
         <v>106912</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C26" s="24"/>
       <c r="D26" s="34">
         <v>489000</v>
       </c>
       <c r="E26" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="H26" s="3" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="J26" s="55" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K26" s="18"/>
     </row>
@@ -4709,185 +4998,185 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="52.6640625" customWidth="1"/>
+    <col min="1" max="2" width="52.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="147" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="197" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="147" t="s">
+      <c r="B1" s="197" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" s="156" t="s">
-        <v>140</v>
-      </c>
-      <c r="B2" s="148" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="156" t="s">
+    <row r="2" spans="1:2" ht="45.75">
+      <c r="A2" s="254" t="s">
+        <v>152</v>
+      </c>
+      <c r="B2" s="198" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="254" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="148" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A4" s="156" t="s">
-        <v>85</v>
-      </c>
-      <c r="B4" s="148" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A5" s="156" t="s">
-        <v>211</v>
-      </c>
-      <c r="B5" s="148" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="96" x14ac:dyDescent="0.2">
-      <c r="A6" s="156" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="148" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="48" x14ac:dyDescent="0.2">
-      <c r="A7" s="156" t="s">
-        <v>214</v>
-      </c>
-      <c r="B7" s="148" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A8" s="156" t="s">
-        <v>60</v>
-      </c>
-      <c r="B8" s="148" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A9" s="156" t="s">
-        <v>102</v>
-      </c>
-      <c r="B9" s="148" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A10" s="156" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="157" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A11" s="156" t="s">
-        <v>219</v>
-      </c>
-      <c r="B11" s="157" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="48" x14ac:dyDescent="0.2">
-      <c r="A12" s="156" t="s">
+      <c r="B3" s="198" t="s">
         <v>221</v>
       </c>
-      <c r="B12" s="148" t="s">
+    </row>
+    <row r="4" spans="1:2" ht="30.75">
+      <c r="A4" s="254" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" s="198" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="156" t="s">
-        <v>68</v>
-      </c>
-      <c r="B13" s="157" t="s">
+    <row r="5" spans="1:2" ht="30.75">
+      <c r="A5" s="254" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="156" t="s">
+      <c r="B5" s="198" t="s">
         <v>224</v>
       </c>
-      <c r="B14" s="157" t="s">
+    </row>
+    <row r="6" spans="1:2" ht="91.5">
+      <c r="A6" s="254" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="198" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A15" s="156" t="s">
+    <row r="7" spans="1:2" ht="45.75">
+      <c r="A7" s="254" t="s">
         <v>226</v>
       </c>
-      <c r="B15" s="157" t="s">
+      <c r="B7" s="198" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A16" s="156" t="s">
-        <v>71</v>
-      </c>
-      <c r="B16" s="157" t="s">
+    <row r="8" spans="1:2" ht="45.75">
+      <c r="A8" s="254" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="198" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A17" s="156" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="148" t="s">
+    <row r="9" spans="1:2" ht="45.75">
+      <c r="A9" s="254" t="s">
+        <v>111</v>
+      </c>
+      <c r="B9" s="198" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A18" s="156" t="s">
+    <row r="10" spans="1:2" ht="30.75">
+      <c r="A10" s="254" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="255" t="s">
         <v>230</v>
       </c>
-      <c r="B18" s="157" t="s">
+    </row>
+    <row r="11" spans="1:2" ht="30.75">
+      <c r="A11" s="254" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" ht="64" x14ac:dyDescent="0.2">
-      <c r="A19" s="156" t="s">
+      <c r="B11" s="255" t="s">
         <v>232</v>
       </c>
-      <c r="B19" s="157" t="s">
+    </row>
+    <row r="12" spans="1:2" ht="45.75">
+      <c r="A12" s="254" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="156" t="s">
+      <c r="B12" s="198" t="s">
         <v>234</v>
       </c>
-      <c r="B20" s="157" t="s">
+    </row>
+    <row r="13" spans="1:2" ht="30.75">
+      <c r="A13" s="254" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" s="255" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A21" s="156" t="s">
+    <row r="14" spans="1:2">
+      <c r="A14" s="254" t="s">
+        <v>236</v>
+      </c>
+      <c r="B14" s="255" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="30.75">
+      <c r="A15" s="254" t="s">
+        <v>238</v>
+      </c>
+      <c r="B15" s="255" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="30.75">
+      <c r="A16" s="254" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="255" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="30.75">
+      <c r="A17" s="254" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="198" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="30.75">
+      <c r="A18" s="254" t="s">
+        <v>242</v>
+      </c>
+      <c r="B18" s="255" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="76.5">
+      <c r="A19" s="254" t="s">
+        <v>244</v>
+      </c>
+      <c r="B19" s="255" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="30.75">
+      <c r="A20" s="254" t="s">
+        <v>246</v>
+      </c>
+      <c r="B20" s="255" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="45.75">
+      <c r="A21" s="254" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="158" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A22" s="156" t="s">
-        <v>237</v>
-      </c>
-      <c r="B22" s="157" t="s">
-        <v>238</v>
+      <c r="B21" s="256" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="30.75">
+      <c r="A22" s="254" t="s">
+        <v>249</v>
+      </c>
+      <c r="B22" s="255" t="s">
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -4958,8 +5247,8 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -4984,6 +5273,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -5063,6 +5353,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -5207,39 +5502,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D06A8A7-AAD0-46D5-9E3E-4D298B186157}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D06A8A7-AAD0-46D5-9E3E-4D298B186157}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84AEDBCE-AE29-4AA3-A5BD-B932231712F2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
-    <ds:schemaRef ds:uri="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84AEDBCE-AE29-4AA3-A5BD-B932231712F2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3011BB0-07FE-4680-800E-7F4C36F905EE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
-    <ds:schemaRef ds:uri="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E36ED78C-029F-4A50-B3B7-CA985A738900}"/>
 </file>
--- a/01_Input/00_CO Validation/Bangladesh - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Bangladesh - Energy Projects.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UNDP-BD\Energy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="653" documentId="13_ncr:1_{F9E229CD-093B-4957-8526-AA7B64B04BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6F11B5D-5BEE-4400-A444-2EA03BC518C6}"/>
+  <xr:revisionPtr revIDLastSave="656" documentId="13_ncr:1_{F9E229CD-093B-4957-8526-AA7B64B04BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE47DFBB-AFFD-4ADD-986A-E01736B1750E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -140,7 +140,7 @@
     <t>Policy Population</t>
   </si>
   <si>
-    <t>115022</t>
+    <t>117898</t>
   </si>
   <si>
     <t>Promoting Energy-Related Low Carbon Urban Development in Bangladesh (LCUD)</t>
@@ -264,7 +264,7 @@
 Farmers and fishers are the users of the solar cold storage</t>
   </si>
   <si>
-    <t>93426</t>
+    <t>85984</t>
   </si>
   <si>
     <t>Local Government Initiative on Climate Change (LoGIC)</t>
@@ -1877,15 +1877,66 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1905,57 +1956,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3359,7 +3359,7 @@
     </row>
     <row r="24" spans="1:21" ht="275.25">
       <c r="A24" s="69">
-        <v>106912</v>
+        <v>105918</v>
       </c>
       <c r="B24" s="69" t="s">
         <v>114</v>
@@ -3538,14 +3538,14 @@
       </c>
     </row>
     <row r="2" spans="1:13" s="92" customFormat="1" ht="91.5" customHeight="1">
-      <c r="A2" s="214" t="s">
+      <c r="A2" s="231" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="217" t="s">
+      <c r="B2" s="234" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="232"/>
-      <c r="D2" s="235" t="s">
+      <c r="C2" s="224"/>
+      <c r="D2" s="227" t="s">
         <v>123</v>
       </c>
       <c r="E2" s="88" t="s">
@@ -3561,11 +3561,11 @@
       <c r="I2" s="253" t="s">
         <v>125</v>
       </c>
-      <c r="J2" s="221" t="s">
+      <c r="J2" s="211" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="226"/>
-      <c r="L2" s="223" t="s">
+      <c r="K2" s="216"/>
+      <c r="L2" s="213" t="s">
         <v>126</v>
       </c>
       <c r="M2" s="118" t="s">
@@ -3573,10 +3573,10 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="45.75">
-      <c r="A3" s="215"/>
-      <c r="B3" s="218"/>
-      <c r="C3" s="233"/>
-      <c r="D3" s="236"/>
+      <c r="A3" s="232"/>
+      <c r="B3" s="235"/>
+      <c r="C3" s="225"/>
+      <c r="D3" s="228"/>
       <c r="E3" s="65" t="s">
         <v>128</v>
       </c>
@@ -3585,17 +3585,17 @@
       <c r="H3" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="I3" s="230"/>
-      <c r="J3" s="222"/>
-      <c r="K3" s="227"/>
-      <c r="L3" s="224"/>
+      <c r="I3" s="221"/>
+      <c r="J3" s="212"/>
+      <c r="K3" s="217"/>
+      <c r="L3" s="214"/>
       <c r="M3" s="119"/>
     </row>
     <row r="4" spans="1:13" ht="45.75">
-      <c r="A4" s="216"/>
-      <c r="B4" s="219"/>
-      <c r="C4" s="234"/>
-      <c r="D4" s="237"/>
+      <c r="A4" s="233"/>
+      <c r="B4" s="236"/>
+      <c r="C4" s="226"/>
+      <c r="D4" s="229"/>
       <c r="E4" s="67" t="s">
         <v>129</v>
       </c>
@@ -3606,17 +3606,17 @@
       <c r="H4" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="231"/>
-      <c r="J4" s="222"/>
-      <c r="K4" s="227"/>
-      <c r="L4" s="224"/>
+      <c r="I4" s="222"/>
+      <c r="J4" s="212"/>
+      <c r="K4" s="217"/>
+      <c r="L4" s="214"/>
       <c r="M4" s="119"/>
     </row>
     <row r="5" spans="1:13" s="92" customFormat="1" ht="76.5">
-      <c r="A5" s="220" t="s">
+      <c r="A5" s="237" t="s">
         <v>130</v>
       </c>
-      <c r="B5" s="212" t="s">
+      <c r="B5" s="220" t="s">
         <v>38</v>
       </c>
       <c r="C5" s="89"/>
@@ -3631,19 +3631,19 @@
         <v>133</v>
       </c>
       <c r="H5" s="89"/>
-      <c r="I5" s="213" t="s">
+      <c r="I5" s="223" t="s">
         <v>134</v>
       </c>
-      <c r="J5" s="222"/>
-      <c r="K5" s="227"/>
-      <c r="L5" s="224"/>
+      <c r="J5" s="212"/>
+      <c r="K5" s="217"/>
+      <c r="L5" s="214"/>
       <c r="M5" s="118" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="37.5" customHeight="1">
-      <c r="A6" s="220"/>
-      <c r="B6" s="212"/>
+      <c r="A6" s="237"/>
+      <c r="B6" s="220"/>
       <c r="C6" s="60"/>
       <c r="D6" s="66"/>
       <c r="E6" s="67" t="s">
@@ -3656,15 +3656,15 @@
       <c r="H6" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="I6" s="213"/>
-      <c r="J6" s="222"/>
-      <c r="K6" s="227"/>
-      <c r="L6" s="224"/>
+      <c r="I6" s="223"/>
+      <c r="J6" s="212"/>
+      <c r="K6" s="217"/>
+      <c r="L6" s="214"/>
       <c r="M6" s="119"/>
     </row>
     <row r="7" spans="1:13" ht="45" customHeight="1">
-      <c r="A7" s="220"/>
-      <c r="B7" s="212"/>
+      <c r="A7" s="237"/>
+      <c r="B7" s="220"/>
       <c r="C7" s="60"/>
       <c r="D7" s="66"/>
       <c r="E7" s="65" t="s">
@@ -3677,15 +3677,15 @@
       <c r="H7" s="95" t="s">
         <v>137</v>
       </c>
-      <c r="I7" s="213"/>
-      <c r="J7" s="222"/>
-      <c r="K7" s="227"/>
-      <c r="L7" s="224"/>
+      <c r="I7" s="223"/>
+      <c r="J7" s="212"/>
+      <c r="K7" s="217"/>
+      <c r="L7" s="214"/>
       <c r="M7" s="119"/>
     </row>
     <row r="8" spans="1:13" s="99" customFormat="1" ht="45.75">
-      <c r="A8" s="229"/>
-      <c r="B8" s="212" t="s">
+      <c r="A8" s="219"/>
+      <c r="B8" s="220" t="s">
         <v>45</v>
       </c>
       <c r="C8" s="88"/>
@@ -3710,15 +3710,15 @@
       <c r="J8" s="88" t="s">
         <v>49</v>
       </c>
-      <c r="K8" s="227"/>
-      <c r="L8" s="224"/>
+      <c r="K8" s="217"/>
+      <c r="L8" s="214"/>
       <c r="M8" s="120" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:13" s="13" customFormat="1" ht="60.75">
-      <c r="A9" s="229"/>
-      <c r="B9" s="212"/>
+      <c r="A9" s="219"/>
+      <c r="B9" s="220"/>
       <c r="C9" s="63"/>
       <c r="D9" s="64"/>
       <c r="E9" s="63" t="s">
@@ -3737,13 +3737,13 @@
         <v>53</v>
       </c>
       <c r="J9" s="63"/>
-      <c r="K9" s="227"/>
-      <c r="L9" s="224"/>
+      <c r="K9" s="217"/>
+      <c r="L9" s="214"/>
       <c r="M9" s="121"/>
     </row>
     <row r="10" spans="1:13" s="13" customFormat="1" ht="76.5">
-      <c r="A10" s="229"/>
-      <c r="B10" s="212"/>
+      <c r="A10" s="219"/>
+      <c r="B10" s="220"/>
       <c r="C10" s="63"/>
       <c r="D10" s="64"/>
       <c r="E10" s="63" t="s">
@@ -3762,15 +3762,15 @@
         <v>55</v>
       </c>
       <c r="J10" s="63"/>
-      <c r="K10" s="228"/>
-      <c r="L10" s="225"/>
+      <c r="K10" s="218"/>
+      <c r="L10" s="215"/>
       <c r="M10" s="121"/>
     </row>
     <row r="11" spans="1:13" ht="183">
-      <c r="A11" s="211" t="s">
+      <c r="A11" s="230" t="s">
         <v>143</v>
       </c>
-      <c r="B11" s="212" t="s">
+      <c r="B11" s="220" t="s">
         <v>144</v>
       </c>
       <c r="C11" s="71"/>
@@ -3800,8 +3800,8 @@
       <c r="M11" s="119"/>
     </row>
     <row r="12" spans="1:13" s="92" customFormat="1" ht="106.5">
-      <c r="A12" s="211"/>
-      <c r="B12" s="212"/>
+      <c r="A12" s="230"/>
+      <c r="B12" s="220"/>
       <c r="C12" s="100"/>
       <c r="D12" s="101" t="s">
         <v>148</v>
@@ -3831,8 +3831,8 @@
       </c>
     </row>
     <row r="13" spans="1:13" s="92" customFormat="1" ht="91.5">
-      <c r="A13" s="211"/>
-      <c r="B13" s="212"/>
+      <c r="A13" s="230"/>
+      <c r="B13" s="220"/>
       <c r="C13" s="100"/>
       <c r="D13" s="101" t="s">
         <v>151</v>
@@ -3865,7 +3865,7 @@
       <c r="A14" s="74" t="s">
         <v>68</v>
       </c>
-      <c r="B14" s="212" t="s">
+      <c r="B14" s="220" t="s">
         <v>69</v>
       </c>
       <c r="C14" s="75" t="s">
@@ -3897,8 +3897,8 @@
       <c r="M14" s="119"/>
     </row>
     <row r="15" spans="1:13" ht="305.25">
-      <c r="A15" s="213"/>
-      <c r="B15" s="212"/>
+      <c r="A15" s="223"/>
+      <c r="B15" s="220"/>
       <c r="C15" s="75" t="s">
         <v>70</v>
       </c>
@@ -3930,8 +3930,8 @@
       <c r="M15" s="119"/>
     </row>
     <row r="16" spans="1:13" s="92" customFormat="1" ht="167.25">
-      <c r="A16" s="213"/>
-      <c r="B16" s="212"/>
+      <c r="A16" s="223"/>
+      <c r="B16" s="220"/>
       <c r="C16" s="108" t="s">
         <v>70</v>
       </c>
@@ -3956,8 +3956,8 @@
       </c>
     </row>
     <row r="17" spans="1:13" ht="106.5">
-      <c r="A17" s="213"/>
-      <c r="B17" s="212"/>
+      <c r="A17" s="223"/>
+      <c r="B17" s="220"/>
       <c r="C17" s="75" t="s">
         <v>70</v>
       </c>
@@ -4207,6 +4207,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
     <mergeCell ref="J2:J7"/>
     <mergeCell ref="L2:L10"/>
     <mergeCell ref="K2:K10"/>
@@ -4216,14 +4224,6 @@
     <mergeCell ref="I5:I7"/>
     <mergeCell ref="C2:C4"/>
     <mergeCell ref="D2:D4"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <hyperlinks>
@@ -5185,68 +5185,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-    <SharedWithUsers xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59">
-      <UserInfo>
-        <DisplayName>Akiko Yamamoto</DisplayName>
-        <AccountId>84</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Arif Mohammad Faisal</DisplayName>
-        <AccountId>1690</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Maliha Muzammil</DisplayName>
-        <AccountId>1969</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Van Nguyen</DisplayName>
-        <AccountId>1970</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Riad Meddeb</DisplayName>
-        <AccountId>9</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Benjamin Keller</DisplayName>
-        <AccountId>1227</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Bahtiyar Kurt</DisplayName>
-        <AccountId>206</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Stefano Pistolese</DisplayName>
-        <AccountId>772</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -5501,8 +5439,70 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+    <SharedWithUsers xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59">
+      <UserInfo>
+        <DisplayName>Akiko Yamamoto</DisplayName>
+        <AccountId>84</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Arif Mohammad Faisal</DisplayName>
+        <AccountId>1690</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Maliha Muzammil</DisplayName>
+        <AccountId>1969</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Van Nguyen</DisplayName>
+        <AccountId>1970</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Riad Meddeb</DisplayName>
+        <AccountId>9</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Benjamin Keller</DisplayName>
+        <AccountId>1227</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Bahtiyar Kurt</DisplayName>
+        <AccountId>206</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Stefano Pistolese</DisplayName>
+        <AccountId>772</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D06A8A7-AAD0-46D5-9E3E-4D298B186157}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E36ED78C-029F-4A50-B3B7-CA985A738900}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5510,5 +5510,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E36ED78C-029F-4A50-B3B7-CA985A738900}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D06A8A7-AAD0-46D5-9E3E-4D298B186157}"/>
 </file>
--- a/01_Input/00_CO Validation/Bangladesh - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Bangladesh - Energy Projects.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28908"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UNDP-BD\Energy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/UNDPSustainableEnergyHub/Shared Documents/General/0. CURRENT FOLDER - Sustainable Energy Hub/05. Accounting for Progress to 500M/7. CO Validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="656" documentId="13_ncr:1_{F9E229CD-093B-4957-8526-AA7B64B04BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE47DFBB-AFFD-4ADD-986A-E01736B1750E}"/>
+  <xr:revisionPtr revIDLastSave="753" documentId="13_ncr:1_{F9E229CD-093B-4957-8526-AA7B64B04BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{763B6DAF-DF7C-402B-8A56-F53B0409DE42}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects (3)" sheetId="4" r:id="rId1"/>
-    <sheet name="Projects (2)" sheetId="3" r:id="rId2"/>
-    <sheet name="Projects" sheetId="1" r:id="rId3"/>
+    <sheet name="Projects (2)" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="Projects" sheetId="1" state="hidden" r:id="rId3"/>
     <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -41,12 +41,21 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={33AAE0C7-20DB-431D-B68F-2AE92B1E54FA}</author>
     <author>tc={19BDA1B9-E07E-4FD8-9A58-298F2E5F5765}</author>
     <author>tc={59D014D4-747A-4DE4-96E6-5AA8FEA984BB}</author>
     <author>tc={E1032D12-67C6-4765-8703-4600D0039D02}</author>
   </authors>
   <commentList>
-    <comment ref="A5" authorId="0" shapeId="0" xr:uid="{19BDA1B9-E07E-4FD8-9A58-298F2E5F5765}">
+    <comment ref="H4" authorId="0" shapeId="0" xr:uid="{33AAE0C7-20DB-431D-B68F-2AE92B1E54FA}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Instead of using ODP ton, I used ton CO2 eq based on their information</t>
+      </text>
+    </comment>
+    <comment ref="A5" authorId="1" shapeId="0" xr:uid="{19BDA1B9-E07E-4FD8-9A58-298F2E5F5765}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -54,7 +63,7 @@
     There is no such ID on the website</t>
       </text>
     </comment>
-    <comment ref="H14" authorId="1" shapeId="0" xr:uid="{59D014D4-747A-4DE4-96E6-5AA8FEA984BB}">
+    <comment ref="H15" authorId="2" shapeId="0" xr:uid="{59D014D4-747A-4DE4-96E6-5AA8FEA984BB}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -62,7 +71,7 @@
     Instead of using ODP ton, I used ton CO2 eq based on their information</t>
       </text>
     </comment>
-    <comment ref="A18" authorId="2" shapeId="0" xr:uid="{E1032D12-67C6-4765-8703-4600D0039D02}">
+    <comment ref="A19" authorId="3" shapeId="0" xr:uid="{E1032D12-67C6-4765-8703-4600D0039D02}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -75,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="256">
   <si>
     <t>Project ID</t>
   </si>
@@ -152,18 +161,50 @@
     <t>Energy (MW added)</t>
   </si>
   <si>
-    <t>No. of waste to energy facilities, rooftop PV, energy efficiency in building, etc</t>
-  </si>
-  <si>
-    <t>The project addresses the development challenge of increased negative economic and environmental impacts from fossil use and other non-sustainable practices in urban areas by enabling low-carbon interventions and investments in energy-efficiency (EE) and renewable energy (RE) in buildings and built environment and to support urban development in Bangladesh. 
-GHG emission reduction of 1.573 million tons of tCO2 (lifetime) resulting from EE, RE and W2E interventions (Direct) and 4.718 million tons of CO2 as consequential (indirect) emission reduction after the project’s end. About 600 Kw of energy generation is expected.
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">The project addresses the development challenge of increased negative economic and environmental impacts from fossil use and other non-sustainable practices in urban areas by enabling low-carbon interventions and investments in energy-efficiency (EE) and renewable energy (RE) in buildings and built environment and to support urban development in Bangladesh. 
+GHG emission reduction of 1.573 million tons of tCO2 (lifetime) resulting from EE, RE and W2E interventions (Direct) and 4.718 million tons of CO2 as consequential (indirect) emission reduction after the project’s end. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>About 600 Kw of energy generation is expecte</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">d.
 1 Bangladesh Low-Carbon Cities Network established ; Database on energy performance on commercial building established at SREDA;BNBC revised with EE adopted 
 2 waste to energy
 3 rooftop PV (public)
 10 rooftop PV (private)
 6 energy effociency in buildings(public)
 24 energy efficiency in buildings(private)
-On comment column: Expected to generate 1MW of energy</t>
+On comment column: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Expected to generate 1MW of energy</t>
+    </r>
   </si>
   <si>
     <t>GEF</t>
@@ -181,6 +222,11 @@
     <t>No. of low carbon policy, guideline and standard</t>
   </si>
   <si>
+    <t xml:space="preserve">2 Policies/regulatory frameworks:               (1) GHG inventory system adopted in Dhaka &amp; Chittagong City  
+(2) Dhaka &amp; Chittagong City have formulated investment plans for LCUD investments and measures
+</t>
+  </si>
+  <si>
     <t>Renewable Energy</t>
   </si>
   <si>
@@ -196,6 +242,9 @@
     <t>GHG Emission Reduction target in updated NDC</t>
   </si>
   <si>
+    <t>1.57 M Ton CO2eq</t>
+  </si>
+  <si>
     <t>116395</t>
   </si>
   <si>
@@ -208,15 +257,18 @@
     <t>Number of people benefiting from the development of EV ecosystem</t>
   </si>
   <si>
-    <t>This Project is to reduce GHG emissions with EV ecosystem development that promote environmentally friendly, energy-efficient, low-carbon transport and urban systems in Bangladesh with an enhanced policy-regulatory institutional framework with appropriate regulations for EVs and EV charging stations, accompanied by tailored capacity-building and awareness-raising efforts
+    <t xml:space="preserve">This Project is to reduce GHG emissions with EV ecosystem development that promote environmentally friendly, energy-efficient, low-carbon transport and urban systems in Bangladesh with an enhanced policy-regulatory institutional framework with appropriate regulations for EVs and EV charging stations, accompanied by tailored capacity-building and awareness-raising efforts
 Total no. of project beneficiaries are 672,600 that includes passengers of e-bus, 2-3-4 wheelers, technicians, govt staffs, private sectors etc.
 Assessment of Regulatory Framework and Market development for EV and EVCS, Recycling and Disposal of Batteries with strategy for environmentally sound manufacturing of EV and EV Components;Preparation of PPP business models for local charging stations and installation of hybrid grid-solar charging stations as well as, Battery recycling and reuse in Bangladesh
 100 persons will be trained on operation and maintenance of charging infrastructure (e-Buses and 2-3-wheeler station; 100 persons will be trained on environmentally sound and safe handling and recycling of batteries and verification
 Installation of 4 Charging Station (EV Charger, 300-500 kW) for e-Buses; Installation of 3 Solar Hybrid (80 kW; 25 to 30 kW from Solar) for 2-3-4 Wheelers; 
-On comment column: It is expected that 100,000 people will be benefitted</t>
+</t>
   </si>
   <si>
     <t xml:space="preserve">GHG Emission Reduction target </t>
+  </si>
+  <si>
+    <t>oo</t>
   </si>
   <si>
     <t>Capacity Building Training</t>
@@ -231,9 +283,6 @@
   </si>
   <si>
     <t>https://open.undp.org/projects/00093848</t>
-  </si>
-  <si>
-    <t>Number of nano-grids installed and operational.</t>
   </si>
   <si>
     <t>Nano-grid will cover 20-25 households
@@ -251,13 +300,7 @@
     <t>Agriculture and Food System</t>
   </si>
   <si>
-    <t xml:space="preserve">Hectares of agricultural land irrigated through solar irrigation pumps; </t>
-  </si>
-  <si>
     <t>Install solar irrigation pumps for community</t>
-  </si>
-  <si>
-    <t>Number of solar cold storage units installed and operational</t>
   </si>
   <si>
     <t>Install solar cold storage
@@ -273,7 +316,7 @@
     <t>https://open.undp.org/projects/00085984</t>
   </si>
   <si>
-    <t>Renewable energy capacity installed</t>
+    <t>Renewable energy capacity installed (MW)</t>
   </si>
   <si>
     <t>NA</t>
@@ -289,10 +332,7 @@
     <t>Water Services</t>
   </si>
   <si>
-    <t>Number of households benefiting from drinking water supply with electric solar powered motors</t>
-  </si>
-  <si>
-    <t>325 HH</t>
+    <t>Number of people benefiting from drinking water supply with electric solar powered motors</t>
   </si>
   <si>
     <t>54 community level drinking water supply with electric solar powered motors implemented by Union Parishads
@@ -300,6 +340,9 @@
 On comment column: About 325 household will be benefitted</t>
   </si>
   <si>
+    <t>Renewable energy capacity installed</t>
+  </si>
+  <si>
     <t>7 community level rooftop solar home systems  implemented by Union Parishads
 Budget is updated
 On comment column: It is expected that about 350KW energy will be generated</t>
@@ -317,6 +360,9 @@
     <t>GHG emission reductions (ton CO2eq)</t>
   </si>
   <si>
+    <t>1.73 M Ton CO2eq</t>
+  </si>
+  <si>
     <t>The project’s ultimate goal is to implement structural changes in RAC manufacturing and servicing sectors for cleaner production and contribute to the quality of people's lives, through the protection of the ozone layer and reduction in direct and indirect emissions. This project will phase-out 310.78 kg HCFC-22 equivalent to 17.09 ODP tons, which is 66% of Bangladesh´s consumption of HCFCs in RAC manufacturing sector, contributing to the reduction target for 2025.
 Baseline: Consumption of ODS 47.22 ODP ton</t>
   </si>
@@ -359,9 +405,13 @@
     <t>Number of low carbon policy and strategy</t>
   </si>
   <si>
-    <t xml:space="preserve">Enhanced transparency framework and data transparency system for Paris agreement
-Update emission reduction target for non-energy sector
-National strategy and investment plan for achieving NET ZERO </t>
+    <t xml:space="preserve">Policy Recommendation on following 5 points:
+1.	Climate finance strategy &amp; NDC investment plan
+2.	Roadmap for Net Zero strategies
+3.	Scoping study on adopting national circular economy strategy
+4.	Roadmap on National Hydrogen Stategy
+5.	Gender responsive NDC implementation plan
+ </t>
   </si>
   <si>
     <t xml:space="preserve">Global project
@@ -391,9 +441,6 @@
     <t>Number of households using improved cooking  stove</t>
   </si>
   <si>
-    <t>5000 HH</t>
-  </si>
-  <si>
     <t>local Villages of the CHT area faces serious health related problems due to high GHG gas emitting cooking stoves that are also fuel inefficient. A2I has been working with local innovators to develop energy efficient fuel stoves that are also environmentally friendly for the residents of that area.
 15-25% of households using improved cooking stove
 On comment column: About 5,000 Household got the benefits</t>
@@ -448,7 +495,7 @@
     <t>Education Services</t>
   </si>
   <si>
-    <t>No. of schools that are using the Multimedia Classroom</t>
+    <t>No. of students that are using the Multimedia Classroom</t>
   </si>
   <si>
     <t>As we progress through the generations, Technological advancement is happening at an exponential rate. To fully support our youth, technological advancements are also essential in the education sector. On top of that the Bangladeshi Government has taken the initiative to engulf the education stream of Bangladesh under one digital format. To accomodate this initiative, we developed a highly efficient Multimedia Classroom system that is completely powered through solar energy. With this innovation, we can empower our local youth in rural areas to recieve the same education as urban areas.
@@ -507,6 +554,9 @@
 24 energy efficiency in buildings(private)</t>
   </si>
   <si>
+    <t>No. of waste to energy facilities, rooftop PV, energy efficiency in building, etc</t>
+  </si>
+  <si>
     <t xml:space="preserve">The project addresses the development challenge of increased negative economic and environmental impacts from fossil use and other non-sustainable practices in urban areas by enabling low-carbon interventions and investments in energy-efficiency (EE) and renewable energy (RE) in buildings and built environment and to support urban development in Bangladesh. 
 GHG emission reduction of 1.573 million tons of tCO2 (lifetime) resulting from EE, RE and W2E interventions (Direct) and 4.718 million tons of CO2 as consequential (indirect) emission reduction after the project’s end. About 600 Kw of energy generation is expected.
 1 Bangladesh Low-Carbon Cities Network established ; Database on energy performance on commercial building established at SREDA;BNBC revised with EE adopted </t>
@@ -557,6 +607,9 @@
 300 to 450 households </t>
   </si>
   <si>
+    <t>Number of nano-grids installed and operational.</t>
+  </si>
+  <si>
     <t>Nano-grid will cover 20-25 households</t>
   </si>
   <si>
@@ -564,6 +617,12 @@
   </si>
   <si>
     <t>Agricultural Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hectares of agricultural land irrigated through solar irrigation pumps; </t>
+  </si>
+  <si>
+    <t>Number of solar cold storage units installed and operational</t>
   </si>
   <si>
     <t>0093426</t>
@@ -678,6 +737,9 @@
     <t>US$1250000</t>
   </si>
   <si>
+    <t>No. of schools that are using the Multimedia Classroom</t>
+  </si>
+  <si>
     <t>As we progress through the generations, Technological advancement is happening at an exponential rate. To fully support our youth, technological advancements are also essential in the education sector. On top of that the Bangladeshi Government has taken the initiative to engulf the education stream of Bangladesh under one digital format. To accomodate this initiative, we developed a highly efficient Multimedia Classroom system that is completely powered through solar energy. With this innovation, we can empower our local youth in rural areas to recieve the same education as urban areas.</t>
   </si>
   <si>
@@ -785,6 +847,11 @@
   </si>
   <si>
     <t>US$ 5356014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enhanced transparency framework and data transparency system for Paris agreement
+Update emission reduction target for non-energy sector
+National strategy and investment plan for achieving NET ZERO </t>
   </si>
   <si>
     <t>Global project</t>
@@ -908,7 +975,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1022,8 +1089,14 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1040,6 +1113,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFCD5B4"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1293,7 +1378,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="257">
+  <cellXfs count="269">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1871,6 +1956,40 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2000,8 +2119,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2327,13 +2446,16 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="H4" dT="2023-09-14T12:31:30.86" personId="{CFBED7FB-5460-4899-87EB-EE1CA4BE3B26}" id="{33AAE0C7-20DB-431D-B68F-2AE92B1E54FA}">
+    <text>Instead of using ODP ton, I used ton CO2 eq based on their information</text>
+  </threadedComment>
   <threadedComment ref="A5" dT="2023-09-14T11:50:18.65" personId="{CFBED7FB-5460-4899-87EB-EE1CA4BE3B26}" id="{19BDA1B9-E07E-4FD8-9A58-298F2E5F5765}">
     <text>There is no such ID on the website</text>
   </threadedComment>
-  <threadedComment ref="H14" dT="2023-09-14T12:31:30.86" personId="{CFBED7FB-5460-4899-87EB-EE1CA4BE3B26}" id="{59D014D4-747A-4DE4-96E6-5AA8FEA984BB}">
+  <threadedComment ref="H15" dT="2023-09-14T12:31:30.86" personId="{CFBED7FB-5460-4899-87EB-EE1CA4BE3B26}" id="{59D014D4-747A-4DE4-96E6-5AA8FEA984BB}">
     <text>Instead of using ODP ton, I used ton CO2 eq based on their information</text>
   </threadedComment>
-  <threadedComment ref="A18" dT="2023-09-14T12:22:55.91" personId="{CFBED7FB-5460-4899-87EB-EE1CA4BE3B26}" id="{E1032D12-67C6-4765-8703-4600D0039D02}">
+  <threadedComment ref="A19" dT="2023-09-14T12:22:55.91" personId="{CFBED7FB-5460-4899-87EB-EE1CA4BE3B26}" id="{E1032D12-67C6-4765-8703-4600D0039D02}">
     <text>This ID on the website is different</text>
   </threadedComment>
 </ThreadedComments>
@@ -2341,7 +2463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D47B4E4F-0AFC-46D6-97E6-4C30BF9BA353}">
-  <dimension ref="A1:U24"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="128" bestFit="1" customWidth="1"/>
@@ -2368,7 +2490,7 @@
     <col min="22" max="16384" width="8.85546875" style="128"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="30.75">
+    <row r="1" spans="1:21" ht="30">
       <c r="A1" s="141" t="s">
         <v>0</v>
       </c>
@@ -2450,37 +2572,40 @@
         <v>24</v>
       </c>
       <c r="F2" s="69" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="141"/>
+      <c r="H2" s="209">
+        <f>600/1000</f>
+        <v>0.6</v>
+      </c>
+      <c r="I2" s="264" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="141"/>
-      <c r="H2" s="69">
-        <v>1</v>
-      </c>
-      <c r="I2" s="252" t="s">
+      <c r="J2" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="147" t="s">
+      <c r="K2" s="217">
+        <v>0.5</v>
+      </c>
+      <c r="L2" s="205" t="s">
         <v>27</v>
-      </c>
-      <c r="K2" s="63"/>
-      <c r="L2" s="205" t="s">
-        <v>28</v>
       </c>
       <c r="M2" s="72"/>
       <c r="N2" s="154" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O2" s="72"/>
       <c r="P2" s="72"/>
       <c r="Q2" s="72"/>
       <c r="R2" s="72"/>
       <c r="S2" s="68" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T2" s="72"/>
       <c r="U2" s="68"/>
     </row>
-    <row r="3" spans="1:21" ht="45.75">
+    <row r="3" spans="1:21" ht="106.5">
       <c r="A3" s="148"/>
       <c r="B3" s="149"/>
       <c r="C3" s="150"/>
@@ -2489,19 +2614,21 @@
         <v>19</v>
       </c>
       <c r="F3" s="69" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="141"/>
+      <c r="H3" s="219" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="141"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="210"/>
+      <c r="I3" s="222"/>
       <c r="J3" s="153"/>
       <c r="K3" s="199"/>
       <c r="L3" s="205" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M3" s="72"/>
       <c r="N3" s="154" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O3" s="72" t="s">
         <v>32</v>
@@ -2531,18 +2658,18 @@
         <v>36</v>
       </c>
       <c r="G4" s="141"/>
-      <c r="H4" s="69">
-        <v>1573000</v>
-      </c>
-      <c r="I4" s="210"/>
+      <c r="H4" s="216" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="222"/>
       <c r="J4" s="159"/>
       <c r="K4" s="199"/>
       <c r="L4" s="205" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M4" s="72"/>
       <c r="N4" s="154" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O4" s="72"/>
       <c r="P4" s="72"/>
@@ -2554,38 +2681,40 @@
     </row>
     <row r="5" spans="1:21" s="129" customFormat="1" ht="60.75">
       <c r="A5" s="160" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5" s="161" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C5" s="162"/>
       <c r="D5" s="163">
         <v>1788991</v>
       </c>
       <c r="E5" s="164" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F5" s="165" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G5" s="141"/>
-      <c r="H5" s="69">
-        <v>100000</v>
-      </c>
-      <c r="I5" s="209" t="s">
-        <v>41</v>
+      <c r="H5" s="209">
+        <v>672600</v>
+      </c>
+      <c r="I5" s="221" t="s">
+        <v>42</v>
       </c>
       <c r="J5" s="200" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" s="217">
+        <v>0.5</v>
+      </c>
+      <c r="L5" s="205" t="s">
         <v>27</v>
-      </c>
-      <c r="K5" s="63"/>
-      <c r="L5" s="205" t="s">
-        <v>28</v>
       </c>
       <c r="M5" s="72"/>
       <c r="N5" s="154" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O5" s="72"/>
       <c r="P5" s="72"/>
@@ -2604,23 +2733,23 @@
         <v>35</v>
       </c>
       <c r="F6" s="69" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G6" s="141">
         <v>0</v>
       </c>
-      <c r="H6" s="69">
-        <v>15660</v>
-      </c>
-      <c r="I6" s="210"/>
+      <c r="H6" s="209" t="s">
+        <v>44</v>
+      </c>
+      <c r="I6" s="222"/>
       <c r="J6" s="153"/>
       <c r="K6" s="199"/>
       <c r="L6" s="205" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M6" s="72"/>
       <c r="N6" s="154" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O6" s="72"/>
       <c r="P6" s="72"/>
@@ -2630,33 +2759,31 @@
       <c r="T6" s="72"/>
       <c r="U6" s="68"/>
     </row>
-    <row r="7" spans="1:21" ht="200.25" customHeight="1">
-      <c r="A7" s="169"/>
-      <c r="B7" s="170"/>
-      <c r="C7" s="170"/>
-      <c r="D7" s="171"/>
-      <c r="E7" s="172" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" s="173" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" s="141">
+    <row r="7" spans="1:21" ht="81" customHeight="1">
+      <c r="A7" s="210"/>
+      <c r="B7" s="211"/>
+      <c r="C7" s="211"/>
+      <c r="D7" s="211"/>
+      <c r="E7" s="213" t="str">
+        <f>'Beneficiary Categories'!A3</f>
+        <v>Energy (MW added)</v>
+      </c>
+      <c r="F7" s="214" t="str">
+        <f>'Beneficiary Categories'!B3</f>
+        <v>Number of MW installed capacity</v>
+      </c>
+      <c r="G7" s="215">
         <v>0</v>
       </c>
-      <c r="H7" s="69">
-        <v>200</v>
-      </c>
-      <c r="I7" s="210"/>
-      <c r="J7" s="159"/>
+      <c r="H7" s="209">
+        <v>0.03</v>
+      </c>
+      <c r="I7" s="222"/>
+      <c r="J7" s="153"/>
       <c r="K7" s="199"/>
-      <c r="L7" s="205" t="s">
-        <v>28</v>
-      </c>
+      <c r="L7" s="205"/>
       <c r="M7" s="72"/>
-      <c r="N7" s="154" t="s">
-        <v>29</v>
-      </c>
+      <c r="N7" s="154"/>
       <c r="O7" s="72"/>
       <c r="P7" s="72"/>
       <c r="Q7" s="72"/>
@@ -2665,120 +2792,120 @@
       <c r="T7" s="72"/>
       <c r="U7" s="68"/>
     </row>
-    <row r="8" spans="1:21" s="126" customFormat="1" ht="91.5">
-      <c r="A8" s="174">
-        <v>93848</v>
-      </c>
-      <c r="B8" s="175" t="s">
+    <row r="8" spans="1:21" ht="200.25" customHeight="1">
+      <c r="A8" s="169"/>
+      <c r="B8" s="170"/>
+      <c r="C8" s="170"/>
+      <c r="D8" s="171"/>
+      <c r="E8" s="212" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="206" t="s">
+      <c r="F8" s="173" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="146">
-        <v>9212322</v>
-      </c>
-      <c r="E8" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="69" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="69">
+      <c r="G8" s="141">
         <v>0</v>
       </c>
       <c r="H8" s="69">
-        <v>1</v>
-      </c>
-      <c r="I8" s="173" t="s">
-        <v>48</v>
-      </c>
-      <c r="J8" s="164" t="s">
-        <v>49</v>
-      </c>
-      <c r="K8" s="63"/>
+        <v>200</v>
+      </c>
+      <c r="I8" s="222"/>
+      <c r="J8" s="159"/>
+      <c r="K8" s="199"/>
       <c r="L8" s="205" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M8" s="72"/>
       <c r="N8" s="154" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="O8" s="72"/>
       <c r="P8" s="72"/>
       <c r="Q8" s="72"/>
       <c r="R8" s="72"/>
-      <c r="S8" s="68" t="s">
-        <v>30</v>
-      </c>
+      <c r="S8" s="68"/>
       <c r="T8" s="72"/>
       <c r="U8" s="68"/>
     </row>
-    <row r="9" spans="1:21" s="127" customFormat="1" ht="60.75">
-      <c r="A9" s="177"/>
-      <c r="B9" s="178"/>
-      <c r="C9" s="179"/>
-      <c r="D9" s="180"/>
-      <c r="E9" s="154" t="s">
-        <v>51</v>
+    <row r="9" spans="1:21" s="126" customFormat="1" ht="91.5">
+      <c r="A9" s="174">
+        <v>93848</v>
+      </c>
+      <c r="B9" s="175" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="206" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="146">
+        <v>9212322</v>
+      </c>
+      <c r="E9" s="69" t="s">
+        <v>24</v>
       </c>
       <c r="F9" s="69" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="G9" s="69">
         <v>0</v>
       </c>
-      <c r="H9" s="69">
-        <v>80</v>
-      </c>
-      <c r="I9" s="69" t="s">
-        <v>53</v>
-      </c>
-      <c r="J9" s="181"/>
-      <c r="K9" s="63"/>
+      <c r="H9" s="209">
+        <v>0.06</v>
+      </c>
+      <c r="I9" s="173" t="s">
+        <v>49</v>
+      </c>
+      <c r="J9" s="164" t="s">
+        <v>50</v>
+      </c>
+      <c r="K9" s="217">
+        <v>0.5</v>
+      </c>
       <c r="L9" s="205" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M9" s="72"/>
       <c r="N9" s="154" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O9" s="72"/>
       <c r="P9" s="72"/>
       <c r="Q9" s="72"/>
       <c r="R9" s="72"/>
-      <c r="S9" s="68"/>
+      <c r="S9" s="68" t="s">
+        <v>29</v>
+      </c>
       <c r="T9" s="72"/>
       <c r="U9" s="68"/>
     </row>
-    <row r="10" spans="1:21" s="127" customFormat="1" ht="45.75">
-      <c r="A10" s="182"/>
-      <c r="B10" s="183"/>
-      <c r="C10" s="184"/>
-      <c r="D10" s="185"/>
+    <row r="10" spans="1:21" s="127" customFormat="1" ht="30.75">
+      <c r="A10" s="177"/>
+      <c r="B10" s="178"/>
+      <c r="C10" s="179"/>
+      <c r="D10" s="180"/>
       <c r="E10" s="154" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F10" s="69" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="G10" s="69">
         <v>0</v>
       </c>
-      <c r="H10" s="69">
-        <v>2</v>
+      <c r="H10" s="209">
+        <v>0.15</v>
       </c>
       <c r="I10" s="69" t="s">
-        <v>55</v>
-      </c>
-      <c r="J10" s="186"/>
+        <v>53</v>
+      </c>
+      <c r="J10" s="181"/>
       <c r="K10" s="63"/>
       <c r="L10" s="205" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M10" s="72"/>
       <c r="N10" s="154" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O10" s="72"/>
       <c r="P10" s="72"/>
@@ -2788,210 +2915,210 @@
       <c r="T10" s="72"/>
       <c r="U10" s="68"/>
     </row>
-    <row r="11" spans="1:21" ht="78" customHeight="1">
-      <c r="A11" s="187" t="s">
-        <v>56</v>
-      </c>
-      <c r="B11" s="188" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" s="189" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" s="190">
-        <v>35200000</v>
-      </c>
-      <c r="E11" s="69" t="s">
+    <row r="11" spans="1:21" s="127" customFormat="1" ht="45.75">
+      <c r="A11" s="182"/>
+      <c r="B11" s="183"/>
+      <c r="C11" s="184"/>
+      <c r="D11" s="185"/>
+      <c r="E11" s="154" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="69" t="s">
-        <v>59</v>
-      </c>
-      <c r="G11" s="69" t="s">
-        <v>60</v>
-      </c>
-      <c r="H11" s="69">
-        <v>1.1200000000000001</v>
+      <c r="G11" s="69">
+        <v>0</v>
+      </c>
+      <c r="H11" s="209">
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="I11" s="69" t="s">
-        <v>61</v>
-      </c>
-      <c r="J11" s="69" t="s">
-        <v>62</v>
-      </c>
-      <c r="K11" s="69"/>
+        <v>54</v>
+      </c>
+      <c r="J11" s="186"/>
+      <c r="K11" s="63"/>
       <c r="L11" s="205" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M11" s="72"/>
       <c r="N11" s="154" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="O11" s="72"/>
       <c r="P11" s="72"/>
       <c r="Q11" s="72"/>
       <c r="R11" s="72"/>
-      <c r="S11" s="68" t="s">
-        <v>30</v>
-      </c>
+      <c r="S11" s="68"/>
       <c r="T11" s="72"/>
       <c r="U11" s="68"/>
     </row>
-    <row r="12" spans="1:21" ht="91.5">
-      <c r="A12" s="166"/>
-      <c r="B12" s="178"/>
-      <c r="C12" s="180"/>
-      <c r="D12" s="191">
-        <v>7000000</v>
+    <row r="12" spans="1:21" ht="78" customHeight="1">
+      <c r="A12" s="187" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="188" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="189" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="190">
+        <v>35200000</v>
       </c>
       <c r="E12" s="69" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="F12" s="69" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G12" s="69" t="s">
+        <v>59</v>
+      </c>
+      <c r="H12" s="69">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="I12" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="H12" s="69" t="s">
-        <v>65</v>
-      </c>
-      <c r="I12" s="69" t="s">
-        <v>66</v>
-      </c>
-      <c r="J12" s="181"/>
-      <c r="K12" s="69"/>
+      <c r="J12" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="K12" s="218">
+        <v>0.5</v>
+      </c>
       <c r="L12" s="205" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M12" s="72"/>
       <c r="N12" s="154" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O12" s="72"/>
       <c r="P12" s="72"/>
       <c r="Q12" s="72"/>
       <c r="R12" s="72"/>
-      <c r="S12" s="68"/>
+      <c r="S12" s="68" t="s">
+        <v>29</v>
+      </c>
       <c r="T12" s="72"/>
       <c r="U12" s="68"/>
     </row>
-    <row r="13" spans="1:21" ht="76.5">
-      <c r="A13" s="169"/>
-      <c r="B13" s="183"/>
-      <c r="C13" s="185"/>
+    <row r="13" spans="1:21" ht="91.5">
+      <c r="A13" s="166"/>
+      <c r="B13" s="178"/>
+      <c r="C13" s="180"/>
       <c r="D13" s="191">
-        <v>1300000</v>
+        <v>7000000</v>
       </c>
       <c r="E13" s="69" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="F13" s="69" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="69" t="s">
         <v>59</v>
       </c>
-      <c r="G13" s="69" t="s">
-        <v>60</v>
-      </c>
-      <c r="H13" s="69">
-        <v>0.35</v>
+      <c r="H13" s="209">
+        <v>1463</v>
       </c>
       <c r="I13" s="69" t="s">
-        <v>67</v>
-      </c>
-      <c r="J13" s="186"/>
+        <v>64</v>
+      </c>
+      <c r="J13" s="181"/>
       <c r="K13" s="69"/>
       <c r="L13" s="205" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M13" s="72"/>
       <c r="N13" s="154" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O13" s="72"/>
       <c r="P13" s="72"/>
       <c r="Q13" s="72"/>
       <c r="R13" s="72"/>
-      <c r="S13" s="68" t="s">
-        <v>30</v>
-      </c>
+      <c r="S13" s="68"/>
       <c r="T13" s="72"/>
       <c r="U13" s="68"/>
     </row>
-    <row r="14" spans="1:21" ht="106.5">
-      <c r="A14" s="164" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14" s="161" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="131" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" s="192">
-        <v>5356014</v>
-      </c>
-      <c r="E14" t="s">
-        <v>35</v>
+    <row r="14" spans="1:21" ht="75">
+      <c r="A14" s="169"/>
+      <c r="B14" s="183"/>
+      <c r="C14" s="185"/>
+      <c r="D14" s="191">
+        <v>1300000</v>
+      </c>
+      <c r="E14" s="69" t="s">
+        <v>24</v>
       </c>
       <c r="F14" s="69" t="s">
-        <v>71</v>
-      </c>
-      <c r="G14" s="192"/>
-      <c r="H14" s="192">
-        <v>1730798</v>
+        <v>65</v>
+      </c>
+      <c r="G14" s="69" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14" s="69">
+        <v>0.35</v>
       </c>
       <c r="I14" s="69" t="s">
-        <v>72</v>
-      </c>
-      <c r="J14" s="176" t="s">
-        <v>73</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="J14" s="186"/>
       <c r="K14" s="69"/>
       <c r="L14" s="205" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M14" s="72"/>
       <c r="N14" s="154" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O14" s="72"/>
       <c r="P14" s="72"/>
       <c r="Q14" s="72"/>
       <c r="R14" s="72"/>
-      <c r="S14" s="68"/>
+      <c r="S14" s="68" t="s">
+        <v>29</v>
+      </c>
       <c r="T14" s="72"/>
       <c r="U14" s="68"/>
     </row>
-    <row r="15" spans="1:21" ht="137.25">
-      <c r="A15" s="132"/>
-      <c r="B15" s="133"/>
-      <c r="C15" s="133"/>
-      <c r="D15" s="134"/>
-      <c r="E15" s="69" t="s">
-        <v>74</v>
+    <row r="15" spans="1:21" ht="106.5">
+      <c r="A15" s="164" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="161" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="131" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" s="192">
+        <v>5356014</v>
+      </c>
+      <c r="E15" t="s">
+        <v>35</v>
       </c>
       <c r="F15" s="69" t="s">
-        <v>75</v>
-      </c>
-      <c r="G15" s="192">
-        <v>30268</v>
-      </c>
-      <c r="H15" s="192">
-        <v>110000</v>
+        <v>70</v>
+      </c>
+      <c r="G15" s="192"/>
+      <c r="H15" s="216" t="s">
+        <v>71</v>
       </c>
       <c r="I15" s="69" t="s">
-        <v>76</v>
-      </c>
-      <c r="J15" s="193"/>
-      <c r="K15" s="194">
-        <v>0.4</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="J15" s="176" t="s">
+        <v>73</v>
+      </c>
+      <c r="K15" s="69"/>
       <c r="L15" s="205" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M15" s="72"/>
       <c r="N15" s="154" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O15" s="72"/>
       <c r="P15" s="72"/>
@@ -3001,32 +3128,36 @@
       <c r="T15" s="72"/>
       <c r="U15" s="68"/>
     </row>
-    <row r="16" spans="1:21" s="129" customFormat="1" ht="106.5">
-      <c r="A16" s="135"/>
-      <c r="B16" s="136"/>
-      <c r="C16" s="136"/>
-      <c r="D16" s="137"/>
+    <row r="16" spans="1:21" ht="135">
+      <c r="A16" s="132"/>
+      <c r="B16" s="133"/>
+      <c r="C16" s="133"/>
+      <c r="D16" s="134"/>
       <c r="E16" s="69" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F16" s="69" t="s">
-        <v>78</v>
-      </c>
-      <c r="G16" s="69"/>
+        <v>75</v>
+      </c>
+      <c r="G16" s="192">
+        <v>30268</v>
+      </c>
       <c r="H16" s="192">
-        <v>6</v>
+        <v>110000</v>
       </c>
       <c r="I16" s="69" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J16" s="193"/>
-      <c r="K16" s="69"/>
+      <c r="K16" s="194">
+        <v>0.4</v>
+      </c>
       <c r="L16" s="205" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M16" s="72"/>
       <c r="N16" s="154" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O16" s="72"/>
       <c r="P16" s="72"/>
@@ -3036,32 +3167,32 @@
       <c r="T16" s="72"/>
       <c r="U16" s="68"/>
     </row>
-    <row r="17" spans="1:21" ht="60.75">
-      <c r="A17" s="138"/>
-      <c r="B17" s="139"/>
-      <c r="C17" s="139"/>
-      <c r="D17" s="140"/>
+    <row r="17" spans="1:21" s="129" customFormat="1" ht="105">
+      <c r="A17" s="135"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="136"/>
+      <c r="D17" s="137"/>
       <c r="E17" s="69" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="F17" s="69" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G17" s="69"/>
-      <c r="H17" s="69">
-        <v>1220</v>
+      <c r="H17" s="192">
+        <v>6</v>
       </c>
       <c r="I17" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="J17" s="186"/>
+        <v>79</v>
+      </c>
+      <c r="J17" s="193"/>
       <c r="K17" s="69"/>
       <c r="L17" s="205" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M17" s="72"/>
       <c r="N17" s="154" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O17" s="72"/>
       <c r="P17" s="72"/>
@@ -3071,138 +3202,133 @@
       <c r="T17" s="72"/>
       <c r="U17" s="68"/>
     </row>
-    <row r="18" spans="1:21" ht="106.5">
-      <c r="A18" s="195" t="s">
-        <v>82</v>
-      </c>
-      <c r="B18" s="141" t="s">
-        <v>83</v>
-      </c>
-      <c r="C18" s="69"/>
-      <c r="D18" s="192">
-        <v>475000</v>
-      </c>
+    <row r="18" spans="1:21" ht="75">
+      <c r="A18" s="138"/>
+      <c r="B18" s="139"/>
+      <c r="C18" s="139"/>
+      <c r="D18" s="140"/>
       <c r="E18" s="69" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F18" s="69" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G18" s="69"/>
-      <c r="H18" s="69" t="s">
-        <v>85</v>
+      <c r="H18" s="69">
+        <v>1220</v>
       </c>
       <c r="I18" s="69" t="s">
-        <v>86</v>
-      </c>
-      <c r="J18" s="69" t="s">
-        <v>87</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="J18" s="186"/>
       <c r="K18" s="69"/>
       <c r="L18" s="205" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M18" s="72"/>
       <c r="N18" s="154" t="s">
-        <v>29</v>
-      </c>
-      <c r="O18" s="72" t="s">
-        <v>32</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="O18" s="72"/>
       <c r="P18" s="72"/>
-      <c r="Q18" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="R18" s="72" t="s">
-        <v>89</v>
-      </c>
+      <c r="Q18" s="72"/>
+      <c r="R18" s="72"/>
       <c r="S18" s="68"/>
-      <c r="T18" s="72" t="s">
-        <v>34</v>
-      </c>
+      <c r="T18" s="72"/>
       <c r="U18" s="68"/>
     </row>
-    <row r="19" spans="1:21" s="129" customFormat="1" ht="106.5">
-      <c r="A19" s="69">
-        <v>93849</v>
+    <row r="19" spans="1:21" ht="198">
+      <c r="A19" s="195" t="s">
+        <v>82</v>
       </c>
       <c r="B19" s="141" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" s="207" t="s">
-        <v>91</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="C19" s="69"/>
       <c r="D19" s="192">
-        <v>150000</v>
+        <v>475000</v>
       </c>
       <c r="E19" s="69" t="s">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="F19" s="69" t="s">
-        <v>93</v>
-      </c>
-      <c r="G19" s="69">
-        <v>0</v>
-      </c>
-      <c r="H19" s="69" t="s">
-        <v>94</v>
+        <v>84</v>
+      </c>
+      <c r="G19" s="69"/>
+      <c r="H19" s="219" t="s">
+        <v>85</v>
       </c>
       <c r="I19" s="69" t="s">
-        <v>95</v>
-      </c>
-      <c r="J19" s="172" t="s">
-        <v>96</v>
-      </c>
-      <c r="K19" s="69"/>
+        <v>86</v>
+      </c>
+      <c r="J19" s="69" t="s">
+        <v>87</v>
+      </c>
+      <c r="K19" s="218">
+        <v>0.5</v>
+      </c>
       <c r="L19" s="205" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M19" s="72"/>
       <c r="N19" s="154" t="s">
-        <v>29</v>
-      </c>
-      <c r="O19" s="72"/>
+        <v>28</v>
+      </c>
+      <c r="O19" s="72" t="s">
+        <v>32</v>
+      </c>
       <c r="P19" s="72"/>
-      <c r="Q19" s="72"/>
-      <c r="R19" s="72"/>
+      <c r="Q19" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="R19" s="72" t="s">
+        <v>89</v>
+      </c>
       <c r="S19" s="68"/>
-      <c r="T19" s="72"/>
+      <c r="T19" s="72" t="s">
+        <v>34</v>
+      </c>
       <c r="U19" s="68"/>
     </row>
-    <row r="20" spans="1:21" s="129" customFormat="1" ht="121.5">
-      <c r="A20" s="69"/>
-      <c r="B20" s="69" t="s">
-        <v>97</v>
-      </c>
-      <c r="C20" s="192"/>
+    <row r="20" spans="1:21" s="129" customFormat="1" ht="106.5">
+      <c r="A20" s="69">
+        <v>93849</v>
+      </c>
+      <c r="B20" s="141" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" s="207" t="s">
+        <v>91</v>
+      </c>
       <c r="D20" s="192">
-        <v>600000</v>
+        <v>150000</v>
       </c>
       <c r="E20" s="69" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="F20" s="69" t="s">
-        <v>98</v>
-      </c>
-      <c r="G20" s="194">
-        <v>0.7</v>
+        <v>93</v>
+      </c>
+      <c r="G20" s="69">
+        <v>0</v>
       </c>
       <c r="H20" s="69">
-        <v>5000</v>
+        <f>5000*4.5</f>
+        <v>22500</v>
       </c>
       <c r="I20" s="69" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="J20" s="172" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K20" s="69"/>
       <c r="L20" s="205" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M20" s="72"/>
       <c r="N20" s="154" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O20" s="72"/>
       <c r="P20" s="72"/>
@@ -3212,101 +3338,93 @@
       <c r="T20" s="72"/>
       <c r="U20" s="68"/>
     </row>
-    <row r="21" spans="1:21" s="129" customFormat="1" ht="91.5">
+    <row r="21" spans="1:21" s="129" customFormat="1" ht="120">
       <c r="A21" s="69"/>
       <c r="B21" s="69" t="s">
-        <v>101</v>
-      </c>
-      <c r="C21" s="69"/>
+        <v>96</v>
+      </c>
+      <c r="C21" s="192"/>
       <c r="D21" s="192">
-        <v>300000</v>
+        <v>600000</v>
       </c>
       <c r="E21" s="69" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="F21" s="69" t="s">
-        <v>102</v>
-      </c>
-      <c r="G21" s="69">
-        <v>0</v>
+        <v>97</v>
+      </c>
+      <c r="G21" s="194">
+        <v>0.7</v>
       </c>
       <c r="H21" s="69">
-        <v>1</v>
+        <v>5000</v>
       </c>
       <c r="I21" s="69" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="J21" s="172" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K21" s="69"/>
       <c r="L21" s="205" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M21" s="72"/>
       <c r="N21" s="154" t="s">
-        <v>29</v>
-      </c>
-      <c r="O21" s="72" t="s">
-        <v>32</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="O21" s="72"/>
       <c r="P21" s="72"/>
-      <c r="Q21" s="72" t="s">
-        <v>104</v>
-      </c>
-      <c r="R21" s="72" t="s">
-        <v>105</v>
-      </c>
+      <c r="Q21" s="72"/>
+      <c r="R21" s="72"/>
       <c r="S21" s="68"/>
-      <c r="T21" s="72" t="s">
-        <v>34</v>
-      </c>
+      <c r="T21" s="72"/>
       <c r="U21" s="68"/>
     </row>
-    <row r="22" spans="1:21" ht="144" customHeight="1">
+    <row r="22" spans="1:21" s="129" customFormat="1" ht="90">
       <c r="A22" s="69"/>
       <c r="B22" s="69" t="s">
-        <v>106</v>
-      </c>
-      <c r="C22" s="192"/>
-      <c r="D22" s="196">
-        <v>160000</v>
+        <v>100</v>
+      </c>
+      <c r="C22" s="69"/>
+      <c r="D22" s="192">
+        <v>300000</v>
       </c>
       <c r="E22" s="69" t="s">
         <v>19</v>
       </c>
       <c r="F22" s="69" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G22" s="69">
+        <v>0</v>
+      </c>
+      <c r="H22" s="69">
         <v>1</v>
       </c>
-      <c r="H22" s="69">
-        <v>3</v>
-      </c>
       <c r="I22" s="69" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="J22" s="172" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K22" s="69"/>
       <c r="L22" s="205" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M22" s="72"/>
       <c r="N22" s="154" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O22" s="72" t="s">
-        <v>109</v>
+        <v>32</v>
       </c>
       <c r="P22" s="72"/>
       <c r="Q22" s="72" t="s">
-        <v>33</v>
+        <v>103</v>
       </c>
       <c r="R22" s="72" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="S22" s="68"/>
       <c r="T22" s="72" t="s">
@@ -3314,144 +3432,197 @@
       </c>
       <c r="U22" s="68"/>
     </row>
-    <row r="23" spans="1:21" s="129" customFormat="1" ht="121.5">
+    <row r="23" spans="1:21" ht="144" customHeight="1">
       <c r="A23" s="69"/>
       <c r="B23" s="69" t="s">
-        <v>110</v>
-      </c>
-      <c r="C23" s="130"/>
+        <v>105</v>
+      </c>
+      <c r="C23" s="192"/>
       <c r="D23" s="196">
-        <v>1250000</v>
+        <v>160000</v>
       </c>
       <c r="E23" s="69" t="s">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="F23" s="69" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="G23" s="69">
-        <v>326</v>
+        <v>1</v>
       </c>
       <c r="H23" s="69">
-        <v>2000</v>
+        <v>3</v>
       </c>
       <c r="I23" s="69" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="J23" s="172" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K23" s="69"/>
       <c r="L23" s="205" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M23" s="72"/>
       <c r="N23" s="154" t="s">
-        <v>29</v>
-      </c>
-      <c r="O23" s="72"/>
+        <v>28</v>
+      </c>
+      <c r="O23" s="72" t="s">
+        <v>108</v>
+      </c>
       <c r="P23" s="72"/>
-      <c r="Q23" s="72"/>
-      <c r="R23" s="72"/>
+      <c r="Q23" s="72" t="s">
+        <v>33</v>
+      </c>
+      <c r="R23" s="72" t="s">
+        <v>89</v>
+      </c>
       <c r="S23" s="68"/>
-      <c r="T23" s="72"/>
+      <c r="T23" s="72" t="s">
+        <v>34</v>
+      </c>
       <c r="U23" s="68"/>
     </row>
-    <row r="24" spans="1:21" ht="275.25">
-      <c r="A24" s="69">
-        <v>105918</v>
-      </c>
+    <row r="24" spans="1:21" s="129" customFormat="1" ht="121.5">
+      <c r="A24" s="69"/>
       <c r="B24" s="69" t="s">
-        <v>114</v>
-      </c>
-      <c r="C24" s="208" t="s">
-        <v>115</v>
-      </c>
-      <c r="D24" s="192">
-        <v>489000</v>
+        <v>109</v>
+      </c>
+      <c r="C24" s="130"/>
+      <c r="D24" s="196">
+        <v>1250000</v>
       </c>
       <c r="E24" s="69" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="F24" s="69" t="s">
-        <v>116</v>
-      </c>
-      <c r="G24" s="69" t="s">
-        <v>117</v>
-      </c>
-      <c r="H24" s="69"/>
+        <v>111</v>
+      </c>
+      <c r="G24" s="69">
+        <v>326</v>
+      </c>
+      <c r="H24" s="69">
+        <v>2000</v>
+      </c>
       <c r="I24" s="69" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="J24" s="172" t="s">
-        <v>27</v>
+        <v>99</v>
       </c>
       <c r="K24" s="69"/>
       <c r="L24" s="205" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M24" s="72"/>
       <c r="N24" s="154" t="s">
-        <v>29</v>
-      </c>
-      <c r="O24" s="72" t="s">
+        <v>28</v>
+      </c>
+      <c r="O24" s="72"/>
+      <c r="P24" s="72"/>
+      <c r="Q24" s="72"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="68"/>
+      <c r="T24" s="72"/>
+      <c r="U24" s="68"/>
+    </row>
+    <row r="25" spans="1:21" ht="275.25">
+      <c r="A25" s="69">
+        <v>105918</v>
+      </c>
+      <c r="B25" s="69" t="s">
+        <v>113</v>
+      </c>
+      <c r="C25" s="208" t="s">
+        <v>114</v>
+      </c>
+      <c r="D25" s="192">
+        <v>489000</v>
+      </c>
+      <c r="E25" s="69" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" s="220" t="s">
+        <v>115</v>
+      </c>
+      <c r="G25" s="220" t="s">
+        <v>116</v>
+      </c>
+      <c r="H25" s="69"/>
+      <c r="I25" s="69" t="s">
+        <v>117</v>
+      </c>
+      <c r="J25" s="172" t="s">
+        <v>26</v>
+      </c>
+      <c r="K25" s="218">
+        <v>0.5</v>
+      </c>
+      <c r="L25" s="205" t="s">
+        <v>27</v>
+      </c>
+      <c r="M25" s="72"/>
+      <c r="N25" s="154" t="s">
+        <v>28</v>
+      </c>
+      <c r="O25" s="72" t="s">
         <v>32</v>
       </c>
-      <c r="P24" s="72"/>
-      <c r="Q24" s="72" t="s">
+      <c r="P25" s="72"/>
+      <c r="Q25" s="72" t="s">
         <v>88</v>
       </c>
-      <c r="R24" s="72" t="s">
+      <c r="R25" s="72" t="s">
         <v>89</v>
       </c>
-      <c r="S24" s="68"/>
-      <c r="T24" s="72" t="s">
+      <c r="S25" s="68"/>
+      <c r="T25" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="U24" s="68"/>
+      <c r="U25" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="I5:I7"/>
+    <mergeCell ref="I5:I8"/>
     <mergeCell ref="I2:I4"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <dataValidations count="9">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q24" xr:uid="{50BC6D76-B0DE-424B-A0F5-F3C85CF484BB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q25" xr:uid="{50BC6D76-B0DE-424B-A0F5-F3C85CF484BB}">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P24" xr:uid="{62483C04-38BE-4F6D-B81D-E1F3BC42C93A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P25" xr:uid="{62483C04-38BE-4F6D-B81D-E1F3BC42C93A}">
       <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N24" xr:uid="{08FCFAEA-6806-46C6-962B-8245A865ECF4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N25" xr:uid="{08FCFAEA-6806-46C6-962B-8245A865ECF4}">
       <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O24" xr:uid="{CBE1B3B5-5FA1-4DA6-AA75-48A7E29C1A64}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O25" xr:uid="{CBE1B3B5-5FA1-4DA6-AA75-48A7E29C1A64}">
       <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy, Overall"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L24" xr:uid="{07A695C6-F7C4-4590-B736-45B3A80CC5E9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L25" xr:uid="{07A695C6-F7C4-4590-B736-45B3A80CC5E9}">
       <formula1>"Non-VF, VF"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M24" xr:uid="{25115A9B-B357-42FD-B1AC-232114B311C3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M25" xr:uid="{25115A9B-B357-42FD-B1AC-232114B311C3}">
       <formula1>"Finance, Gender, Efficiency, Just, Health"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T24" xr:uid="{2F04C272-1E8B-47DF-A0A3-277723DA9DED}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T25" xr:uid="{2F04C272-1E8B-47DF-A0A3-277723DA9DED}">
       <formula1>"National, Regional, City, Community"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S24" xr:uid="{32854381-4DCD-4E29-9E8B-45CF8418AA7A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S25" xr:uid="{32854381-4DCD-4E29-9E8B-45CF8418AA7A}">
       <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Other, Unknown"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R24" xr:uid="{064C5753-C5FB-40A5-96E4-2253C486FFE0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R25" xr:uid="{064C5753-C5FB-40A5-96E4-2253C486FFE0}">
       <formula1>"Electricity Access, Energy Efficiency, Renewable Energy, Infrastructure,  Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid, Research &amp; Innovation, Grant &amp; Investment"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C14" r:id="rId1" display="HPMP II (AC Unit)" xr:uid="{ACE86EB8-CF9E-4242-B2CD-7BAFAD17151A}"/>
+    <hyperlink ref="C15" r:id="rId1" display="HPMP II (AC Unit)" xr:uid="{ACE86EB8-CF9E-4242-B2CD-7BAFAD17151A}"/>
     <hyperlink ref="C2:C4" r:id="rId2" display="https://open.undp.org/projects/00117898" xr:uid="{3277A9E4-BD92-4AFB-8573-4567E8BDAFA0}"/>
-    <hyperlink ref="C11" r:id="rId3" xr:uid="{74EF9CA8-7A6E-4FA1-B9EF-6E1DC13A2A73}"/>
-    <hyperlink ref="C8" r:id="rId4" xr:uid="{FE483E24-F0BE-4EAB-8EB4-866373D3F2A8}"/>
-    <hyperlink ref="C19" r:id="rId5" xr:uid="{9D78E2DE-2D6F-4D16-8261-3E6C23E43D87}"/>
-    <hyperlink ref="C24" r:id="rId6" xr:uid="{DEA73ED1-834B-41E0-B669-B5199BF88860}"/>
+    <hyperlink ref="C12" r:id="rId3" xr:uid="{74EF9CA8-7A6E-4FA1-B9EF-6E1DC13A2A73}"/>
+    <hyperlink ref="C9" r:id="rId4" xr:uid="{FE483E24-F0BE-4EAB-8EB4-866373D3F2A8}"/>
+    <hyperlink ref="C20" r:id="rId5" xr:uid="{9D78E2DE-2D6F-4D16-8261-3E6C23E43D87}"/>
+    <hyperlink ref="C25" r:id="rId6" xr:uid="{DEA73ED1-834B-41E0-B669-B5199BF88860}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3463,13 +3634,13 @@
           <x14:formula1>
             <xm:f>'Beneficiary Categories'!$A$2:$A$16</xm:f>
           </x14:formula1>
-          <xm:sqref>F8:F10 F2</xm:sqref>
+          <xm:sqref>F9:F11 F2</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4E9ADF49-5F72-4534-9020-A6DCAA2AA448}">
           <x14:formula1>
             <xm:f>'Beneficiary Categories'!$A$2:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E24</xm:sqref>
+          <xm:sqref>E2:E25</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3507,7 +3678,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="82" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E1" s="60" t="s">
         <v>4</v>
@@ -3531,71 +3702,71 @@
         <v>10</v>
       </c>
       <c r="L1" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="M1" s="117" t="s">
         <v>120</v>
       </c>
-      <c r="M1" s="117" t="s">
+    </row>
+    <row r="2" spans="1:13" s="92" customFormat="1" ht="91.5" customHeight="1">
+      <c r="A2" s="243" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" s="92" customFormat="1" ht="91.5" customHeight="1">
-      <c r="A2" s="231" t="s">
+      <c r="B2" s="246" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="236"/>
+      <c r="D2" s="239" t="s">
         <v>122</v>
-      </c>
-      <c r="B2" s="234" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="224"/>
-      <c r="D2" s="227" t="s">
-        <v>123</v>
       </c>
       <c r="E2" s="88" t="s">
         <v>24</v>
       </c>
       <c r="F2" s="89"/>
       <c r="G2" s="90" t="s">
+        <v>123</v>
+      </c>
+      <c r="H2" s="91" t="s">
         <v>124</v>
       </c>
-      <c r="H2" s="91" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" s="253" t="s">
+      <c r="I2" s="265" t="s">
         <v>125</v>
       </c>
-      <c r="J2" s="211" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="216"/>
-      <c r="L2" s="213" t="s">
+      <c r="J2" s="223" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" s="228"/>
+      <c r="L2" s="225" t="s">
         <v>126</v>
       </c>
       <c r="M2" s="118" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="45.75">
-      <c r="A3" s="232"/>
-      <c r="B3" s="235"/>
-      <c r="C3" s="225"/>
-      <c r="D3" s="228"/>
+    <row r="3" spans="1:13" ht="45">
+      <c r="A3" s="244"/>
+      <c r="B3" s="247"/>
+      <c r="C3" s="237"/>
+      <c r="D3" s="240"/>
       <c r="E3" s="65" t="s">
         <v>128</v>
       </c>
       <c r="F3" s="66"/>
       <c r="G3" s="74"/>
       <c r="H3" s="64" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="221"/>
-      <c r="J3" s="212"/>
-      <c r="K3" s="217"/>
-      <c r="L3" s="214"/>
+        <v>30</v>
+      </c>
+      <c r="I3" s="233"/>
+      <c r="J3" s="224"/>
+      <c r="K3" s="229"/>
+      <c r="L3" s="226"/>
       <c r="M3" s="119"/>
     </row>
-    <row r="4" spans="1:13" ht="45.75">
-      <c r="A4" s="233"/>
-      <c r="B4" s="236"/>
-      <c r="C4" s="226"/>
-      <c r="D4" s="229"/>
+    <row r="4" spans="1:13" ht="45">
+      <c r="A4" s="245"/>
+      <c r="B4" s="248"/>
+      <c r="C4" s="238"/>
+      <c r="D4" s="241"/>
       <c r="E4" s="67" t="s">
         <v>129</v>
       </c>
@@ -3606,18 +3777,18 @@
       <c r="H4" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="222"/>
-      <c r="J4" s="212"/>
-      <c r="K4" s="217"/>
-      <c r="L4" s="214"/>
+      <c r="I4" s="234"/>
+      <c r="J4" s="224"/>
+      <c r="K4" s="229"/>
+      <c r="L4" s="226"/>
       <c r="M4" s="119"/>
     </row>
-    <row r="5" spans="1:13" s="92" customFormat="1" ht="76.5">
-      <c r="A5" s="237" t="s">
+    <row r="5" spans="1:13" s="92" customFormat="1" ht="75">
+      <c r="A5" s="249" t="s">
         <v>130</v>
       </c>
-      <c r="B5" s="220" t="s">
-        <v>38</v>
+      <c r="B5" s="232" t="s">
+        <v>39</v>
       </c>
       <c r="C5" s="89"/>
       <c r="D5" s="93" t="s">
@@ -3631,19 +3802,19 @@
         <v>133</v>
       </c>
       <c r="H5" s="89"/>
-      <c r="I5" s="223" t="s">
+      <c r="I5" s="235" t="s">
         <v>134</v>
       </c>
-      <c r="J5" s="212"/>
-      <c r="K5" s="217"/>
-      <c r="L5" s="214"/>
+      <c r="J5" s="224"/>
+      <c r="K5" s="229"/>
+      <c r="L5" s="226"/>
       <c r="M5" s="118" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="37.5" customHeight="1">
-      <c r="A6" s="237"/>
-      <c r="B6" s="220"/>
+      <c r="A6" s="249"/>
+      <c r="B6" s="232"/>
       <c r="C6" s="60"/>
       <c r="D6" s="66"/>
       <c r="E6" s="67" t="s">
@@ -3654,17 +3825,17 @@
         <v>15660</v>
       </c>
       <c r="H6" s="94" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" s="223"/>
-      <c r="J6" s="212"/>
-      <c r="K6" s="217"/>
-      <c r="L6" s="214"/>
+        <v>43</v>
+      </c>
+      <c r="I6" s="235"/>
+      <c r="J6" s="224"/>
+      <c r="K6" s="229"/>
+      <c r="L6" s="226"/>
       <c r="M6" s="119"/>
     </row>
     <row r="7" spans="1:13" ht="45" customHeight="1">
-      <c r="A7" s="237"/>
-      <c r="B7" s="220"/>
+      <c r="A7" s="249"/>
+      <c r="B7" s="232"/>
       <c r="C7" s="60"/>
       <c r="D7" s="66"/>
       <c r="E7" s="65" t="s">
@@ -3677,16 +3848,16 @@
       <c r="H7" s="95" t="s">
         <v>137</v>
       </c>
-      <c r="I7" s="223"/>
-      <c r="J7" s="212"/>
-      <c r="K7" s="217"/>
-      <c r="L7" s="214"/>
+      <c r="I7" s="235"/>
+      <c r="J7" s="224"/>
+      <c r="K7" s="229"/>
+      <c r="L7" s="226"/>
       <c r="M7" s="119"/>
     </row>
-    <row r="8" spans="1:13" s="99" customFormat="1" ht="45.75">
-      <c r="A8" s="219"/>
-      <c r="B8" s="220" t="s">
-        <v>45</v>
+    <row r="8" spans="1:13" s="99" customFormat="1" ht="45">
+      <c r="A8" s="231"/>
+      <c r="B8" s="232" t="s">
+        <v>47</v>
       </c>
       <c r="C8" s="88"/>
       <c r="D8" s="96" t="s">
@@ -3702,27 +3873,27 @@
         <v>139</v>
       </c>
       <c r="H8" s="88" t="s">
-        <v>47</v>
+        <v>140</v>
       </c>
       <c r="I8" s="98" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J8" s="88" t="s">
-        <v>49</v>
-      </c>
-      <c r="K8" s="217"/>
-      <c r="L8" s="214"/>
+        <v>50</v>
+      </c>
+      <c r="K8" s="229"/>
+      <c r="L8" s="226"/>
       <c r="M8" s="120" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" s="13" customFormat="1" ht="60.75">
-      <c r="A9" s="219"/>
-      <c r="B9" s="220"/>
+        <v>142</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" s="13" customFormat="1" ht="75">
+      <c r="A9" s="231"/>
+      <c r="B9" s="232"/>
       <c r="C9" s="63"/>
       <c r="D9" s="64"/>
       <c r="E9" s="63" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F9" s="69">
         <v>0</v>
@@ -3731,23 +3902,23 @@
         <v>80</v>
       </c>
       <c r="H9" s="63" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="I9" s="63" t="s">
         <v>53</v>
       </c>
       <c r="J9" s="63"/>
-      <c r="K9" s="217"/>
-      <c r="L9" s="214"/>
+      <c r="K9" s="229"/>
+      <c r="L9" s="226"/>
       <c r="M9" s="121"/>
     </row>
-    <row r="10" spans="1:13" s="13" customFormat="1" ht="76.5">
-      <c r="A10" s="219"/>
-      <c r="B10" s="220"/>
+    <row r="10" spans="1:13" s="13" customFormat="1" ht="75">
+      <c r="A10" s="231"/>
+      <c r="B10" s="232"/>
       <c r="C10" s="63"/>
       <c r="D10" s="64"/>
       <c r="E10" s="63" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F10" s="69">
         <v>0</v>
@@ -3756,138 +3927,138 @@
         <v>2</v>
       </c>
       <c r="H10" s="63" t="s">
+        <v>145</v>
+      </c>
+      <c r="I10" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="I10" s="63" t="s">
-        <v>55</v>
-      </c>
       <c r="J10" s="63"/>
-      <c r="K10" s="218"/>
-      <c r="L10" s="215"/>
+      <c r="K10" s="230"/>
+      <c r="L10" s="227"/>
       <c r="M10" s="121"/>
     </row>
-    <row r="11" spans="1:13" ht="183">
-      <c r="A11" s="230" t="s">
-        <v>143</v>
-      </c>
-      <c r="B11" s="220" t="s">
-        <v>144</v>
+    <row r="11" spans="1:13" ht="180">
+      <c r="A11" s="242" t="s">
+        <v>146</v>
+      </c>
+      <c r="B11" s="232" t="s">
+        <v>147</v>
       </c>
       <c r="C11" s="71"/>
       <c r="D11" s="85" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E11" s="63" t="s">
         <v>24</v>
       </c>
       <c r="F11" s="72" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G11" s="77">
         <v>1.1200000000000001</v>
       </c>
       <c r="H11" s="72" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I11" s="64" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J11" s="71" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K11" s="62"/>
       <c r="L11" s="62"/>
       <c r="M11" s="119"/>
     </row>
-    <row r="12" spans="1:13" s="92" customFormat="1" ht="106.5">
-      <c r="A12" s="230"/>
-      <c r="B12" s="220"/>
+    <row r="12" spans="1:13" s="92" customFormat="1" ht="105">
+      <c r="A12" s="242"/>
+      <c r="B12" s="232"/>
       <c r="C12" s="100"/>
       <c r="D12" s="101" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E12" s="100" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F12" s="102" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G12" s="103" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H12" s="102" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I12" s="104" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="J12" s="100" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K12" s="105"/>
       <c r="L12" s="105"/>
       <c r="M12" s="118" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" s="92" customFormat="1" ht="91.5">
-      <c r="A13" s="230"/>
-      <c r="B13" s="220"/>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" s="92" customFormat="1" ht="90">
+      <c r="A13" s="242"/>
+      <c r="B13" s="232"/>
       <c r="C13" s="100"/>
       <c r="D13" s="101" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E13" s="100" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F13" s="102" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G13" s="103" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H13" s="102" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I13" s="104" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="J13" s="100" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K13" s="105"/>
       <c r="L13" s="105"/>
       <c r="M13" s="118" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="321">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="315">
       <c r="A14" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" s="232" t="s">
         <v>68</v>
       </c>
-      <c r="B14" s="220" t="s">
+      <c r="C14" s="75" t="s">
         <v>69</v>
       </c>
-      <c r="C14" s="75" t="s">
-        <v>70</v>
-      </c>
       <c r="D14" s="84" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E14" s="77" t="s">
         <v>74</v>
       </c>
       <c r="F14" s="76" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G14" s="76">
         <v>17.09</v>
       </c>
       <c r="H14" s="74" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="I14" s="74" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J14" s="71" t="s">
         <v>73</v>
@@ -3896,14 +4067,14 @@
       <c r="L14" s="62"/>
       <c r="M14" s="119"/>
     </row>
-    <row r="15" spans="1:13" ht="305.25">
-      <c r="A15" s="223"/>
-      <c r="B15" s="220"/>
+    <row r="15" spans="1:13" ht="315">
+      <c r="A15" s="235"/>
+      <c r="B15" s="232"/>
       <c r="C15" s="75" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D15" s="84" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E15" s="77" t="s">
         <v>74</v>
@@ -3929,14 +4100,14 @@
       <c r="L15" s="62"/>
       <c r="M15" s="119"/>
     </row>
-    <row r="16" spans="1:13" s="92" customFormat="1" ht="167.25">
-      <c r="A16" s="223"/>
-      <c r="B16" s="220"/>
+    <row r="16" spans="1:13" s="92" customFormat="1" ht="195">
+      <c r="A16" s="235"/>
+      <c r="B16" s="232"/>
       <c r="C16" s="108" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D16" s="91" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E16" s="103" t="s">
         <v>77</v>
@@ -3944,7 +4115,7 @@
       <c r="F16" s="90"/>
       <c r="G16" s="109"/>
       <c r="I16" s="90" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="J16" s="110" t="s">
         <v>73</v>
@@ -3952,17 +4123,17 @@
       <c r="K16" s="105"/>
       <c r="L16" s="105"/>
       <c r="M16" s="122" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="106.5">
-      <c r="A17" s="223"/>
-      <c r="B17" s="220"/>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="105">
+      <c r="A17" s="235"/>
+      <c r="B17" s="232"/>
       <c r="C17" s="75" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D17" s="64" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E17" s="77" t="s">
         <v>136</v>
@@ -3984,16 +4155,16 @@
       <c r="L17" s="62"/>
       <c r="M17" s="119"/>
     </row>
-    <row r="18" spans="1:13" ht="167.25">
+    <row r="18" spans="1:13" ht="180">
       <c r="A18" s="78" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B18" s="79" t="s">
         <v>83</v>
       </c>
       <c r="C18" s="62"/>
       <c r="D18" s="83" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E18" s="80" t="s">
         <v>19</v>
@@ -4001,26 +4172,26 @@
       <c r="F18" s="73"/>
       <c r="G18" s="74"/>
       <c r="H18" s="80" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="I18" s="64" t="s">
         <v>86</v>
       </c>
       <c r="J18" s="68" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K18" s="62"/>
       <c r="L18" s="62"/>
       <c r="M18" s="119"/>
     </row>
-    <row r="19" spans="1:13" s="92" customFormat="1" ht="183">
+    <row r="19" spans="1:13" s="92" customFormat="1" ht="195">
       <c r="A19" s="105"/>
       <c r="B19" s="111" t="s">
         <v>90</v>
       </c>
       <c r="C19" s="112"/>
       <c r="D19" s="96" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E19" s="104" t="s">
         <v>92</v>
@@ -4029,62 +4200,62 @@
         <v>0</v>
       </c>
       <c r="G19" s="90" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H19" s="104" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I19" s="104" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="J19" s="114" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="K19" s="105"/>
       <c r="L19" s="105"/>
       <c r="M19" s="123" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" s="92" customFormat="1" ht="336">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" s="92" customFormat="1" ht="345">
       <c r="A20" s="105"/>
       <c r="B20" s="88" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C20" s="112"/>
       <c r="D20" s="96" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E20" s="104" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F20" s="113">
         <v>0.7</v>
       </c>
       <c r="G20" s="90"/>
       <c r="H20" s="104" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I20" s="104" t="s">
+        <v>176</v>
+      </c>
+      <c r="J20" s="114" t="s">
         <v>173</v>
-      </c>
-      <c r="J20" s="114" t="s">
-        <v>170</v>
       </c>
       <c r="K20" s="105"/>
       <c r="L20" s="105"/>
       <c r="M20" s="124" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" s="92" customFormat="1" ht="106.5">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" s="92" customFormat="1" ht="105">
       <c r="A21" s="62"/>
       <c r="B21" s="70" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C21" s="71"/>
       <c r="D21" s="84" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E21" s="70" t="s">
         <v>19</v>
@@ -4096,26 +4267,26 @@
         <v>1</v>
       </c>
       <c r="H21" s="70" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I21" s="70" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J21" s="87" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="K21" s="62"/>
       <c r="L21" s="62"/>
       <c r="M21" s="125"/>
     </row>
-    <row r="22" spans="1:13" ht="91.5">
+    <row r="22" spans="1:13" ht="90">
       <c r="A22" s="62"/>
       <c r="B22" s="70" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C22" s="81"/>
       <c r="D22" s="86" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E22" s="70" t="s">
         <v>19</v>
@@ -4127,29 +4298,29 @@
         <v>3</v>
       </c>
       <c r="H22" s="70" t="s">
+        <v>106</v>
+      </c>
+      <c r="I22" s="70" t="s">
         <v>107</v>
       </c>
-      <c r="I22" s="70" t="s">
-        <v>108</v>
-      </c>
       <c r="J22" s="87" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="K22" s="62"/>
       <c r="L22" s="62"/>
       <c r="M22" s="119"/>
     </row>
-    <row r="23" spans="1:13" s="92" customFormat="1" ht="381.75">
+    <row r="23" spans="1:13" s="92" customFormat="1" ht="405">
       <c r="A23" s="105"/>
       <c r="B23" s="104" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C23" s="115"/>
       <c r="D23" s="116" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E23" s="104" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F23" s="100">
         <v>326</v>
@@ -4158,46 +4329,46 @@
         <v>1000</v>
       </c>
       <c r="H23" s="104" t="s">
-        <v>112</v>
+        <v>182</v>
       </c>
       <c r="I23" s="104" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J23" s="114" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="K23" s="105"/>
       <c r="L23" s="105"/>
       <c r="M23" s="118" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="336">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="345">
       <c r="A24" s="77">
         <v>106912</v>
       </c>
       <c r="B24" s="64" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C24" s="77"/>
       <c r="D24" s="84" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E24" s="64" t="s">
         <v>128</v>
       </c>
       <c r="F24" s="64" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G24" s="74"/>
       <c r="H24" s="64" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I24" s="64" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J24" s="87" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K24" s="62"/>
       <c r="L24" s="67" t="s">
@@ -4252,7 +4423,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K26"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33" customWidth="1"/>
@@ -4266,7 +4437,7 @@
     <col min="11" max="11" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4277,7 +4448,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="59" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -4298,14 +4469,14 @@
         <v>9</v>
       </c>
       <c r="K1" s="39" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="105">
+      <c r="A2" s="258" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="91.5">
-      <c r="A2" s="246" t="s">
-        <v>122</v>
-      </c>
-      <c r="B2" s="241" t="s">
+      <c r="B2" s="253" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="1"/>
@@ -4316,44 +4487,44 @@
         <v>24</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>25</v>
+        <v>124</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="I2" s="238" t="s">
-        <v>183</v>
+        <v>123</v>
+      </c>
+      <c r="I2" s="250" t="s">
+        <v>187</v>
       </c>
       <c r="J2" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="238" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="76.5">
-      <c r="A3" s="247"/>
-      <c r="B3" s="242"/>
+        <v>26</v>
+      </c>
+      <c r="K2" s="250" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="75">
+      <c r="A3" s="259"/>
+      <c r="B3" s="254"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="17" t="s">
         <v>128</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="I3" s="239"/>
+        <v>189</v>
+      </c>
+      <c r="I3" s="251"/>
       <c r="J3" s="41"/>
-      <c r="K3" s="239"/>
-    </row>
-    <row r="4" spans="1:11" ht="60.75">
-      <c r="A4" s="248"/>
-      <c r="B4" s="243"/>
+      <c r="K3" s="251"/>
+    </row>
+    <row r="4" spans="1:11" ht="60">
+      <c r="A4" s="260"/>
+      <c r="B4" s="255"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="7" t="s">
@@ -4364,18 +4535,18 @@
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="I4" s="240"/>
+        <v>190</v>
+      </c>
+      <c r="I4" s="252"/>
       <c r="J4" s="42"/>
-      <c r="K4" s="240"/>
-    </row>
-    <row r="5" spans="1:11" ht="106.5">
-      <c r="A5" s="246" t="s">
+      <c r="K4" s="252"/>
+    </row>
+    <row r="5" spans="1:11" ht="105">
+      <c r="A5" s="258" t="s">
         <v>130</v>
       </c>
-      <c r="B5" s="241" t="s">
-        <v>38</v>
+      <c r="B5" s="253" t="s">
+        <v>39</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="8">
@@ -4387,21 +4558,21 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="I5" s="238" t="s">
-        <v>188</v>
+        <v>191</v>
+      </c>
+      <c r="I5" s="250" t="s">
+        <v>192</v>
       </c>
       <c r="J5" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5" s="238" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="45.75">
-      <c r="A6" s="247"/>
-      <c r="B6" s="242"/>
+        <v>26</v>
+      </c>
+      <c r="K5" s="250" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="45">
+      <c r="A6" s="259"/>
+      <c r="B6" s="254"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="7" t="s">
@@ -4410,54 +4581,54 @@
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="I6" s="239"/>
+        <v>194</v>
+      </c>
+      <c r="I6" s="251"/>
       <c r="J6" s="41"/>
-      <c r="K6" s="239"/>
-    </row>
-    <row r="7" spans="1:11" ht="106.5">
-      <c r="A7" s="247"/>
-      <c r="B7" s="242"/>
+      <c r="K6" s="251"/>
+    </row>
+    <row r="7" spans="1:11" ht="105">
+      <c r="A7" s="259"/>
+      <c r="B7" s="254"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="17" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="F7" s="9"/>
       <c r="G7" s="1"/>
       <c r="H7" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="I7" s="239"/>
+      <c r="I7" s="251"/>
       <c r="J7" s="42"/>
-      <c r="K7" s="240"/>
-    </row>
-    <row r="8" spans="1:11" ht="167.25">
-      <c r="A8" s="248"/>
-      <c r="B8" s="243"/>
+      <c r="K7" s="252"/>
+    </row>
+    <row r="8" spans="1:11" ht="180">
+      <c r="A8" s="260"/>
+      <c r="B8" s="255"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="7" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="I8" s="240"/>
+        <v>197</v>
+      </c>
+      <c r="I8" s="252"/>
       <c r="J8" s="55" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K8" s="56"/>
     </row>
-    <row r="9" spans="1:11" s="13" customFormat="1" ht="45.75">
-      <c r="A9" s="249" t="s">
-        <v>194</v>
-      </c>
-      <c r="B9" s="241" t="s">
-        <v>45</v>
+    <row r="9" spans="1:11" s="13" customFormat="1" ht="45">
+      <c r="A9" s="261" t="s">
+        <v>198</v>
+      </c>
+      <c r="B9" s="253" t="s">
+        <v>47</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="10">
@@ -4467,7 +4638,7 @@
         <v>24</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>47</v>
+        <v>140</v>
       </c>
       <c r="G9" s="11">
         <v>0</v>
@@ -4477,28 +4648,28 @@
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="44" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K9" s="47" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" s="13" customFormat="1" ht="60.75">
-      <c r="A10" s="250"/>
-      <c r="B10" s="242"/>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="13" customFormat="1" ht="75">
+      <c r="A10" s="262"/>
+      <c r="B10" s="254"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="G10" s="11">
         <v>0</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>53</v>
@@ -4506,120 +4677,120 @@
       <c r="J10" s="45"/>
       <c r="K10" s="48"/>
     </row>
-    <row r="11" spans="1:11" s="13" customFormat="1" ht="45.75">
-      <c r="A11" s="251"/>
-      <c r="B11" s="243"/>
+    <row r="11" spans="1:11" s="13" customFormat="1" ht="60">
+      <c r="A11" s="263"/>
+      <c r="B11" s="255"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>54</v>
+        <v>145</v>
       </c>
       <c r="G11" s="11">
         <v>0</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="J11" s="46"/>
       <c r="K11" s="49" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="137.25">
-      <c r="A12" s="244" t="s">
-        <v>143</v>
-      </c>
-      <c r="B12" s="245" t="s">
-        <v>144</v>
+        <v>202</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="135">
+      <c r="A12" s="256" t="s">
+        <v>146</v>
+      </c>
+      <c r="B12" s="257" t="s">
+        <v>147</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="50" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>24</v>
       </c>
       <c r="F12" s="35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G12" s="35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H12" s="35" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="J12" s="51" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K12" s="52" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="76.5">
-      <c r="A13" s="244"/>
-      <c r="B13" s="245"/>
+        <v>206</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="75">
+      <c r="A13" s="256"/>
+      <c r="B13" s="257"/>
       <c r="C13" s="14"/>
       <c r="D13" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F13" s="35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G13" s="35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K13" s="57" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="60.75">
-      <c r="A14" s="244"/>
-      <c r="B14" s="245"/>
+        <v>209</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="60">
+      <c r="A14" s="256"/>
+      <c r="B14" s="257"/>
       <c r="C14" s="14"/>
       <c r="D14" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F14" s="35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G14" s="35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H14" s="35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K14" s="57" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -4633,15 +4804,15 @@
       <c r="H15" s="20"/>
       <c r="I15" s="18"/>
     </row>
-    <row r="16" spans="1:11" ht="321">
+    <row r="16" spans="1:11" ht="315">
       <c r="A16" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" s="253" t="s">
         <v>68</v>
       </c>
-      <c r="B16" s="241" t="s">
+      <c r="C16" s="22" t="s">
         <v>69</v>
-      </c>
-      <c r="C16" s="22" t="s">
-        <v>70</v>
       </c>
       <c r="D16" s="23">
         <v>5356014</v>
@@ -4650,27 +4821,27 @@
         <v>74</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="G16" s="23" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H16" s="23" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="I16" s="21" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J16" s="14" t="s">
         <v>73</v>
       </c>
       <c r="K16" s="18"/>
     </row>
-    <row r="17" spans="1:11" ht="183">
-      <c r="A17" s="238"/>
-      <c r="B17" s="242"/>
+    <row r="17" spans="1:11" ht="195">
+      <c r="A17" s="250"/>
+      <c r="B17" s="254"/>
       <c r="C17" s="22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D17" s="23">
         <v>5356014</v>
@@ -4679,7 +4850,7 @@
         <v>74</v>
       </c>
       <c r="F17" s="21" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="G17" s="23">
         <v>30268</v>
@@ -4688,48 +4859,48 @@
         <v>110000</v>
       </c>
       <c r="I17" s="21" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="J17" s="14" t="s">
         <v>73</v>
       </c>
       <c r="K17" s="18"/>
     </row>
-    <row r="18" spans="1:11" ht="167.25">
-      <c r="A18" s="239"/>
-      <c r="B18" s="242"/>
+    <row r="18" spans="1:11" ht="195">
+      <c r="A18" s="251"/>
+      <c r="B18" s="254"/>
       <c r="C18" s="22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="E18" s="24" t="s">
         <v>77</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G18" s="21"/>
       <c r="H18" s="23" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I18" s="21" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="J18" s="55" t="s">
         <v>73</v>
       </c>
       <c r="K18" s="18"/>
     </row>
-    <row r="19" spans="1:11" ht="106.5">
-      <c r="A19" s="240"/>
-      <c r="B19" s="243"/>
+    <row r="19" spans="1:11" ht="105">
+      <c r="A19" s="252"/>
+      <c r="B19" s="255"/>
       <c r="C19" s="22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="E19" s="24" t="s">
         <v>136</v>
@@ -4749,9 +4920,9 @@
       </c>
       <c r="K19" s="18"/>
     </row>
-    <row r="20" spans="1:11" ht="106.5">
+    <row r="20" spans="1:11" ht="105">
       <c r="A20" s="30" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B20" s="36" t="s">
         <v>83</v>
@@ -4764,21 +4935,21 @@
         <v>19</v>
       </c>
       <c r="F20" s="32" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="G20" s="19"/>
       <c r="H20" s="33" t="s">
-        <v>85</v>
+        <v>219</v>
       </c>
       <c r="I20" s="18"/>
       <c r="J20" s="55" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K20" s="55" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="183">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="195">
       <c r="A21" s="18"/>
       <c r="B21" s="9" t="s">
         <v>90</v>
@@ -4791,55 +4962,55 @@
         <v>92</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G21" s="27">
         <v>0</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="J21" s="54" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="K21" s="18"/>
     </row>
-    <row r="22" spans="1:11" ht="336">
+    <row r="22" spans="1:11" ht="345">
       <c r="A22" s="18"/>
       <c r="B22" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C22" s="25"/>
       <c r="D22" s="26">
         <v>600000</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G22" s="27">
         <v>0.7</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="J22" s="53" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="K22" s="18"/>
     </row>
-    <row r="23" spans="1:11" ht="106.5">
+    <row r="23" spans="1:11" ht="105">
       <c r="A23" s="18"/>
       <c r="B23" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C23" s="14"/>
       <c r="D23" s="26">
@@ -4849,7 +5020,7 @@
         <v>74</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G23" s="14">
         <v>0</v>
@@ -4858,17 +5029,17 @@
         <v>1</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J23" s="53" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="K23" s="18"/>
     </row>
-    <row r="24" spans="1:11" ht="91.5">
+    <row r="24" spans="1:11" ht="90">
       <c r="A24" s="18"/>
       <c r="B24" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C24" s="25"/>
       <c r="D24" s="28">
@@ -4878,7 +5049,7 @@
         <v>19</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G24" s="14">
         <v>1</v>
@@ -4887,27 +5058,27 @@
         <v>3</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J24" s="53" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="K24" s="18"/>
     </row>
-    <row r="25" spans="1:11" ht="381.75">
+    <row r="25" spans="1:11" ht="405">
       <c r="A25" s="18"/>
       <c r="B25" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C25" s="29"/>
       <c r="D25" s="28">
         <v>1250000</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>112</v>
+        <v>182</v>
       </c>
       <c r="G25" s="14">
         <v>326</v>
@@ -4916,19 +5087,19 @@
         <v>1000</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J25" s="53" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="K25" s="18"/>
     </row>
-    <row r="26" spans="1:11" ht="336">
+    <row r="26" spans="1:11" ht="345">
       <c r="A26" s="37">
         <v>106912</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C26" s="24"/>
       <c r="D26" s="34">
@@ -4938,19 +5109,19 @@
         <v>128</v>
       </c>
       <c r="F26" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>117</v>
-      </c>
       <c r="H26" s="3" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="J26" s="55" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K26" s="18"/>
     </row>
@@ -5011,172 +5182,172 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="45.75">
-      <c r="A2" s="254" t="s">
-        <v>152</v>
+    <row r="2" spans="1:2" ht="45">
+      <c r="A2" s="266" t="s">
+        <v>155</v>
       </c>
       <c r="B2" s="198" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="254" t="s">
+      <c r="A3" s="266" t="s">
         <v>24</v>
       </c>
       <c r="B3" s="198" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="30.75">
-      <c r="A4" s="254" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="45">
+      <c r="A4" s="266" t="s">
         <v>92</v>
       </c>
       <c r="B4" s="198" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="30.75">
-      <c r="A5" s="254" t="s">
-        <v>223</v>
+        <v>227</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="30">
+      <c r="A5" s="266" t="s">
+        <v>228</v>
       </c>
       <c r="B5" s="198" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="91.5">
-      <c r="A6" s="254" t="s">
-        <v>51</v>
+        <v>229</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="90">
+      <c r="A6" s="266" t="s">
+        <v>52</v>
       </c>
       <c r="B6" s="198" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="45.75">
-      <c r="A7" s="254" t="s">
-        <v>226</v>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="45">
+      <c r="A7" s="266" t="s">
+        <v>231</v>
       </c>
       <c r="B7" s="198" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="45.75">
-      <c r="A8" s="254" t="s">
-        <v>63</v>
+        <v>232</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="45">
+      <c r="A8" s="266" t="s">
+        <v>62</v>
       </c>
       <c r="B8" s="198" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="45.75">
-      <c r="A9" s="254" t="s">
-        <v>111</v>
+        <v>233</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="45">
+      <c r="A9" s="266" t="s">
+        <v>110</v>
       </c>
       <c r="B9" s="198" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="30.75">
-      <c r="A10" s="254" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="255" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="30.75">
-      <c r="A11" s="254" t="s">
-        <v>231</v>
-      </c>
-      <c r="B11" s="255" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="45.75">
-      <c r="A12" s="254" t="s">
-        <v>233</v>
+        <v>234</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="45">
+      <c r="A10" s="266" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="267" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="30">
+      <c r="A11" s="266" t="s">
+        <v>236</v>
+      </c>
+      <c r="B11" s="267" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="45">
+      <c r="A12" s="266" t="s">
+        <v>238</v>
       </c>
       <c r="B12" s="198" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="30.75">
-      <c r="A13" s="254" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="30">
+      <c r="A13" s="266" t="s">
         <v>74</v>
       </c>
-      <c r="B13" s="255" t="s">
-        <v>235</v>
+      <c r="B13" s="267" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="254" t="s">
-        <v>236</v>
-      </c>
-      <c r="B14" s="255" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="30.75">
-      <c r="A15" s="254" t="s">
-        <v>238</v>
-      </c>
-      <c r="B15" s="255" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="30.75">
-      <c r="A16" s="254" t="s">
+      <c r="A14" s="266" t="s">
+        <v>241</v>
+      </c>
+      <c r="B14" s="267" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="30">
+      <c r="A15" s="266" t="s">
+        <v>243</v>
+      </c>
+      <c r="B15" s="267" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="30">
+      <c r="A16" s="266" t="s">
         <v>77</v>
       </c>
-      <c r="B16" s="255" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="30.75">
-      <c r="A17" s="254" t="s">
-        <v>43</v>
+      <c r="B16" s="267" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="30">
+      <c r="A17" s="266" t="s">
+        <v>45</v>
       </c>
       <c r="B17" s="198" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="30.75">
-      <c r="A18" s="254" t="s">
-        <v>242</v>
-      </c>
-      <c r="B18" s="255" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="76.5">
-      <c r="A19" s="254" t="s">
-        <v>244</v>
-      </c>
-      <c r="B19" s="255" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="30.75">
-      <c r="A20" s="254" t="s">
         <v>246</v>
       </c>
-      <c r="B20" s="255" t="s">
+    </row>
+    <row r="18" spans="1:2" ht="30">
+      <c r="A18" s="266" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" ht="45.75">
-      <c r="A21" s="254" t="s">
+      <c r="B18" s="267" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="75">
+      <c r="A19" s="266" t="s">
+        <v>249</v>
+      </c>
+      <c r="B19" s="267" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="30">
+      <c r="A20" s="266" t="s">
+        <v>251</v>
+      </c>
+      <c r="B20" s="267" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="45">
+      <c r="A21" s="266" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="256" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="30.75">
-      <c r="A22" s="254" t="s">
-        <v>249</v>
-      </c>
-      <c r="B22" s="255" t="s">
-        <v>250</v>
+      <c r="B21" s="268" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="30">
+      <c r="A22" s="266" t="s">
+        <v>254</v>
+      </c>
+      <c r="B22" s="267" t="s">
+        <v>255</v>
       </c>
     </row>
   </sheetData>
@@ -5185,6 +5356,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -5439,7 +5619,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
@@ -5492,23 +5672,14 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D06A8A7-AAD0-46D5-9E3E-4D298B186157}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E36ED78C-029F-4A50-B3B7-CA985A738900}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84AEDBCE-AE29-4AA3-A5BD-B932231712F2}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D06A8A7-AAD0-46D5-9E3E-4D298B186157}"/>
 </file>
--- a/01_Input/00_CO Validation/Bangladesh - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Bangladesh - Energy Projects.xlsx
@@ -442,7 +442,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="296">
+  <cellXfs count="290">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -1204,61 +1204,47 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1355,6 +1341,7 @@
     <author>tc={33AAE0C7-20DB-431D-B68F-2AE92B1E54FA}</author>
     <author>tc={19BDA1B9-E07E-4FD8-9A58-298F2E5F5765}</author>
     <author>tc={59D014D4-747A-4DE4-96E6-5AA8FEA984BB}</author>
+    <author>CO validation update</author>
     <author>tc={E1032D12-67C6-4765-8703-4600D0039D02}</author>
   </authors>
   <commentList>
@@ -1374,7 +1361,7 @@
     There is no such ID on the website</t>
       </text>
     </comment>
-    <comment ref="L16" authorId="2" shapeId="0">
+    <comment ref="L15" authorId="2" shapeId="0">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1382,12 +1369,32 @@
     Instead of using ODP ton, I used ton CO2 eq based on their information</t>
       </text>
     </comment>
-    <comment ref="A21" authorId="3" shapeId="0">
+    <comment ref="K19" authorId="3" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L19" authorId="3" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="A20" authorId="4" shapeId="0">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     This ID on the website is different</t>
+      </text>
+    </comment>
+    <comment ref="K26" authorId="3" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L26" authorId="3" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
       </text>
     </comment>
   </commentList>
@@ -1685,7 +1692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X28"/>
+  <dimension ref="A1:X27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="9.28515625" bestFit="1" customWidth="1" style="128" min="1" max="1"/>
@@ -1872,9 +1879,8 @@
         </is>
       </c>
       <c r="K2" s="141" t="n"/>
-      <c r="L2" s="209">
-        <f>600/1000</f>
-        <v/>
+      <c r="L2" s="209" t="n">
+        <v>0.6</v>
       </c>
       <c r="M2" s="270" t="inlineStr">
         <is>
@@ -1924,7 +1930,11 @@
       <c r="F3" s="151" t="n"/>
       <c r="G3" s="151" t="n"/>
       <c r="H3" s="151" t="n"/>
-      <c r="I3" s="273" t="n"/>
+      <c r="I3" s="152" t="inlineStr">
+        <is>
+          <t>Policy or Regulatory Framework</t>
+        </is>
+      </c>
       <c r="J3" s="221" t="inlineStr">
         <is>
           <t>No. of low carbon policy, guideline and standard</t>
@@ -1979,7 +1989,11 @@
       <c r="F4" s="158" t="n"/>
       <c r="G4" s="158" t="n"/>
       <c r="H4" s="158" t="n"/>
-      <c r="I4" s="274" t="n"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>GHG Emissions Reduction</t>
+        </is>
+      </c>
       <c r="J4" s="154" t="inlineStr">
         <is>
           <t>GHG Emission Reduction target in updated NDC</t>
@@ -1991,7 +2005,6 @@
           <t>1.57 M Ton CO2eq</t>
         </is>
       </c>
-      <c r="M4" s="271" t="n"/>
       <c r="N4" s="159" t="n"/>
       <c r="O4" s="199" t="n"/>
       <c r="P4" s="72" t="n"/>
@@ -2023,9 +2036,9 @@
       <c r="D5" s="163" t="n">
         <v>1788991</v>
       </c>
-      <c r="E5" s="272" t="n"/>
-      <c r="F5" s="272" t="n"/>
-      <c r="G5" s="272" t="n"/>
+      <c r="E5" s="271" t="n"/>
+      <c r="F5" s="271" t="n"/>
+      <c r="G5" s="271" t="n"/>
       <c r="H5" s="163" t="inlineStr">
         <is>
           <t>Non-VF</t>
@@ -2086,7 +2099,11 @@
       <c r="F6" s="168" t="n"/>
       <c r="G6" s="168" t="n"/>
       <c r="H6" s="168" t="n"/>
-      <c r="I6" s="273" t="n"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>GHG Emissions Reduction</t>
+        </is>
+      </c>
       <c r="J6" s="221" t="inlineStr">
         <is>
           <t xml:space="preserve">GHG Emission Reduction target </t>
@@ -2100,7 +2117,6 @@
           <t>oo</t>
         </is>
       </c>
-      <c r="M6" s="273" t="n"/>
       <c r="N6" s="153" t="n"/>
       <c r="O6" s="199" t="n"/>
       <c r="P6" s="72" t="n"/>
@@ -2126,10 +2142,15 @@
       <c r="F7" s="211" t="n"/>
       <c r="G7" s="211" t="n"/>
       <c r="H7" s="211" t="n"/>
-      <c r="I7" s="273" t="n"/>
-      <c r="J7" s="214">
-        <f>'Beneficiary Categories'!B3</f>
-        <v/>
+      <c r="I7" s="213" t="inlineStr">
+        <is>
+          <t>Energy (MW added)</t>
+        </is>
+      </c>
+      <c r="J7" s="214" t="inlineStr">
+        <is>
+          <t>Number of MW installed capacity</t>
+        </is>
       </c>
       <c r="K7" s="215" t="n">
         <v>0</v>
@@ -2137,7 +2158,6 @@
       <c r="L7" s="209" t="n">
         <v>0.03</v>
       </c>
-      <c r="M7" s="273" t="n"/>
       <c r="N7" s="153" t="n"/>
       <c r="O7" s="199" t="n"/>
       <c r="P7" s="72" t="n"/>
@@ -2159,7 +2179,11 @@
       <c r="F8" s="171" t="n"/>
       <c r="G8" s="171" t="n"/>
       <c r="H8" s="171" t="n"/>
-      <c r="I8" s="274" t="n"/>
+      <c r="I8" s="212" t="inlineStr">
+        <is>
+          <t>Capacity Building Training</t>
+        </is>
+      </c>
       <c r="J8" s="173" t="inlineStr">
         <is>
           <t>Number of people trained/educated/informed 
@@ -2173,7 +2197,6 @@
       <c r="L8" s="221" t="n">
         <v>200</v>
       </c>
-      <c r="M8" s="274" t="n"/>
       <c r="N8" s="159" t="n"/>
       <c r="O8" s="199" t="n"/>
       <c r="P8" s="72" t="n"/>
@@ -2191,87 +2214,47 @@
       <c r="X8" s="68" t="n"/>
     </row>
     <row r="9" ht="91.5" customFormat="1" customHeight="1" s="126">
-      <c r="A9" s="275" t="n"/>
-      <c r="B9" s="276" t="n"/>
-      <c r="C9" s="276" t="n"/>
-      <c r="D9" s="277" t="n"/>
-      <c r="E9" s="277" t="n"/>
-      <c r="F9" s="277" t="n"/>
-      <c r="G9" s="277" t="n"/>
-      <c r="H9" s="277" t="n"/>
-      <c r="I9" s="212" t="inlineStr">
+      <c r="A9" s="174" t="n">
+        <v>93848</v>
+      </c>
+      <c r="B9" s="175" t="inlineStr">
+        <is>
+          <t>Adaptation Initiative for Climate Vulnerable Offshore Small Islands and Riverine Charland in Bangladesh</t>
+        </is>
+      </c>
+      <c r="C9" s="206" t="inlineStr">
+        <is>
+          <t>https://open.undp.org/projects/00093848</t>
+        </is>
+      </c>
+      <c r="D9" s="146" t="n">
+        <v>9212322</v>
+      </c>
+      <c r="E9" s="269" t="n"/>
+      <c r="F9" s="269" t="n"/>
+      <c r="G9" s="269" t="n"/>
+      <c r="H9" s="146" t="inlineStr">
+        <is>
+          <t>Non-VF</t>
+        </is>
+      </c>
+      <c r="I9" s="221" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
         </is>
       </c>
-      <c r="J9" s="173" t="inlineStr">
-        <is>
-          <t>Installed capacity in MW for access/productive-use outputs</t>
-        </is>
-      </c>
-      <c r="K9" s="141" t="n">
+      <c r="J9" s="221" t="inlineStr">
+        <is>
+          <t>Energy (MW added)</t>
+        </is>
+      </c>
+      <c r="K9" s="221" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="278" t="n"/>
-      <c r="M9" s="279" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
-      <c r="N9" s="159" t="n"/>
-      <c r="O9" s="280" t="n"/>
-      <c r="P9" s="281" t="n"/>
-      <c r="Q9" s="282" t="n"/>
-      <c r="R9" s="281" t="n"/>
-      <c r="S9" s="281" t="n"/>
-      <c r="T9" s="281" t="n"/>
-      <c r="U9" s="281" t="n"/>
-      <c r="V9" s="283" t="n"/>
-      <c r="W9" s="281" t="n"/>
-      <c r="X9" s="283" t="n"/>
-    </row>
-    <row r="10" ht="30.75" customFormat="1" customHeight="1" s="127">
-      <c r="A10" s="174" t="n">
-        <v>93848</v>
-      </c>
-      <c r="B10" s="175" t="inlineStr">
-        <is>
-          <t>Adaptation Initiative for Climate Vulnerable Offshore Small Islands and Riverine Charland in Bangladesh</t>
-        </is>
-      </c>
-      <c r="C10" s="206" t="inlineStr">
-        <is>
-          <t>https://open.undp.org/projects/00093848</t>
-        </is>
-      </c>
-      <c r="D10" s="146" t="n">
-        <v>9212322</v>
-      </c>
-      <c r="E10" s="269" t="n"/>
-      <c r="F10" s="269" t="n"/>
-      <c r="G10" s="269" t="n"/>
-      <c r="H10" s="146" t="inlineStr">
-        <is>
-          <t>Non-VF</t>
-        </is>
-      </c>
-      <c r="I10" s="221" t="inlineStr">
-        <is>
-          <t>Energy (MW added)</t>
-        </is>
-      </c>
-      <c r="J10" s="221" t="inlineStr">
-        <is>
-          <t>Energy (MW added)</t>
-        </is>
-      </c>
-      <c r="K10" s="221" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="209" t="n">
+      <c r="L9" s="209" t="n">
         <v>0.06</v>
       </c>
-      <c r="M10" s="173" t="inlineStr">
+      <c r="M9" s="173" t="inlineStr">
         <is>
           <t>Nano-grid will cover 20-25 households
 30 nano-grids with covering
@@ -2279,14 +2262,64 @@
 On comment column: It is expected that about 1MW energy will be generated</t>
         </is>
       </c>
-      <c r="N10" s="164" t="inlineStr">
+      <c r="N9" s="164" t="inlineStr">
         <is>
           <t>Adaptation Fund</t>
         </is>
       </c>
-      <c r="O10" s="217" t="n">
+      <c r="O9" s="217" t="n">
         <v>0.5</v>
       </c>
+      <c r="P9" s="72" t="n"/>
+      <c r="Q9" s="154" t="inlineStr">
+        <is>
+          <t>Close the gap on energy access</t>
+        </is>
+      </c>
+      <c r="R9" s="72" t="n"/>
+      <c r="S9" s="72" t="n"/>
+      <c r="T9" s="72" t="n"/>
+      <c r="U9" s="72" t="n"/>
+      <c r="V9" s="68" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="W9" s="72" t="n"/>
+      <c r="X9" s="68" t="n"/>
+    </row>
+    <row r="10" ht="30.75" customFormat="1" customHeight="1" s="127">
+      <c r="A10" s="177" t="n"/>
+      <c r="B10" s="178" t="n"/>
+      <c r="C10" s="179" t="n"/>
+      <c r="D10" s="180" t="n"/>
+      <c r="E10" s="180" t="n"/>
+      <c r="F10" s="180" t="n"/>
+      <c r="G10" s="180" t="n"/>
+      <c r="H10" s="180" t="n"/>
+      <c r="I10" s="154" t="inlineStr">
+        <is>
+          <t>Agriculture and Food System</t>
+        </is>
+      </c>
+      <c r="J10" s="221" t="inlineStr">
+        <is>
+          <t>Energy (MW added)</t>
+        </is>
+      </c>
+      <c r="K10" s="221" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="209" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M10" s="221" t="inlineStr">
+        <is>
+          <t>Install solar irrigation pumps for community</t>
+        </is>
+      </c>
+      <c r="N10" s="181" t="n"/>
+      <c r="O10" s="63" t="n"/>
       <c r="P10" s="72" t="n"/>
       <c r="Q10" s="154" t="inlineStr">
         <is>
@@ -2297,23 +2330,19 @@
       <c r="S10" s="72" t="n"/>
       <c r="T10" s="72" t="n"/>
       <c r="U10" s="72" t="n"/>
-      <c r="V10" s="68" t="inlineStr">
-        <is>
-          <t>Solar</t>
-        </is>
-      </c>
+      <c r="V10" s="68" t="n"/>
       <c r="W10" s="72" t="n"/>
       <c r="X10" s="68" t="n"/>
     </row>
     <row r="11" ht="45.75" customFormat="1" customHeight="1" s="127">
-      <c r="A11" s="177" t="n"/>
-      <c r="B11" s="178" t="n"/>
-      <c r="C11" s="179" t="n"/>
-      <c r="D11" s="180" t="n"/>
-      <c r="E11" s="180" t="n"/>
-      <c r="F11" s="180" t="n"/>
-      <c r="G11" s="180" t="n"/>
-      <c r="H11" s="180" t="n"/>
+      <c r="A11" s="182" t="n"/>
+      <c r="B11" s="183" t="n"/>
+      <c r="C11" s="184" t="n"/>
+      <c r="D11" s="185" t="n"/>
+      <c r="E11" s="185" t="n"/>
+      <c r="F11" s="185" t="n"/>
+      <c r="G11" s="185" t="n"/>
+      <c r="H11" s="185" t="n"/>
       <c r="I11" s="154" t="inlineStr">
         <is>
           <t>Agriculture and Food System</t>
@@ -2328,14 +2357,15 @@
         <v>0</v>
       </c>
       <c r="L11" s="209" t="n">
-        <v>0.15</v>
+        <v>0.036</v>
       </c>
       <c r="M11" s="221" t="inlineStr">
         <is>
-          <t>Install solar irrigation pumps for community</t>
-        </is>
-      </c>
-      <c r="N11" s="181" t="n"/>
+          <t>Install solar cold storage
+Farmers and fishers are the users of the solar cold storage</t>
+        </is>
+      </c>
+      <c r="N11" s="186" t="n"/>
       <c r="O11" s="63" t="n"/>
       <c r="P11" s="72" t="n"/>
       <c r="Q11" s="154" t="inlineStr">
@@ -2352,87 +2382,99 @@
       <c r="X11" s="68" t="n"/>
     </row>
     <row r="12" ht="78" customHeight="1">
-      <c r="A12" s="182" t="n"/>
-      <c r="B12" s="183" t="n"/>
-      <c r="C12" s="184" t="n"/>
-      <c r="D12" s="185" t="n"/>
-      <c r="E12" s="185" t="n"/>
-      <c r="F12" s="185" t="n"/>
-      <c r="G12" s="185" t="n"/>
-      <c r="H12" s="185" t="n"/>
-      <c r="I12" s="154" t="inlineStr">
-        <is>
-          <t>Agriculture and Food System</t>
+      <c r="A12" s="187" t="inlineStr">
+        <is>
+          <t>85984</t>
+        </is>
+      </c>
+      <c r="B12" s="188" t="inlineStr">
+        <is>
+          <t>Local Government Initiative on Climate Change (LoGIC)</t>
+        </is>
+      </c>
+      <c r="C12" s="189" t="inlineStr">
+        <is>
+          <t>https://open.undp.org/projects/00085984</t>
+        </is>
+      </c>
+      <c r="D12" s="190" t="n">
+        <v>35200000</v>
+      </c>
+      <c r="E12" s="272" t="n"/>
+      <c r="F12" s="272" t="n"/>
+      <c r="G12" s="272" t="n"/>
+      <c r="H12" s="190" t="inlineStr">
+        <is>
+          <t>Non-VF</t>
+        </is>
+      </c>
+      <c r="I12" s="221" t="inlineStr">
+        <is>
+          <t>Energy (MW added)</t>
         </is>
       </c>
       <c r="J12" s="221" t="inlineStr">
         <is>
-          <t>Energy (MW added)</t>
-        </is>
-      </c>
-      <c r="K12" s="221" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="209" t="n">
-        <v>0.036</v>
+          <t>Renewable energy capacity installed (MW)</t>
+        </is>
+      </c>
+      <c r="K12" s="221" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L12" s="221" t="n">
+        <v>1.12</v>
       </c>
       <c r="M12" s="221" t="inlineStr">
         <is>
-          <t>Install solar cold storage
-Farmers and fishers are the users of the solar cold storage</t>
-        </is>
-      </c>
-      <c r="N12" s="186" t="n"/>
-      <c r="O12" s="63" t="n"/>
+          <t>59 community solar irrigation pumps implemented by Union Parishads
+Total beneficieres are 400,000 vulnerable households. Main project componants are adaptive livelihood support, social protection service, support for solar home system.</t>
+        </is>
+      </c>
+      <c r="N12" s="221" t="inlineStr">
+        <is>
+          <t>(EU-17.05m, SIDA-17.97m)</t>
+        </is>
+      </c>
+      <c r="O12" s="218" t="n">
+        <v>0.5</v>
+      </c>
       <c r="P12" s="72" t="n"/>
       <c r="Q12" s="154" t="inlineStr">
         <is>
-          <t>Close the gap on energy access</t>
+          <t>Accelerating just energy transition</t>
         </is>
       </c>
       <c r="R12" s="72" t="n"/>
       <c r="S12" s="72" t="n"/>
       <c r="T12" s="72" t="n"/>
       <c r="U12" s="72" t="n"/>
-      <c r="V12" s="68" t="n"/>
+      <c r="V12" s="68" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
       <c r="W12" s="72" t="n"/>
       <c r="X12" s="68" t="n"/>
     </row>
     <row r="13" ht="91.5" customHeight="1">
-      <c r="A13" s="187" t="inlineStr">
-        <is>
-          <t>85984</t>
-        </is>
-      </c>
-      <c r="B13" s="188" t="inlineStr">
-        <is>
-          <t>Local Government Initiative on Climate Change (LoGIC)</t>
-        </is>
-      </c>
-      <c r="C13" s="189" t="inlineStr">
-        <is>
-          <t>https://open.undp.org/projects/00085984</t>
-        </is>
-      </c>
-      <c r="D13" s="190" t="n">
-        <v>35200000</v>
-      </c>
-      <c r="E13" s="284" t="n"/>
-      <c r="F13" s="284" t="n"/>
-      <c r="G13" s="284" t="n"/>
-      <c r="H13" s="190" t="inlineStr">
-        <is>
-          <t>Non-VF</t>
-        </is>
-      </c>
+      <c r="A13" s="166" t="n"/>
+      <c r="B13" s="178" t="n"/>
+      <c r="C13" s="180" t="n"/>
+      <c r="D13" s="191" t="n"/>
+      <c r="E13" s="191" t="n"/>
+      <c r="F13" s="191" t="n"/>
+      <c r="G13" s="191" t="n"/>
+      <c r="H13" s="191" t="n"/>
       <c r="I13" s="221" t="inlineStr">
         <is>
-          <t>Energy (MW added)</t>
+          <t>Water Services</t>
         </is>
       </c>
       <c r="J13" s="221" t="inlineStr">
         <is>
-          <t>Renewable energy capacity installed (MW)</t>
+          <t>Number of people benefiting from drinking water supply with electric solar powered motors</t>
         </is>
       </c>
       <c r="K13" s="221" t="inlineStr">
@@ -2440,23 +2482,18 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="L13" s="221" t="n">
-        <v>1.12</v>
+      <c r="L13" s="209" t="n">
+        <v>1463</v>
       </c>
       <c r="M13" s="221" t="inlineStr">
         <is>
-          <t>59 community solar irrigation pumps implemented by Union Parishads
-Total beneficieres are 400,000 vulnerable households. Main project componants are adaptive livelihood support, social protection service, support for solar home system.</t>
-        </is>
-      </c>
-      <c r="N13" s="221" t="inlineStr">
-        <is>
-          <t>(EU-17.05m, SIDA-17.97m)</t>
-        </is>
-      </c>
-      <c r="O13" s="218" t="n">
-        <v>0.5</v>
-      </c>
+          <t>54 community level drinking water supply with electric solar powered motors implemented by Union Parishads
+Budget is updated
+On comment column: About 325 household will be benefitted</t>
+        </is>
+      </c>
+      <c r="N13" s="181" t="n"/>
+      <c r="O13" s="221" t="n"/>
       <c r="P13" s="72" t="n"/>
       <c r="Q13" s="154" t="inlineStr">
         <is>
@@ -2467,18 +2504,14 @@
       <c r="S13" s="72" t="n"/>
       <c r="T13" s="72" t="n"/>
       <c r="U13" s="72" t="n"/>
-      <c r="V13" s="68" t="inlineStr">
-        <is>
-          <t>Solar</t>
-        </is>
-      </c>
+      <c r="V13" s="68" t="n"/>
       <c r="W13" s="72" t="n"/>
       <c r="X13" s="68" t="n"/>
     </row>
     <row r="14" ht="75" customHeight="1">
-      <c r="A14" s="166" t="n"/>
-      <c r="B14" s="178" t="n"/>
-      <c r="C14" s="180" t="n"/>
+      <c r="A14" s="169" t="n"/>
+      <c r="B14" s="183" t="n"/>
+      <c r="C14" s="185" t="n"/>
       <c r="D14" s="191" t="n"/>
       <c r="E14" s="191" t="n"/>
       <c r="F14" s="191" t="n"/>
@@ -2486,12 +2519,12 @@
       <c r="H14" s="191" t="n"/>
       <c r="I14" s="221" t="inlineStr">
         <is>
-          <t>Water Services</t>
+          <t>Energy (MW added)</t>
         </is>
       </c>
       <c r="J14" s="221" t="inlineStr">
         <is>
-          <t>Number of people benefiting from drinking water supply with electric solar powered motors</t>
+          <t>Renewable energy capacity installed</t>
         </is>
       </c>
       <c r="K14" s="221" t="inlineStr">
@@ -2499,17 +2532,17 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="L14" s="209" t="n">
-        <v>1463</v>
+      <c r="L14" s="221" t="n">
+        <v>0.35</v>
       </c>
       <c r="M14" s="221" t="inlineStr">
         <is>
-          <t>54 community level drinking water supply with electric solar powered motors implemented by Union Parishads
+          <t>7 community level rooftop solar home systems  implemented by Union Parishads
 Budget is updated
-On comment column: About 325 household will be benefitted</t>
-        </is>
-      </c>
-      <c r="N14" s="181" t="n"/>
+On comment column: It is expected that about 350KW energy will be generated</t>
+        </is>
+      </c>
+      <c r="N14" s="186" t="n"/>
       <c r="O14" s="221" t="n"/>
       <c r="P14" s="72" t="n"/>
       <c r="Q14" s="154" t="inlineStr">
@@ -2521,45 +2554,68 @@
       <c r="S14" s="72" t="n"/>
       <c r="T14" s="72" t="n"/>
       <c r="U14" s="72" t="n"/>
-      <c r="V14" s="68" t="n"/>
+      <c r="V14" s="68" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
       <c r="W14" s="72" t="n"/>
       <c r="X14" s="68" t="n"/>
     </row>
     <row r="15" ht="106.5" customHeight="1">
-      <c r="A15" s="169" t="n"/>
-      <c r="B15" s="183" t="n"/>
-      <c r="C15" s="185" t="n"/>
-      <c r="D15" s="191" t="n"/>
-      <c r="E15" s="191" t="n"/>
-      <c r="F15" s="191" t="n"/>
-      <c r="G15" s="191" t="n"/>
-      <c r="H15" s="191" t="n"/>
-      <c r="I15" s="221" t="inlineStr">
-        <is>
-          <t>Energy (MW added)</t>
+      <c r="A15" s="164" t="inlineStr">
+        <is>
+          <t>00110796(AC Unit) &amp; 00117012 (PMU)</t>
+        </is>
+      </c>
+      <c r="B15" s="161" t="inlineStr">
+        <is>
+          <t>HCFC Phase-Out Management Plan (HPMP Stage-II) For Compliance with the 2020 and 2025 Control Targets Under the Montreal Protocol</t>
+        </is>
+      </c>
+      <c r="C15" s="131" t="inlineStr">
+        <is>
+          <t>HPMP II (AC Unit); HPMP II (PMU)</t>
+        </is>
+      </c>
+      <c r="D15" s="192" t="n">
+        <v>5356014</v>
+      </c>
+      <c r="E15" s="273" t="n"/>
+      <c r="F15" s="273" t="n"/>
+      <c r="G15" s="273" t="n"/>
+      <c r="H15" s="192" t="inlineStr">
+        <is>
+          <t>Non-VF</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>GHG Emissions Reduction</t>
         </is>
       </c>
       <c r="J15" s="221" t="inlineStr">
         <is>
-          <t>Renewable energy capacity installed</t>
-        </is>
-      </c>
-      <c r="K15" s="221" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="L15" s="221" t="n">
-        <v>0.35</v>
+          <t>GHG emission reductions (ton CO2eq)</t>
+        </is>
+      </c>
+      <c r="K15" s="192" t="n"/>
+      <c r="L15" s="216" t="inlineStr">
+        <is>
+          <t>1.73 M Ton CO2eq</t>
+        </is>
       </c>
       <c r="M15" s="221" t="inlineStr">
         <is>
-          <t>7 community level rooftop solar home systems  implemented by Union Parishads
-Budget is updated
-On comment column: It is expected that about 350KW energy will be generated</t>
-        </is>
-      </c>
-      <c r="N15" s="186" t="n"/>
+          <t>The project’s ultimate goal is to implement structural changes in RAC manufacturing and servicing sectors for cleaner production and contribute to the quality of people's lives, through the protection of the ozone layer and reduction in direct and indirect emissions. This project will phase-out 310.78 kg HCFC-22 equivalent to 17.09 ODP tons, which is 66% of Bangladesh´s consumption of HCFCs in RAC manufacturing sector, contributing to the reduction target for 2025.
+Baseline: Consumption of ODS 47.22 ODP ton</t>
+        </is>
+      </c>
+      <c r="N15" s="176" t="inlineStr">
+        <is>
+          <t>MLF</t>
+        </is>
+      </c>
       <c r="O15" s="221" t="n"/>
       <c r="P15" s="72" t="n"/>
       <c r="Q15" s="154" t="inlineStr">
@@ -2571,69 +2627,45 @@
       <c r="S15" s="72" t="n"/>
       <c r="T15" s="72" t="n"/>
       <c r="U15" s="72" t="n"/>
-      <c r="V15" s="68" t="inlineStr">
-        <is>
-          <t>Solar</t>
-        </is>
-      </c>
+      <c r="V15" s="68" t="n"/>
       <c r="W15" s="72" t="n"/>
       <c r="X15" s="68" t="n"/>
     </row>
     <row r="16" ht="135" customHeight="1">
-      <c r="A16" s="164" t="inlineStr">
-        <is>
-          <t>00110796(AC Unit) &amp; 00117012 (PMU)</t>
-        </is>
-      </c>
-      <c r="B16" s="161" t="inlineStr">
-        <is>
-          <t>HCFC Phase-Out Management Plan (HPMP Stage-II) For Compliance with the 2020 and 2025 Control Targets Under the Montreal Protocol</t>
-        </is>
-      </c>
-      <c r="C16" s="131" t="inlineStr">
-        <is>
-          <t>HPMP II (AC Unit); HPMP II (PMU)</t>
-        </is>
-      </c>
-      <c r="D16" s="192" t="n">
-        <v>5356014</v>
-      </c>
-      <c r="E16" s="285" t="n"/>
-      <c r="F16" s="285" t="n"/>
-      <c r="G16" s="285" t="n"/>
-      <c r="H16" s="192" t="inlineStr">
-        <is>
-          <t>Non-VF</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>GHG Emissions Reduction</t>
+      <c r="A16" s="132" t="n"/>
+      <c r="B16" s="133" t="n"/>
+      <c r="C16" s="133" t="n"/>
+      <c r="D16" s="134" t="n"/>
+      <c r="E16" s="134" t="n"/>
+      <c r="F16" s="134" t="n"/>
+      <c r="G16" s="134" t="n"/>
+      <c r="H16" s="134" t="n"/>
+      <c r="I16" s="221" t="inlineStr">
+        <is>
+          <t>Other Energy Services</t>
         </is>
       </c>
       <c r="J16" s="221" t="inlineStr">
         <is>
-          <t>GHG emission reductions (ton CO2eq)</t>
-        </is>
-      </c>
-      <c r="K16" s="192" t="n"/>
-      <c r="L16" s="216" t="inlineStr">
-        <is>
-          <t>1.73 M Ton CO2eq</t>
-        </is>
+          <t>Number of people benefiting from livelihoods strengthened through solutions for management of natural resources, ecosystem services, chemicals and waste.</t>
+        </is>
+      </c>
+      <c r="K16" s="192" t="n">
+        <v>30268</v>
+      </c>
+      <c r="L16" s="192" t="n">
+        <v>110000</v>
       </c>
       <c r="M16" s="221" t="inlineStr">
         <is>
-          <t>The project’s ultimate goal is to implement structural changes in RAC manufacturing and servicing sectors for cleaner production and contribute to the quality of people's lives, through the protection of the ozone layer and reduction in direct and indirect emissions. This project will phase-out 310.78 kg HCFC-22 equivalent to 17.09 ODP tons, which is 66% of Bangladesh´s consumption of HCFCs in RAC manufacturing sector, contributing to the reduction target for 2025.
-Baseline: Consumption of ODS 47.22 ODP ton</t>
-        </is>
-      </c>
-      <c r="N16" s="176" t="inlineStr">
-        <is>
-          <t>MLF</t>
-        </is>
-      </c>
-      <c r="O16" s="221" t="n"/>
+          <t xml:space="preserve"> A total of 110,000 (women: 44,000, men: 66,000) people will be benefiting from livelihoods strengthened through solutions for management of natural resources, ecosystem services, chemicals and waste. 
+Access to other service (electric vehicles, industries efficiency etc.) - No of people will be benefiting from livelihoods strengthened through solutions for management of natural resources, ecosystem services, chemicals and waste. </t>
+        </is>
+      </c>
+      <c r="N16" s="193" t="n"/>
+      <c r="O16" s="194" t="n">
+        <v>0.4</v>
+      </c>
       <c r="P16" s="72" t="n"/>
       <c r="Q16" s="154" t="inlineStr">
         <is>
@@ -2649,40 +2681,36 @@
       <c r="X16" s="68" t="n"/>
     </row>
     <row r="17" ht="105" customFormat="1" customHeight="1" s="129">
-      <c r="A17" s="132" t="n"/>
-      <c r="B17" s="133" t="n"/>
-      <c r="C17" s="133" t="n"/>
-      <c r="D17" s="134" t="n"/>
-      <c r="E17" s="134" t="n"/>
-      <c r="F17" s="134" t="n"/>
-      <c r="G17" s="134" t="n"/>
-      <c r="H17" s="134" t="n"/>
+      <c r="A17" s="135" t="n"/>
+      <c r="B17" s="136" t="n"/>
+      <c r="C17" s="136" t="n"/>
+      <c r="D17" s="137" t="n"/>
+      <c r="E17" s="137" t="n"/>
+      <c r="F17" s="137" t="n"/>
+      <c r="G17" s="137" t="n"/>
+      <c r="H17" s="137" t="n"/>
       <c r="I17" s="221" t="inlineStr">
         <is>
-          <t>Other Energy Services</t>
+          <t>Small Enterprises</t>
         </is>
       </c>
       <c r="J17" s="221" t="inlineStr">
         <is>
-          <t>Number of people benefiting from livelihoods strengthened through solutions for management of natural resources, ecosystem services, chemicals and waste.</t>
-        </is>
-      </c>
-      <c r="K17" s="192" t="n">
-        <v>30268</v>
-      </c>
+          <t>Number of small enterprises benefiting from the project</t>
+        </is>
+      </c>
+      <c r="K17" s="221" t="n"/>
       <c r="L17" s="192" t="n">
-        <v>110000</v>
+        <v>6</v>
       </c>
       <c r="M17" s="221" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A total of 110,000 (women: 44,000, men: 66,000) people will be benefiting from livelihoods strengthened through solutions for management of natural resources, ecosystem services, chemicals and waste. 
-Access to other service (electric vehicles, industries efficiency etc.) - No of people will be benefiting from livelihoods strengthened through solutions for management of natural resources, ecosystem services, chemicals and waste. </t>
+          <t xml:space="preserve">The HPMP Stage II project is supporting six private sector small enterprises namely Unitech Products (BD) Ltd., Elite Hi-Tech Industries Ltd., AC Bazar Industry, Supreme Air Conditioning, Cooling Point Engineering Services and Walton Hi-Tech Industries Ltd with a funding support of  5,356,014.
+On comment column: Six private companies are getting benefits from the project.The objective of this project is to phase out of 17.09 ODP tones (1,730,798 CO2-eq tons) from 5 air conditioning and 1 chiller manufacturing/assembler enterprises. </t>
         </is>
       </c>
       <c r="N17" s="193" t="n"/>
-      <c r="O17" s="194" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="O17" s="221" t="n"/>
       <c r="P17" s="72" t="n"/>
       <c r="Q17" s="154" t="inlineStr">
         <is>
@@ -2698,35 +2726,34 @@
       <c r="X17" s="68" t="n"/>
     </row>
     <row r="18" ht="75" customHeight="1">
-      <c r="A18" s="135" t="n"/>
-      <c r="B18" s="136" t="n"/>
-      <c r="C18" s="136" t="n"/>
-      <c r="D18" s="137" t="n"/>
-      <c r="E18" s="137" t="n"/>
-      <c r="F18" s="137" t="n"/>
-      <c r="G18" s="137" t="n"/>
-      <c r="H18" s="137" t="n"/>
+      <c r="A18" s="138" t="n"/>
+      <c r="B18" s="139" t="n"/>
+      <c r="C18" s="139" t="n"/>
+      <c r="D18" s="140" t="n"/>
+      <c r="E18" s="140" t="n"/>
+      <c r="F18" s="140" t="n"/>
+      <c r="G18" s="140" t="n"/>
+      <c r="H18" s="140" t="n"/>
       <c r="I18" s="221" t="inlineStr">
         <is>
-          <t>Small Enterprises</t>
+          <t>Capacity Building Training</t>
         </is>
       </c>
       <c r="J18" s="221" t="inlineStr">
         <is>
-          <t>Number of small enterprises benefiting from the project</t>
+          <t xml:space="preserve">Number of individuals who participate in trainings for energy activities. </t>
         </is>
       </c>
       <c r="K18" s="221" t="n"/>
-      <c r="L18" s="192" t="n">
-        <v>6</v>
+      <c r="L18" s="221" t="n">
+        <v>1220</v>
       </c>
       <c r="M18" s="221" t="inlineStr">
         <is>
-          <t xml:space="preserve">The HPMP Stage II project is supporting six private sector small enterprises namely Unitech Products (BD) Ltd., Elite Hi-Tech Industries Ltd., AC Bazar Industry, Supreme Air Conditioning, Cooling Point Engineering Services and Walton Hi-Tech Industries Ltd with a funding support of  5,356,014.
-On comment column: Six private companies are getting benefits from the project.The objective of this project is to phase out of 17.09 ODP tones (1,730,798 CO2-eq tons) from 5 air conditioning and 1 chiller manufacturing/assembler enterprises. </t>
-        </is>
-      </c>
-      <c r="N18" s="193" t="n"/>
+          <t>The project has a comprehensive capacity development plan to capacitate 1220 individuals on new technology, policies and regulations implementation.</t>
+        </is>
+      </c>
+      <c r="N18" s="186" t="n"/>
       <c r="O18" s="221" t="n"/>
       <c r="P18" s="72" t="n"/>
       <c r="Q18" s="154" t="inlineStr">
@@ -2751,116 +2778,72 @@
       <c r="F19" s="140" t="n"/>
       <c r="G19" s="140" t="n"/>
       <c r="H19" s="140" t="n"/>
-      <c r="I19" s="221" t="inlineStr">
-        <is>
-          <t>Capacity Building Training</t>
-        </is>
-      </c>
-      <c r="J19" s="221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Number of individuals who participate in trainings for energy activities. </t>
-        </is>
-      </c>
-      <c r="K19" s="221" t="n"/>
-      <c r="L19" s="221" t="n">
-        <v>1220</v>
-      </c>
-      <c r="M19" s="221" t="inlineStr">
-        <is>
-          <t>The project has a comprehensive capacity development plan to capacitate 1220 individuals on new technology, policies and regulations implementation.</t>
-        </is>
-      </c>
-      <c r="N19" s="186" t="n"/>
-      <c r="O19" s="221" t="n"/>
-      <c r="P19" s="72" t="n"/>
-      <c r="Q19" s="154" t="inlineStr">
-        <is>
-          <t>Accelerating just energy transition</t>
-        </is>
-      </c>
-      <c r="R19" s="72" t="n"/>
-      <c r="S19" s="72" t="n"/>
-      <c r="T19" s="72" t="n"/>
-      <c r="U19" s="72" t="n"/>
-      <c r="V19" s="68" t="n"/>
-      <c r="W19" s="72" t="n"/>
-      <c r="X19" s="68" t="n"/>
+      <c r="I19" s="274" t="inlineStr">
+        <is>
+          <t>Energy (MW added)</t>
+        </is>
+      </c>
+      <c r="J19" s="274" t="inlineStr">
+        <is>
+          <t>Installed capacity in MW for access/productive-use outputs</t>
+        </is>
+      </c>
+      <c r="K19" s="275" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="275" t="n"/>
+      <c r="M19" s="274" t="n"/>
+      <c r="N19" s="276" t="n"/>
+      <c r="O19" s="274" t="n"/>
+      <c r="P19" s="277" t="n"/>
+      <c r="Q19" s="278" t="n"/>
+      <c r="R19" s="277" t="n"/>
+      <c r="S19" s="277" t="n"/>
+      <c r="T19" s="277" t="n"/>
+      <c r="U19" s="277" t="n"/>
+      <c r="V19" s="279" t="n"/>
+      <c r="W19" s="277" t="n"/>
+      <c r="X19" s="279" t="n"/>
     </row>
     <row r="20" ht="106.5" customFormat="1" customHeight="1" s="129">
-      <c r="A20" s="138" t="n"/>
-      <c r="B20" s="139" t="n"/>
-      <c r="C20" s="139" t="n"/>
-      <c r="D20" s="140" t="n"/>
-      <c r="E20" s="140" t="n"/>
-      <c r="F20" s="140" t="n"/>
-      <c r="G20" s="140" t="n"/>
-      <c r="H20" s="140" t="n"/>
-      <c r="I20" s="286" t="inlineStr">
-        <is>
-          <t>Energy (MW added)</t>
-        </is>
-      </c>
-      <c r="J20" s="286" t="inlineStr">
-        <is>
-          <t>Installed capacity in MW for access/productive-use outputs</t>
-        </is>
-      </c>
-      <c r="K20" s="286" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="278" t="n"/>
-      <c r="M20" s="278" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
-      <c r="N20" s="287" t="n"/>
-      <c r="O20" s="286" t="n"/>
-      <c r="P20" s="281" t="n"/>
-      <c r="Q20" s="282" t="n"/>
-      <c r="R20" s="281" t="n"/>
-      <c r="S20" s="281" t="n"/>
-      <c r="T20" s="281" t="n"/>
-      <c r="U20" s="281" t="n"/>
-      <c r="V20" s="283" t="n"/>
-      <c r="W20" s="281" t="n"/>
-      <c r="X20" s="283" t="n"/>
-    </row>
-    <row r="21" ht="120" customFormat="1" customHeight="1" s="129">
-      <c r="A21" s="195" t="inlineStr">
+      <c r="A20" s="195" t="inlineStr">
         <is>
           <t>134586</t>
         </is>
       </c>
-      <c r="B21" s="141" t="inlineStr">
+      <c r="B20" s="141" t="inlineStr">
         <is>
           <t>Climate Promise: From Pledge to Impact</t>
         </is>
       </c>
-      <c r="C21" s="221" t="n"/>
-      <c r="D21" s="192" t="n">
+      <c r="C20" s="221" t="inlineStr">
+        <is>
+          <t>https://open.undp.org/projects/00093849</t>
+        </is>
+      </c>
+      <c r="D20" s="192" t="n">
         <v>475000</v>
       </c>
-      <c r="E21" s="285" t="n"/>
-      <c r="F21" s="285" t="n"/>
-      <c r="G21" s="285" t="n"/>
-      <c r="H21" s="192" t="inlineStr">
+      <c r="E20" s="273" t="n"/>
+      <c r="F20" s="273" t="n"/>
+      <c r="G20" s="273" t="n"/>
+      <c r="H20" s="192" t="inlineStr">
         <is>
           <t>Non-VF</t>
         </is>
       </c>
-      <c r="I21" s="221" t="inlineStr">
+      <c r="I20" s="221" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
         </is>
       </c>
-      <c r="J21" s="221" t="inlineStr">
+      <c r="J20" s="221" t="inlineStr">
         <is>
           <t>Number of low carbon policy and strategy</t>
         </is>
       </c>
-      <c r="K21" s="221" t="n"/>
-      <c r="L21" s="219" t="inlineStr">
+      <c r="K20" s="221" t="n"/>
+      <c r="L20" s="219" t="inlineStr">
         <is>
           <t xml:space="preserve">Policy Recommendation on following 5 points:
 1.	Climate finance strategy &amp; NDC investment plan
@@ -2871,7 +2854,7 @@
  </t>
         </is>
       </c>
-      <c r="M21" s="221" t="inlineStr">
+      <c r="M20" s="221" t="inlineStr">
         <is>
           <t xml:space="preserve">Global project
 Enhanced transparency framework and data transparency system for Paris agreement
@@ -2879,96 +2862,146 @@
 National strategy and investment plan for achieving NET ZERO </t>
         </is>
       </c>
-      <c r="N21" s="221" t="inlineStr">
+      <c r="N20" s="221" t="inlineStr">
         <is>
           <t>Government of Germany</t>
         </is>
       </c>
-      <c r="O21" s="218" t="n">
+      <c r="O20" s="218" t="n">
         <v>0.5</v>
       </c>
-      <c r="P21" s="72" t="n"/>
-      <c r="Q21" s="154" t="inlineStr">
+      <c r="P20" s="72" t="n"/>
+      <c r="Q20" s="154" t="inlineStr">
         <is>
           <t>Accelerating just energy transition</t>
         </is>
       </c>
-      <c r="R21" s="72" t="inlineStr">
+      <c r="R20" s="72" t="inlineStr">
         <is>
           <t>Renewable Energy</t>
         </is>
       </c>
-      <c r="S21" s="72" t="n"/>
-      <c r="T21" s="72" t="inlineStr">
+      <c r="S20" s="72" t="n"/>
+      <c r="T20" s="72" t="inlineStr">
         <is>
           <t>NDC Support</t>
         </is>
       </c>
-      <c r="U21" s="72" t="inlineStr">
+      <c r="U20" s="72" t="inlineStr">
         <is>
           <t>Decarbonization</t>
         </is>
       </c>
-      <c r="V21" s="68" t="n"/>
-      <c r="W21" s="72" t="inlineStr">
+      <c r="V20" s="68" t="n"/>
+      <c r="W20" s="72" t="inlineStr">
         <is>
           <t>National</t>
         </is>
       </c>
-      <c r="X21" s="68" t="n"/>
-    </row>
-    <row r="22" ht="90" customFormat="1" customHeight="1" s="129">
-      <c r="A22" s="221" t="n">
+      <c r="X20" s="68" t="n"/>
+    </row>
+    <row r="21" ht="120" customFormat="1" customHeight="1" s="129">
+      <c r="A21" s="221" t="n">
         <v>93849</v>
       </c>
-      <c r="B22" s="141" t="inlineStr">
+      <c r="B21" s="141" t="inlineStr">
         <is>
           <t>Improved Cooking Stoves in CHT area (under A2I project)</t>
         </is>
       </c>
-      <c r="C22" s="207" t="inlineStr">
+      <c r="C21" s="207" t="inlineStr">
         <is>
           <t>https://open.undp.org/projects/00093849</t>
         </is>
       </c>
-      <c r="D22" s="192" t="n">
+      <c r="D21" s="192" t="n">
         <v>150000</v>
       </c>
-      <c r="E22" s="285" t="n"/>
-      <c r="F22" s="285" t="n"/>
-      <c r="G22" s="285" t="n"/>
-      <c r="H22" s="192" t="inlineStr">
+      <c r="E21" s="273" t="n"/>
+      <c r="F21" s="273" t="n"/>
+      <c r="G21" s="273" t="n"/>
+      <c r="H21" s="192" t="inlineStr">
         <is>
           <t>Non-VF</t>
         </is>
       </c>
-      <c r="I22" s="221" t="inlineStr">
+      <c r="I21" s="221" t="inlineStr">
         <is>
           <t>Clean Cooking</t>
         </is>
       </c>
-      <c r="J22" s="221" t="inlineStr">
+      <c r="J21" s="221" t="inlineStr">
         <is>
           <t>Number of households using improved cooking  stove</t>
         </is>
       </c>
-      <c r="K22" s="221" t="n">
+      <c r="K21" s="221" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="221">
-        <f>5000*4.5</f>
-        <v/>
-      </c>
-      <c r="M22" s="221" t="inlineStr">
+      <c r="L21" s="221" t="n">
+        <v>22500</v>
+      </c>
+      <c r="M21" s="221" t="inlineStr">
         <is>
           <t>local Villages of the CHT area faces serious health related problems due to high GHG gas emitting cooking stoves that are also fuel inefficient. A2I has been working with local innovators to develop energy efficient fuel stoves that are also environmentally friendly for the residents of that area.
 15-25% of households using improved cooking stove
 On comment column: About 5,000 Household got the benefits</t>
         </is>
       </c>
+      <c r="N21" s="172" t="inlineStr">
+        <is>
+          <t>Government of Bangladesh-50 million, Other donors (Gate Foundation, FB, Vital strategy, etc.): 9 million)</t>
+        </is>
+      </c>
+      <c r="O21" s="221" t="n"/>
+      <c r="P21" s="72" t="n"/>
+      <c r="Q21" s="154" t="inlineStr">
+        <is>
+          <t>Accelerating just energy transition</t>
+        </is>
+      </c>
+      <c r="R21" s="72" t="n"/>
+      <c r="S21" s="72" t="n"/>
+      <c r="T21" s="72" t="n"/>
+      <c r="U21" s="72" t="n"/>
+      <c r="V21" s="68" t="n"/>
+      <c r="W21" s="72" t="n"/>
+      <c r="X21" s="68" t="n"/>
+    </row>
+    <row r="22" ht="90" customFormat="1" customHeight="1" s="129">
+      <c r="A22" s="221" t="n"/>
+      <c r="B22" s="221" t="n"/>
+      <c r="C22" s="192" t="n"/>
+      <c r="D22" s="192" t="n"/>
+      <c r="E22" s="192" t="n"/>
+      <c r="F22" s="192" t="n"/>
+      <c r="G22" s="192" t="n"/>
+      <c r="H22" s="192" t="n"/>
+      <c r="I22" s="221" t="inlineStr">
+        <is>
+          <t>Water Services</t>
+        </is>
+      </c>
+      <c r="J22" s="221" t="inlineStr">
+        <is>
+          <t>% of people with restrictive access to household water in remote CHT areas</t>
+        </is>
+      </c>
+      <c r="K22" s="194" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L22" s="221" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M22" s="221" t="inlineStr">
+        <is>
+          <t>The southeastern part of Bangladesh is extensively hilly region and the people living here are not habituated to use modern water technologies. So, they have to collect water from natural sources particularly from the downhill springs for drinking, household chores and irrigation. To solve the water crisis of the communities at these regions, A2I has developed a water lifting system using Hydraulic Ram Pump to supply water from downhill source to uphill utilizing the water hammer effect for drinking and irrigation purposes at Bandarban, Bangladesh.
+On comment column: About 5000 farmers get benefits</t>
+        </is>
+      </c>
       <c r="N22" s="172" t="inlineStr">
         <is>
-          <t>Government of Bangladesh-50 million, Other donors (Gate Foundation, FB, Vital strategy, etc.): 9 million)</t>
+          <t>Govt of Bangladesh-50 million, Other donors (Gate Foundation, FB, Vital strategy, etc.): 9 million)</t>
         </is>
       </c>
       <c r="O22" s="221" t="n"/>
@@ -2989,7 +3022,7 @@
     <row r="23" ht="144" customHeight="1">
       <c r="A23" s="221" t="n"/>
       <c r="B23" s="221" t="n"/>
-      <c r="C23" s="192" t="n"/>
+      <c r="C23" s="221" t="n"/>
       <c r="D23" s="192" t="n"/>
       <c r="E23" s="192" t="n"/>
       <c r="F23" s="192" t="n"/>
@@ -2997,24 +3030,23 @@
       <c r="H23" s="192" t="n"/>
       <c r="I23" s="221" t="inlineStr">
         <is>
-          <t>Water Services</t>
+          <t>Policy or Regulatory Framework</t>
         </is>
       </c>
       <c r="J23" s="221" t="inlineStr">
         <is>
-          <t>% of people with restrictive access to household water in remote CHT areas</t>
-        </is>
-      </c>
-      <c r="K23" s="194" t="n">
-        <v>0.7</v>
+          <t>Number of Research innovation centre in Bangladesh</t>
+        </is>
+      </c>
+      <c r="K23" s="221" t="n">
+        <v>0</v>
       </c>
       <c r="L23" s="221" t="n">
-        <v>5000</v>
+        <v>1</v>
       </c>
       <c r="M23" s="221" t="inlineStr">
         <is>
-          <t>The southeastern part of Bangladesh is extensively hilly region and the people living here are not habituated to use modern water technologies. So, they have to collect water from natural sources particularly from the downhill springs for drinking, household chores and irrigation. To solve the water crisis of the communities at these regions, A2I has developed a water lifting system using Hydraulic Ram Pump to supply water from downhill source to uphill utilizing the water hammer effect for drinking and irrigation purposes at Bandarban, Bangladesh.
-On comment column: About 5000 farmers get benefits</t>
+          <t>A2I is in the process of establishing an energy and environment RIC, that will be responsible to output innovative solutions to the energy ecosystem through research.</t>
         </is>
       </c>
       <c r="N23" s="172" t="inlineStr">
@@ -3029,23 +3061,39 @@
           <t>Accelerating just energy transition</t>
         </is>
       </c>
-      <c r="R23" s="72" t="n"/>
+      <c r="R23" s="72" t="inlineStr">
+        <is>
+          <t>Renewable Energy</t>
+        </is>
+      </c>
       <c r="S23" s="72" t="n"/>
-      <c r="T23" s="72" t="n"/>
-      <c r="U23" s="72" t="n"/>
+      <c r="T23" s="72" t="inlineStr">
+        <is>
+          <t>Incentives and Support</t>
+        </is>
+      </c>
+      <c r="U23" s="72" t="inlineStr">
+        <is>
+          <t>Research &amp; Innovation</t>
+        </is>
+      </c>
       <c r="V23" s="68" t="n"/>
-      <c r="W23" s="72" t="n"/>
+      <c r="W23" s="72" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
       <c r="X23" s="68" t="n"/>
     </row>
     <row r="24" ht="121.5" customFormat="1" customHeight="1" s="129">
       <c r="A24" s="221" t="n"/>
       <c r="B24" s="221" t="n"/>
-      <c r="C24" s="221" t="n"/>
-      <c r="D24" s="192" t="n"/>
-      <c r="E24" s="192" t="n"/>
-      <c r="F24" s="192" t="n"/>
-      <c r="G24" s="192" t="n"/>
-      <c r="H24" s="192" t="n"/>
+      <c r="C24" s="192" t="n"/>
+      <c r="D24" s="196" t="n"/>
+      <c r="E24" s="196" t="n"/>
+      <c r="F24" s="196" t="n"/>
+      <c r="G24" s="196" t="n"/>
+      <c r="H24" s="196" t="n"/>
       <c r="I24" s="221" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
@@ -3053,18 +3101,18 @@
       </c>
       <c r="J24" s="221" t="inlineStr">
         <is>
-          <t>Number of Research innovation centre in Bangladesh</t>
+          <t>Number of policy support provided relating to energy and environment</t>
         </is>
       </c>
       <c r="K24" s="221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="221" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M24" s="221" t="inlineStr">
         <is>
-          <t>A2I is in the process of establishing an energy and environment RIC, that will be responsible to output innovative solutions to the energy ecosystem through research.</t>
+          <t>A2I has been working with various goverrnment bodies to develop registration policies regarding the Energy and Environment sector.</t>
         </is>
       </c>
       <c r="N24" s="172" t="inlineStr">
@@ -3081,18 +3129,18 @@
       </c>
       <c r="R24" s="72" t="inlineStr">
         <is>
-          <t>Renewable Energy</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="S24" s="72" t="n"/>
       <c r="T24" s="72" t="inlineStr">
         <is>
-          <t>Incentives and Support</t>
+          <t>National Strategy</t>
         </is>
       </c>
       <c r="U24" s="72" t="inlineStr">
         <is>
-          <t>Research &amp; Innovation</t>
+          <t>Decarbonization</t>
         </is>
       </c>
       <c r="V24" s="68" t="n"/>
@@ -3106,7 +3154,7 @@
     <row r="25" ht="275.25" customHeight="1">
       <c r="A25" s="221" t="n"/>
       <c r="B25" s="221" t="n"/>
-      <c r="C25" s="192" t="n"/>
+      <c r="C25" s="130" t="n"/>
       <c r="D25" s="196" t="n"/>
       <c r="E25" s="196" t="n"/>
       <c r="F25" s="196" t="n"/>
@@ -3114,23 +3162,24 @@
       <c r="H25" s="196" t="n"/>
       <c r="I25" s="221" t="inlineStr">
         <is>
-          <t>Policy or Regulatory Framework</t>
+          <t>Education Services</t>
         </is>
       </c>
       <c r="J25" s="221" t="inlineStr">
         <is>
-          <t>Number of policy support provided relating to energy and environment</t>
+          <t>No. of students that are using the Multimedia Classroom</t>
         </is>
       </c>
       <c r="K25" s="221" t="n">
-        <v>1</v>
+        <v>326</v>
       </c>
       <c r="L25" s="221" t="n">
-        <v>3</v>
+        <v>2000</v>
       </c>
       <c r="M25" s="221" t="inlineStr">
         <is>
-          <t>A2I has been working with various goverrnment bodies to develop registration policies regarding the Energy and Environment sector.</t>
+          <t>As we progress through the generations, Technological advancement is happening at an exponential rate. To fully support our youth, technological advancements are also essential in the education sector. On top of that the Bangladeshi Government has taken the initiative to engulf the education stream of Bangladesh under one digital format. To accomodate this initiative, we developed a highly efficient Multimedia Classroom system that is completely powered through solar energy. With this innovation, we can empower our local youth in rural areas to recieve the same education as urban areas.
+On comment column: About 2000 students get benefits</t>
         </is>
       </c>
       <c r="N25" s="172" t="inlineStr">
@@ -3145,152 +3194,81 @@
           <t>Accelerating just energy transition</t>
         </is>
       </c>
-      <c r="R25" s="72" t="inlineStr">
-        <is>
-          <t>Overall</t>
-        </is>
-      </c>
+      <c r="R25" s="72" t="n"/>
       <c r="S25" s="72" t="n"/>
-      <c r="T25" s="72" t="inlineStr">
-        <is>
-          <t>National Strategy</t>
-        </is>
-      </c>
-      <c r="U25" s="72" t="inlineStr">
-        <is>
-          <t>Decarbonization</t>
-        </is>
-      </c>
+      <c r="T25" s="72" t="n"/>
+      <c r="U25" s="72" t="n"/>
       <c r="V25" s="68" t="n"/>
-      <c r="W25" s="72" t="inlineStr">
-        <is>
-          <t>National</t>
-        </is>
-      </c>
+      <c r="W25" s="72" t="n"/>
       <c r="X25" s="68" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="221" t="n"/>
-      <c r="B26" s="221" t="n"/>
-      <c r="C26" s="130" t="n"/>
-      <c r="D26" s="196" t="n"/>
-      <c r="E26" s="196" t="n"/>
-      <c r="F26" s="196" t="n"/>
-      <c r="G26" s="196" t="n"/>
-      <c r="H26" s="196" t="n"/>
-      <c r="I26" s="221" t="inlineStr">
-        <is>
-          <t>Education Services</t>
-        </is>
-      </c>
-      <c r="J26" s="221" t="inlineStr">
-        <is>
-          <t>No. of students that are using the Multimedia Classroom</t>
-        </is>
-      </c>
-      <c r="K26" s="221" t="n">
-        <v>326</v>
-      </c>
-      <c r="L26" s="221" t="n">
-        <v>2000</v>
-      </c>
-      <c r="M26" s="221" t="inlineStr">
-        <is>
-          <t>As we progress through the generations, Technological advancement is happening at an exponential rate. To fully support our youth, technological advancements are also essential in the education sector. On top of that the Bangladeshi Government has taken the initiative to engulf the education stream of Bangladesh under one digital format. To accomodate this initiative, we developed a highly efficient Multimedia Classroom system that is completely powered through solar energy. With this innovation, we can empower our local youth in rural areas to recieve the same education as urban areas.
-On comment column: About 2000 students get benefits</t>
-        </is>
-      </c>
-      <c r="N26" s="172" t="inlineStr">
-        <is>
-          <t>Govt of Bangladesh-50 million, Other donors (Gate Foundation, FB, Vital strategy, etc.): 9 million)</t>
-        </is>
-      </c>
-      <c r="O26" s="221" t="n"/>
-      <c r="P26" s="72" t="n"/>
-      <c r="Q26" s="154" t="inlineStr">
-        <is>
-          <t>Accelerating just energy transition</t>
-        </is>
-      </c>
-      <c r="R26" s="72" t="n"/>
-      <c r="S26" s="72" t="n"/>
-      <c r="T26" s="72" t="n"/>
-      <c r="U26" s="72" t="n"/>
-      <c r="V26" s="68" t="n"/>
-      <c r="W26" s="72" t="n"/>
-      <c r="X26" s="68" t="n"/>
+      <c r="A26" s="274" t="n"/>
+      <c r="B26" s="274" t="n"/>
+      <c r="C26" s="280" t="n"/>
+      <c r="D26" s="281" t="n"/>
+      <c r="E26" s="281" t="n"/>
+      <c r="F26" s="281" t="n"/>
+      <c r="G26" s="281" t="n"/>
+      <c r="H26" s="281" t="n"/>
+      <c r="I26" s="274" t="inlineStr">
+        <is>
+          <t>Energy (MW added)</t>
+        </is>
+      </c>
+      <c r="J26" s="274" t="inlineStr">
+        <is>
+          <t>Installed capacity in MW for access/productive-use outputs</t>
+        </is>
+      </c>
+      <c r="K26" s="275" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="275" t="n"/>
+      <c r="M26" s="274" t="n"/>
+      <c r="N26" s="172" t="n"/>
+      <c r="O26" s="274" t="n"/>
+      <c r="P26" s="277" t="n"/>
+      <c r="Q26" s="278" t="n"/>
+      <c r="R26" s="277" t="n"/>
+      <c r="S26" s="277" t="n"/>
+      <c r="T26" s="277" t="n"/>
+      <c r="U26" s="277" t="n"/>
+      <c r="V26" s="279" t="n"/>
+      <c r="W26" s="277" t="n"/>
+      <c r="X26" s="279" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="286" t="n"/>
-      <c r="B27" s="286" t="n"/>
-      <c r="C27" s="288" t="n"/>
-      <c r="D27" s="289" t="n"/>
-      <c r="E27" s="289" t="n"/>
-      <c r="F27" s="289" t="n"/>
-      <c r="G27" s="289" t="n"/>
-      <c r="H27" s="289" t="n"/>
-      <c r="I27" s="286" t="inlineStr">
-        <is>
-          <t>Energy (MW added)</t>
-        </is>
-      </c>
-      <c r="J27" s="286" t="inlineStr">
-        <is>
-          <t>Installed capacity in MW for access/productive-use outputs</t>
-        </is>
-      </c>
-      <c r="K27" s="286" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="278" t="n"/>
-      <c r="M27" s="278" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
-      <c r="N27" s="172" t="n"/>
-      <c r="O27" s="286" t="n"/>
-      <c r="P27" s="281" t="n"/>
-      <c r="Q27" s="282" t="n"/>
-      <c r="R27" s="281" t="n"/>
-      <c r="S27" s="281" t="n"/>
-      <c r="T27" s="281" t="n"/>
-      <c r="U27" s="281" t="n"/>
-      <c r="V27" s="283" t="n"/>
-      <c r="W27" s="281" t="n"/>
-      <c r="X27" s="283" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="221" t="n">
+      <c r="A27" s="221" t="n">
         <v>105918</v>
       </c>
-      <c r="B28" s="221" t="inlineStr">
+      <c r="B27" s="221" t="inlineStr">
         <is>
           <t>Bangladesh: First Biennial Update Report to the UNFCCC</t>
         </is>
       </c>
-      <c r="C28" s="208" t="inlineStr">
+      <c r="C27" s="208" t="inlineStr">
         <is>
           <t>https://open.undp.org/projects/00105918</t>
         </is>
       </c>
-      <c r="D28" s="192" t="n">
+      <c r="D27" s="192" t="n">
         <v>489000</v>
       </c>
-      <c r="E28" s="285" t="n"/>
-      <c r="F28" s="285" t="n"/>
-      <c r="G28" s="285" t="n"/>
-      <c r="H28" s="192" t="inlineStr">
+      <c r="E27" s="273" t="n"/>
+      <c r="F27" s="273" t="n"/>
+      <c r="G27" s="273" t="n"/>
+      <c r="H27" s="192" t="inlineStr">
         <is>
           <t>Non-VF</t>
         </is>
       </c>
-      <c r="I28" s="221" t="inlineStr">
+      <c r="I27" s="221" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
         </is>
       </c>
-      <c r="J28" s="220" t="inlineStr">
+      <c r="J27" s="220" t="inlineStr">
         <is>
           <t xml:space="preserve">1. GHG inventory for energy sector
 2. Develop emission scenario until 2041
@@ -3300,7 +3278,7 @@
 </t>
         </is>
       </c>
-      <c r="K28" s="220" t="inlineStr">
+      <c r="K27" s="220" t="inlineStr">
         <is>
           <t xml:space="preserve">1. GHG inventory until 2012 is prepared under 3 National Communications.
 2. Emission Scenario until 2030 is prepared in 3 NCs, NDC, Updated NDC, MRV developed in NDC.
@@ -3310,8 +3288,8 @@
 </t>
         </is>
       </c>
-      <c r="L28" s="221" t="n"/>
-      <c r="M28" s="221" t="inlineStr">
+      <c r="L27" s="221" t="n"/>
+      <c r="M27" s="221" t="inlineStr">
         <is>
           <t>BUR1 project is supporting government to prepare First Biennial Update Report. Through this project, country will get the updated energy circumstances, emission inventory until 2019 and emission scenario until 2041 from energy sector, updated MRV system and grid emission factor.   
 1. GHG inventory until 2019 is prepared.
@@ -3321,50 +3299,46 @@
 5. Gaps and constraints indentified</t>
         </is>
       </c>
-      <c r="N28" s="172" t="inlineStr">
+      <c r="N27" s="172" t="inlineStr">
         <is>
           <t>GEF</t>
         </is>
       </c>
-      <c r="O28" s="218" t="n">
+      <c r="O27" s="218" t="n">
         <v>0.5</v>
       </c>
-      <c r="P28" s="72" t="n"/>
-      <c r="Q28" s="154" t="inlineStr">
+      <c r="P27" s="72" t="n"/>
+      <c r="Q27" s="154" t="inlineStr">
         <is>
           <t>Accelerating just energy transition</t>
         </is>
       </c>
-      <c r="R28" s="72" t="inlineStr">
+      <c r="R27" s="72" t="inlineStr">
         <is>
           <t>Renewable Energy</t>
         </is>
       </c>
-      <c r="S28" s="72" t="n"/>
-      <c r="T28" s="72" t="inlineStr">
+      <c r="S27" s="72" t="n"/>
+      <c r="T27" s="72" t="inlineStr">
         <is>
           <t>NDC Support</t>
         </is>
       </c>
-      <c r="U28" s="72" t="inlineStr">
+      <c r="U27" s="72" t="inlineStr">
         <is>
           <t>Decarbonization</t>
         </is>
       </c>
-      <c r="V28" s="68" t="n"/>
-      <c r="W28" s="72" t="inlineStr">
+      <c r="V27" s="68" t="n"/>
+      <c r="W27" s="72" t="inlineStr">
         <is>
           <t>National</t>
         </is>
       </c>
-      <c r="X28" s="68" t="n"/>
+      <c r="X27" s="68" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="I5:I8"/>
-  </mergeCells>
-  <dataValidations count="12">
+  <dataValidations count="10">
     <dataValidation sqref="Q2:Q25" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
@@ -3395,15 +3369,13 @@
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" display="https://open.undp.org/projects/00117898" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" display="HPMP II (AC Unit)" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -3513,7 +3485,7 @@
         </is>
       </c>
       <c r="C2" s="60" t="n"/>
-      <c r="D2" s="290" t="inlineStr">
+      <c r="D2" s="282" t="inlineStr">
         <is>
           <t>US$3767810</t>
         </is>
@@ -3538,7 +3510,7 @@
           <t>No. of waste to energy facilities, rooftop PV, energy efficiency in building, etc</t>
         </is>
       </c>
-      <c r="I2" s="291" t="inlineStr">
+      <c r="I2" s="283" t="inlineStr">
         <is>
           <t xml:space="preserve">The project addresses the development challenge of increased negative economic and environmental impacts from fossil use and other non-sustainable practices in urban areas by enabling low-carbon interventions and investments in energy-efficiency (EE) and renewable energy (RE) in buildings and built environment and to support urban development in Bangladesh. 
 GHG emission reduction of 1.573 million tons of tCO2 (lifetime) resulting from EE, RE and W2E interventions (Direct) and 4.718 million tons of CO2 as consequential (indirect) emission reduction after the project’s end. About 600 Kw of energy generation is expected.
@@ -3563,10 +3535,10 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="273" t="n"/>
-      <c r="B3" s="273" t="n"/>
-      <c r="C3" s="273" t="n"/>
-      <c r="D3" s="273" t="n"/>
+      <c r="A3" s="284" t="n"/>
+      <c r="B3" s="284" t="n"/>
+      <c r="C3" s="284" t="n"/>
+      <c r="D3" s="284" t="n"/>
       <c r="E3" s="65" t="inlineStr">
         <is>
           <t>Policy and Regulatory Frameworks</t>
@@ -3579,17 +3551,17 @@
           <t>No. of low carbon policy, guideline and standard</t>
         </is>
       </c>
-      <c r="I3" s="273" t="n"/>
-      <c r="J3" s="273" t="n"/>
-      <c r="K3" s="273" t="n"/>
-      <c r="L3" s="273" t="n"/>
+      <c r="I3" s="284" t="n"/>
+      <c r="J3" s="284" t="n"/>
+      <c r="K3" s="284" t="n"/>
+      <c r="L3" s="284" t="n"/>
       <c r="M3" s="119" t="n"/>
     </row>
     <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="274" t="n"/>
-      <c r="B4" s="274" t="n"/>
-      <c r="C4" s="274" t="n"/>
-      <c r="D4" s="274" t="n"/>
+      <c r="A4" s="285" t="n"/>
+      <c r="B4" s="285" t="n"/>
+      <c r="C4" s="285" t="n"/>
+      <c r="D4" s="285" t="n"/>
       <c r="E4" s="67" t="inlineStr">
         <is>
           <t>GHG Emission Reduction</t>
@@ -3604,10 +3576,10 @@
           <t>GHG Emission Reduction target in updated NDC</t>
         </is>
       </c>
-      <c r="I4" s="274" t="n"/>
-      <c r="J4" s="273" t="n"/>
-      <c r="K4" s="273" t="n"/>
-      <c r="L4" s="273" t="n"/>
+      <c r="I4" s="285" t="n"/>
+      <c r="J4" s="284" t="n"/>
+      <c r="K4" s="284" t="n"/>
+      <c r="L4" s="284" t="n"/>
       <c r="M4" s="119" t="n"/>
     </row>
     <row r="5" ht="75" customFormat="1" customHeight="1" s="92">
@@ -3646,9 +3618,9 @@
 Assessment of Regulatory Framework and Market development for EV and EVCS, Recycling and Disposal of Batteries with strategy for environmentally sound manufacturing of EV and EV Components;Preparation of PPP business models for local charging stations and installation of hybrid grid-solar charging stations as well as, Battery recycling and reuse in Bangladesh</t>
         </is>
       </c>
-      <c r="J5" s="273" t="n"/>
-      <c r="K5" s="273" t="n"/>
-      <c r="L5" s="273" t="n"/>
+      <c r="J5" s="284" t="n"/>
+      <c r="K5" s="284" t="n"/>
+      <c r="L5" s="284" t="n"/>
       <c r="M5" s="118" t="inlineStr">
         <is>
           <t>It is expected that 100,000 people will be benefitted</t>
@@ -3656,8 +3628,8 @@
       </c>
     </row>
     <row r="6" ht="37.5" customHeight="1">
-      <c r="A6" s="273" t="n"/>
-      <c r="B6" s="273" t="n"/>
+      <c r="A6" s="284" t="n"/>
+      <c r="B6" s="284" t="n"/>
       <c r="C6" s="60" t="n"/>
       <c r="D6" s="66" t="n"/>
       <c r="E6" s="67" t="inlineStr">
@@ -3674,15 +3646,15 @@
           <t xml:space="preserve">GHG Emission Reduction target </t>
         </is>
       </c>
-      <c r="I6" s="273" t="n"/>
-      <c r="J6" s="273" t="n"/>
-      <c r="K6" s="273" t="n"/>
-      <c r="L6" s="273" t="n"/>
+      <c r="I6" s="284" t="n"/>
+      <c r="J6" s="284" t="n"/>
+      <c r="K6" s="284" t="n"/>
+      <c r="L6" s="284" t="n"/>
       <c r="M6" s="119" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="274" t="n"/>
-      <c r="B7" s="274" t="n"/>
+      <c r="A7" s="285" t="n"/>
+      <c r="B7" s="285" t="n"/>
       <c r="C7" s="60" t="n"/>
       <c r="D7" s="66" t="n"/>
       <c r="E7" s="65" t="inlineStr">
@@ -3699,10 +3671,10 @@
           <t>100 persons will be trained on operation and maintenance of charging infrastructure (e-Buses and 2-3-wheeler station; 100 persons will be trained on environmentally sound and safe handling and recycling of batteries and verification</t>
         </is>
       </c>
-      <c r="I7" s="274" t="n"/>
-      <c r="J7" s="273" t="n"/>
-      <c r="K7" s="273" t="n"/>
-      <c r="L7" s="273" t="n"/>
+      <c r="I7" s="285" t="n"/>
+      <c r="J7" s="284" t="n"/>
+      <c r="K7" s="284" t="n"/>
+      <c r="L7" s="284" t="n"/>
       <c r="M7" s="119" t="n"/>
     </row>
     <row r="8" ht="45" customFormat="1" customHeight="1" s="99">
@@ -3747,8 +3719,8 @@
           <t>Adaptation Fund</t>
         </is>
       </c>
-      <c r="K8" s="273" t="n"/>
-      <c r="L8" s="273" t="n"/>
+      <c r="K8" s="284" t="n"/>
+      <c r="L8" s="284" t="n"/>
       <c r="M8" s="120" t="inlineStr">
         <is>
           <t>It is expected that about 1MW energy will be generated</t>
@@ -3756,8 +3728,8 @@
       </c>
     </row>
     <row r="9" ht="75" customFormat="1" customHeight="1" s="13">
-      <c r="A9" s="273" t="n"/>
-      <c r="B9" s="273" t="n"/>
+      <c r="A9" s="284" t="n"/>
+      <c r="B9" s="284" t="n"/>
       <c r="C9" s="63" t="n"/>
       <c r="D9" s="235" t="n"/>
       <c r="E9" s="63" t="inlineStr">
@@ -3782,13 +3754,13 @@
         </is>
       </c>
       <c r="J9" s="63" t="n"/>
-      <c r="K9" s="273" t="n"/>
-      <c r="L9" s="273" t="n"/>
+      <c r="K9" s="284" t="n"/>
+      <c r="L9" s="284" t="n"/>
       <c r="M9" s="121" t="n"/>
     </row>
     <row r="10" ht="75" customFormat="1" customHeight="1" s="13">
-      <c r="A10" s="274" t="n"/>
-      <c r="B10" s="274" t="n"/>
+      <c r="A10" s="285" t="n"/>
+      <c r="B10" s="285" t="n"/>
       <c r="C10" s="63" t="n"/>
       <c r="D10" s="235" t="n"/>
       <c r="E10" s="63" t="inlineStr">
@@ -3814,8 +3786,8 @@
         </is>
       </c>
       <c r="J10" s="63" t="n"/>
-      <c r="K10" s="274" t="n"/>
-      <c r="L10" s="274" t="n"/>
+      <c r="K10" s="285" t="n"/>
+      <c r="L10" s="285" t="n"/>
       <c r="M10" s="121" t="n"/>
     </row>
     <row r="11" ht="180" customHeight="1">
@@ -3870,8 +3842,8 @@
       <c r="M11" s="119" t="n"/>
     </row>
     <row r="12" ht="105" customFormat="1" customHeight="1" s="92">
-      <c r="A12" s="273" t="n"/>
-      <c r="B12" s="273" t="n"/>
+      <c r="A12" s="284" t="n"/>
+      <c r="B12" s="284" t="n"/>
       <c r="C12" s="100" t="n"/>
       <c r="D12" s="101" t="inlineStr">
         <is>
@@ -3918,8 +3890,8 @@
       </c>
     </row>
     <row r="13" ht="90" customFormat="1" customHeight="1" s="92">
-      <c r="A13" s="274" t="n"/>
-      <c r="B13" s="274" t="n"/>
+      <c r="A13" s="285" t="n"/>
+      <c r="B13" s="285" t="n"/>
       <c r="C13" s="100" t="n"/>
       <c r="D13" s="101" t="inlineStr">
         <is>
@@ -4021,7 +3993,7 @@
     </row>
     <row r="15" ht="315" customHeight="1">
       <c r="A15" s="235" t="n"/>
-      <c r="B15" s="273" t="n"/>
+      <c r="B15" s="284" t="n"/>
       <c r="C15" s="75" t="inlineStr">
         <is>
           <t>HPMP II (AC Unit); HPMP II (PMU)</t>
@@ -4066,8 +4038,8 @@
       <c r="M15" s="119" t="n"/>
     </row>
     <row r="16" ht="195" customFormat="1" customHeight="1" s="92">
-      <c r="A16" s="273" t="n"/>
-      <c r="B16" s="273" t="n"/>
+      <c r="A16" s="284" t="n"/>
+      <c r="B16" s="284" t="n"/>
       <c r="C16" s="108" t="inlineStr">
         <is>
           <t>HPMP II (AC Unit); HPMP II (PMU)</t>
@@ -4104,8 +4076,8 @@
       </c>
     </row>
     <row r="17" ht="105" customHeight="1">
-      <c r="A17" s="274" t="n"/>
-      <c r="B17" s="274" t="n"/>
+      <c r="A17" s="285" t="n"/>
+      <c r="B17" s="285" t="n"/>
       <c r="C17" s="75" t="inlineStr">
         <is>
           <t>HPMP II (AC Unit); HPMP II (PMU)</t>
@@ -4591,7 +4563,7 @@
       </c>
     </row>
     <row r="2" ht="105" customHeight="1">
-      <c r="A2" s="292" t="inlineStr">
+      <c r="A2" s="286" t="inlineStr">
         <is>
           <t>00115022</t>
         </is>
@@ -4692,7 +4664,7 @@
       <c r="K4" s="42" t="n"/>
     </row>
     <row r="5" ht="105" customHeight="1">
-      <c r="A5" s="292" t="inlineStr">
+      <c r="A5" s="286" t="inlineStr">
         <is>
           <t>00116395</t>
         </is>
@@ -4802,7 +4774,7 @@
       <c r="K8" s="56" t="n"/>
     </row>
     <row r="9" ht="45" customFormat="1" customHeight="1" s="13">
-      <c r="A9" s="293" t="inlineStr">
+      <c r="A9" s="287" t="inlineStr">
         <is>
           <t>000 98085</t>
         </is>
@@ -5584,288 +5556,288 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="294" t="inlineStr">
+      <c r="A1" s="288" t="inlineStr">
         <is>
           <t>Beneficiary Category</t>
         </is>
       </c>
-      <c r="B1" s="294" t="inlineStr">
+      <c r="B1" s="288" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
     </row>
     <row r="2" ht="45" customHeight="1">
-      <c r="A2" s="295" t="inlineStr">
+      <c r="A2" s="289" t="inlineStr">
         <is>
           <t>Electricity Access</t>
         </is>
       </c>
-      <c r="B2" s="295" t="inlineStr">
+      <c r="B2" s="289" t="inlineStr">
         <is>
           <t>Number of people, disaggregated by sex, who gain access to clean electricity (direct access to electricity, lighting, cooling, etc.).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="295" t="inlineStr">
+      <c r="A3" s="289" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
         </is>
       </c>
-      <c r="B3" s="295" t="inlineStr">
+      <c r="B3" s="289" t="inlineStr">
         <is>
           <t>Installed renewable or clean-energy power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="295" t="inlineStr">
+      <c r="A4" s="289" t="inlineStr">
         <is>
           <t>Energy Storage (MW)</t>
         </is>
       </c>
-      <c r="B4" s="295" t="inlineStr">
+      <c r="B4" s="289" t="inlineStr">
         <is>
           <t>Installed energy storage power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="295" t="inlineStr">
+      <c r="A5" s="289" t="inlineStr">
         <is>
           <t>Clean Cooking</t>
         </is>
       </c>
-      <c r="B5" s="295" t="inlineStr">
+      <c r="B5" s="289" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean cooking (direct access to clean cook stoves, clean fuels, biomass, etc.).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="90" customHeight="1">
-      <c r="A6" s="295" t="inlineStr">
+      <c r="A6" s="289" t="inlineStr">
         <is>
           <t>Clean Heating</t>
         </is>
       </c>
-      <c r="B6" s="295" t="inlineStr">
+      <c r="B6" s="289" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean heating (direct access to clean electric heaters, clean fuels, etc.).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="295" t="inlineStr">
+      <c r="A7" s="289" t="inlineStr">
         <is>
           <t>Agriculture and Food System</t>
         </is>
       </c>
-      <c r="B7" s="295" t="inlineStr">
+      <c r="B7" s="289" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean, affordable, and sustainable energy for agricultural and food-system activities.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="295" t="inlineStr">
+      <c r="A8" s="289" t="inlineStr">
         <is>
           <t>Health Services</t>
         </is>
       </c>
-      <c r="B8" s="295" t="inlineStr">
+      <c r="B8" s="289" t="inlineStr">
         <is>
           <t>Number of people who gain access to health care facilities through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="45" customHeight="1">
-      <c r="A9" s="295" t="inlineStr">
+      <c r="A9" s="289" t="inlineStr">
         <is>
           <t>Water Services</t>
         </is>
       </c>
-      <c r="B9" s="295" t="inlineStr">
+      <c r="B9" s="289" t="inlineStr">
         <is>
           <t>Number of people who gain access to water services through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1">
-      <c r="A10" s="295" t="inlineStr">
+      <c r="A10" s="289" t="inlineStr">
         <is>
           <t>Education Services</t>
         </is>
       </c>
-      <c r="B10" s="295" t="inlineStr">
+      <c r="B10" s="289" t="inlineStr">
         <is>
           <t>Number of people who gain access to education services through clean energy systems, including students and teachers.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="295" t="inlineStr">
+      <c r="A11" s="289" t="inlineStr">
         <is>
           <t>Transportation and E-mobility Services</t>
         </is>
       </c>
-      <c r="B11" s="295" t="inlineStr">
+      <c r="B11" s="289" t="inlineStr">
         <is>
           <t>Number of people served or energy saved from transport and e-mobility interventions, such as electric vehicles or charging stations.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1">
-      <c r="A12" s="295" t="inlineStr">
+      <c r="A12" s="289" t="inlineStr">
         <is>
           <t>Energy Efficiency Services</t>
         </is>
       </c>
-      <c r="B12" s="295" t="inlineStr">
+      <c r="B12" s="289" t="inlineStr">
         <is>
           <t>Energy saved from energy-efficiency interventions, such as building or industrial efficiency.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="295" t="inlineStr">
+      <c r="A13" s="289" t="inlineStr">
         <is>
           <t>Energy Infrastructure Services</t>
         </is>
       </c>
-      <c r="B13" s="295" t="inlineStr">
+      <c r="B13" s="289" t="inlineStr">
         <is>
           <t>Number of people benefiting from energy infrastructure interventions, such as streetlights, transmission, and distribution lines.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="295" t="inlineStr">
+      <c r="A14" s="289" t="inlineStr">
         <is>
           <t>Other Energy Services</t>
         </is>
       </c>
-      <c r="B14" s="295" t="inlineStr">
+      <c r="B14" s="289" t="inlineStr">
         <is>
           <t>Access to other energy services not captured by the categories above.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="295" t="inlineStr">
+      <c r="A15" s="289" t="inlineStr">
         <is>
           <t>Financing support</t>
         </is>
       </c>
-      <c r="B15" s="295" t="inlineStr">
+      <c r="B15" s="289" t="inlineStr">
         <is>
           <t>Support for the development of the energy market ecosystem.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="295" t="inlineStr">
+      <c r="A16" s="289" t="inlineStr">
         <is>
           <t>Medium Enterprises</t>
         </is>
       </c>
-      <c r="B16" s="295" t="inlineStr">
+      <c r="B16" s="289" t="inlineStr">
         <is>
           <t>Support for the development of medium enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="295" t="inlineStr">
+      <c r="A17" s="289" t="inlineStr">
         <is>
           <t>Small Enterprises</t>
         </is>
       </c>
-      <c r="B17" s="295" t="inlineStr">
+      <c r="B17" s="289" t="inlineStr">
         <is>
           <t>Support for the development of small enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="295" t="inlineStr">
+      <c r="A18" s="289" t="inlineStr">
         <is>
           <t>Capacity Building Training</t>
         </is>
       </c>
-      <c r="B18" s="295" t="inlineStr">
+      <c r="B18" s="289" t="inlineStr">
         <is>
           <t>Number of people benefiting from training on energy business, energy finance, or related implementation capacity.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="75" customHeight="1">
-      <c r="A19" s="295" t="inlineStr">
+      <c r="A19" s="289" t="inlineStr">
         <is>
           <t>Entrepreneurship Training</t>
         </is>
       </c>
-      <c r="B19" s="295" t="inlineStr">
+      <c r="B19" s="289" t="inlineStr">
         <is>
           <t>Training for enterprises on the energy business, assumed to result in direct beneficiaries.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="295" t="inlineStr">
+      <c r="A20" s="289" t="inlineStr">
         <is>
           <t>Market Intervention</t>
         </is>
       </c>
-      <c r="B20" s="295" t="inlineStr">
+      <c r="B20" s="289" t="inlineStr">
         <is>
           <t>Volume of investment leveraged or barriers removed for clean, reliable, affordable, and sustainable energy solutions.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="295" t="inlineStr">
+      <c r="A21" s="289" t="inlineStr">
         <is>
           <t>Campaign Participant</t>
         </is>
       </c>
-      <c r="B21" s="295" t="inlineStr">
+      <c r="B21" s="289" t="inlineStr">
         <is>
           <t>Individuals who participate in advocacy or awareness campaigns on energy.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="295" t="inlineStr">
+      <c r="A22" s="289" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
         </is>
       </c>
-      <c r="B22" s="295" t="inlineStr">
+      <c r="B22" s="289" t="inlineStr">
         <is>
           <t>Policies, regulations, strategies, plans, or frameworks developed, approved, implemented, or strengthened.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="295" t="inlineStr">
+      <c r="A23" s="289" t="inlineStr">
         <is>
           <t>GHG Emissions Reduction</t>
         </is>
       </c>
-      <c r="B23" s="295" t="inlineStr">
+      <c r="B23" s="289" t="inlineStr">
         <is>
           <t>Greenhouse gas emissions reduced or mitigated, in tCO2e.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="295" t="inlineStr">
+      <c r="A24" s="289" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B24" s="295" t="inlineStr">
+      <c r="B24" s="289" t="inlineStr">
         <is>
           <t>Energy-related output that does not fit the standard categories above.</t>
         </is>
